--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-29 19:15 local</t>
+          <t>2026-08-29 19:17 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-29 19:17 local</t>
+          <t>2026-08-30 06:40 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-30 06:40 local</t>
+          <t>2026-08-30 14:26 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
@@ -28,10 +28,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -400,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$8</f>
+              <f>'GPU Rental'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$8</f>
+              <f>'GPU Rental'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -432,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$8</f>
+              <f>'GPU Rental'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$8</f>
+              <f>'GPU Rental'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -464,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$8</f>
+              <f>'GPU Rental'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$8</f>
+              <f>'GPU Rental'!$D$2:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -496,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$8</f>
+              <f>'GPU Rental'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$8</f>
+              <f>'GPU Rental'!$E$2:$E$9</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$8</f>
+              <f>'GPU Rental'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$8</f>
+              <f>'GPU Rental'!$F$2:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$8</f>
+              <f>'GPU Rental'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$8</f>
+              <f>'GPU Rental'!$G$2:$G$9</f>
             </numRef>
           </val>
         </ser>
@@ -592,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$8</f>
+              <f>'GPU Rental'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$8</f>
+              <f>'GPU Rental'!$H$2:$H$9</f>
             </numRef>
           </val>
         </ser>
@@ -1235,7 +1236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1682,8 +1683,62 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I9" s="4">
+        <f>IF(OR(B9="",B8=""),"",B9/B8-1)</f>
+        <v/>
+      </c>
+      <c r="J9" s="4">
+        <f>IF(OR(C9="",C8=""),"",C9/C8-1)</f>
+        <v/>
+      </c>
+      <c r="K9" s="4">
+        <f>IF(OR(D9="",D8=""),"",D9/D8-1)</f>
+        <v/>
+      </c>
+      <c r="L9" s="4">
+        <f>IF(OR(E9="",E8=""),"",E9/E8-1)</f>
+        <v/>
+      </c>
+      <c r="M9" s="4">
+        <f>IF(OR(F9="",F8=""),"",F9/F8-1)</f>
+        <v/>
+      </c>
+      <c r="N9" s="4">
+        <f>IF(OR(G9="",G8=""),"",G9/G8-1)</f>
+        <v/>
+      </c>
+      <c r="O9" s="4">
+        <f>IF(OR(H9="",H8=""),"",H9/H8-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O8"/>
+  <autoFilter ref="A1:O9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31623,7 +31678,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-08-29  (7 rows)</t>
+          <t>2026-08-23 to 2026-08-30  (8 rows)</t>
         </is>
       </c>
     </row>
@@ -31635,7 +31690,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-30 14:26 local</t>
+          <t>2026-08-30 16:51 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
   </definedNames>
@@ -1749,7 +1749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3508,8 +3508,764 @@
         <v>2.3079</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>1.6025</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>1.5743</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>1.7115</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>1.6308</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>1.5865</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>1.5422</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>1.4978</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>1.4189</v>
+      </c>
+      <c r="L14" s="11" t="n">
+        <v>1.3631</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>1.3302</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>1.3204</v>
+      </c>
+      <c r="O14" s="11" t="n">
+        <v>1.3336</v>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>1.3697</v>
+      </c>
+      <c r="Q14" s="11" t="n">
+        <v>1.3854</v>
+      </c>
+      <c r="R14" s="11" t="n">
+        <v>1.397</v>
+      </c>
+      <c r="S14" s="11" t="n">
+        <v>1.4047</v>
+      </c>
+      <c r="T14" s="11" t="n">
+        <v>1.4083</v>
+      </c>
+      <c r="U14" s="11" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="V14" s="11" t="n">
+        <v>1.4037</v>
+      </c>
+      <c r="W14" s="11" t="n">
+        <v>1.3954</v>
+      </c>
+      <c r="X14" s="11" t="n">
+        <v>1.3831</v>
+      </c>
+      <c r="Y14" s="11" t="n">
+        <v>1.3668</v>
+      </c>
+      <c r="Z14" s="11" t="n">
+        <v>1.3465</v>
+      </c>
+      <c r="AA14" s="11" t="n">
+        <v>1.3223</v>
+      </c>
+      <c r="AB14" s="11" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="AC14" s="11" t="n">
+        <v>1.2672</v>
+      </c>
+      <c r="AD14" s="11" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="AE14" s="11" t="n">
+        <v>1.2244</v>
+      </c>
+      <c r="AF14" s="11" t="n">
+        <v>1.2083</v>
+      </c>
+      <c r="AG14" s="11" t="n">
+        <v>1.1958</v>
+      </c>
+      <c r="AH14" s="11" t="n">
+        <v>1.1869</v>
+      </c>
+      <c r="AI14" s="11" t="n">
+        <v>1.1815</v>
+      </c>
+      <c r="AJ14" s="11" t="n">
+        <v>1.1797</v>
+      </c>
+      <c r="AK14" s="11" t="n">
+        <v>1.1815</v>
+      </c>
+      <c r="AL14" s="11" t="n">
+        <v>1.1869</v>
+      </c>
+      <c r="AM14" s="11" t="n">
+        <v>1.1958</v>
+      </c>
+      <c r="AN14" s="11" t="n">
+        <v>1.2083</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>1.6025</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>1.5238</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>1.5924</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>1.6247</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>1.6207</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>1.6094</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>1.5945</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>1.5748</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>1.5516</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>1.5286</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>1.5081</v>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>1.4914</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>1.4796</v>
+      </c>
+      <c r="Q15" s="11" t="n">
+        <v>1.4718</v>
+      </c>
+      <c r="R15" s="11" t="n">
+        <v>1.4661</v>
+      </c>
+      <c r="S15" s="11" t="n">
+        <v>1.4617</v>
+      </c>
+      <c r="T15" s="11" t="n">
+        <v>1.4583</v>
+      </c>
+      <c r="U15" s="11" t="n">
+        <v>1.4554</v>
+      </c>
+      <c r="V15" s="11" t="n">
+        <v>1.4526</v>
+      </c>
+      <c r="W15" s="11" t="n">
+        <v>1.4499</v>
+      </c>
+      <c r="X15" s="11" t="n">
+        <v>1.4469</v>
+      </c>
+      <c r="Y15" s="11" t="n">
+        <v>1.4434</v>
+      </c>
+      <c r="Z15" s="11" t="n">
+        <v>1.4395</v>
+      </c>
+      <c r="AA15" s="11" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="AB15" s="11" t="n">
+        <v>1.4297</v>
+      </c>
+      <c r="AC15" s="11" t="n">
+        <v>1.4237</v>
+      </c>
+      <c r="AD15" s="11" t="n">
+        <v>1.4172</v>
+      </c>
+      <c r="AE15" s="11" t="n">
+        <v>1.4105</v>
+      </c>
+      <c r="AF15" s="11" t="n">
+        <v>1.4035</v>
+      </c>
+      <c r="AG15" s="11" t="n">
+        <v>1.3965</v>
+      </c>
+      <c r="AH15" s="11" t="n">
+        <v>1.3897</v>
+      </c>
+      <c r="AI15" s="11" t="n">
+        <v>1.3831</v>
+      </c>
+      <c r="AJ15" s="11" t="n">
+        <v>1.3767</v>
+      </c>
+      <c r="AK15" s="11" t="n">
+        <v>1.3708</v>
+      </c>
+      <c r="AL15" s="11" t="n">
+        <v>1.3653</v>
+      </c>
+      <c r="AM15" s="11" t="n">
+        <v>1.3603</v>
+      </c>
+      <c r="AN15" s="11" t="n">
+        <v>1.3559</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>5.5835</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>5.5811</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>5.6788</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>5.489</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>5.3021</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>5.2052</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>5.1983</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>5.1489</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <v>5.0978</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>5.0451</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>4.9908</v>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>4.9349</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>4.8774</v>
+      </c>
+      <c r="Q16" s="11" t="n">
+        <v>4.7023</v>
+      </c>
+      <c r="R16" s="11" t="n">
+        <v>4.5615</v>
+      </c>
+      <c r="S16" s="11" t="n">
+        <v>4.455</v>
+      </c>
+      <c r="T16" s="11" t="n">
+        <v>4.3827</v>
+      </c>
+      <c r="U16" s="11" t="n">
+        <v>4.3447</v>
+      </c>
+      <c r="V16" s="11" t="n">
+        <v>4.3411</v>
+      </c>
+      <c r="W16" s="11" t="n">
+        <v>4.3717</v>
+      </c>
+      <c r="X16" s="11" t="n">
+        <v>4.4366</v>
+      </c>
+      <c r="Y16" s="11" t="n">
+        <v>4.5358</v>
+      </c>
+      <c r="Z16" s="11" t="n">
+        <v>4.6692</v>
+      </c>
+      <c r="AA16" s="11" t="n">
+        <v>4.837</v>
+      </c>
+      <c r="AB16" s="11" t="n">
+        <v>5.039</v>
+      </c>
+      <c r="AC16" s="11" t="n">
+        <v>5.1929</v>
+      </c>
+      <c r="AD16" s="11" t="n">
+        <v>5.3262</v>
+      </c>
+      <c r="AE16" s="11" t="n">
+        <v>5.439</v>
+      </c>
+      <c r="AF16" s="11" t="n">
+        <v>5.5313</v>
+      </c>
+      <c r="AG16" s="11" t="n">
+        <v>5.6031</v>
+      </c>
+      <c r="AH16" s="11" t="n">
+        <v>5.6544</v>
+      </c>
+      <c r="AI16" s="11" t="n">
+        <v>5.6851</v>
+      </c>
+      <c r="AJ16" s="11" t="n">
+        <v>5.6954</v>
+      </c>
+      <c r="AK16" s="11" t="n">
+        <v>5.6851</v>
+      </c>
+      <c r="AL16" s="11" t="n">
+        <v>5.6544</v>
+      </c>
+      <c r="AM16" s="11" t="n">
+        <v>5.6031</v>
+      </c>
+      <c r="AN16" s="11" t="n">
+        <v>5.5313</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>5.5835</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>5.5562</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>5.605</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>5.606</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>5.5515</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>5.4904</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>5.4411</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>5.4029</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>5.3679</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>5.335</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>5.3033</v>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>5.2724</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>5.2419</v>
+      </c>
+      <c r="Q17" s="11" t="n">
+        <v>5.2069</v>
+      </c>
+      <c r="R17" s="11" t="n">
+        <v>5.1656</v>
+      </c>
+      <c r="S17" s="11" t="n">
+        <v>5.1216</v>
+      </c>
+      <c r="T17" s="11" t="n">
+        <v>5.0775</v>
+      </c>
+      <c r="U17" s="11" t="n">
+        <v>5.0353</v>
+      </c>
+      <c r="V17" s="11" t="n">
+        <v>4.9967</v>
+      </c>
+      <c r="W17" s="11" t="n">
+        <v>4.9629</v>
+      </c>
+      <c r="X17" s="11" t="n">
+        <v>4.9348</v>
+      </c>
+      <c r="Y17" s="11" t="n">
+        <v>4.9133</v>
+      </c>
+      <c r="Z17" s="11" t="n">
+        <v>4.899</v>
+      </c>
+      <c r="AA17" s="11" t="n">
+        <v>4.8926</v>
+      </c>
+      <c r="AB17" s="11" t="n">
+        <v>4.8943</v>
+      </c>
+      <c r="AC17" s="11" t="n">
+        <v>4.9033</v>
+      </c>
+      <c r="AD17" s="11" t="n">
+        <v>4.917</v>
+      </c>
+      <c r="AE17" s="11" t="n">
+        <v>4.9343</v>
+      </c>
+      <c r="AF17" s="11" t="n">
+        <v>4.9541</v>
+      </c>
+      <c r="AG17" s="11" t="n">
+        <v>4.9753</v>
+      </c>
+      <c r="AH17" s="11" t="n">
+        <v>4.9971</v>
+      </c>
+      <c r="AI17" s="11" t="n">
+        <v>5.0189</v>
+      </c>
+      <c r="AJ17" s="11" t="n">
+        <v>5.0399</v>
+      </c>
+      <c r="AK17" s="11" t="n">
+        <v>5.0597</v>
+      </c>
+      <c r="AL17" s="11" t="n">
+        <v>5.0777</v>
+      </c>
+      <c r="AM17" s="11" t="n">
+        <v>5.0934</v>
+      </c>
+      <c r="AN17" s="11" t="n">
+        <v>5.1067</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>2.6503</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>2.5478</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>2.5159</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>2.5321</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>2.5918</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>2.5485</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>2.4024</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>2.2246</v>
+      </c>
+      <c r="L18" s="11" t="n">
+        <v>2.1021</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>2.0352</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>2.0236</v>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>2.0675</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>2.1668</v>
+      </c>
+      <c r="Q18" s="11" t="n">
+        <v>2.1904</v>
+      </c>
+      <c r="R18" s="11" t="n">
+        <v>2.2119</v>
+      </c>
+      <c r="S18" s="11" t="n">
+        <v>2.2312</v>
+      </c>
+      <c r="T18" s="11" t="n">
+        <v>2.2485</v>
+      </c>
+      <c r="U18" s="11" t="n">
+        <v>2.2636</v>
+      </c>
+      <c r="V18" s="11" t="n">
+        <v>2.2765</v>
+      </c>
+      <c r="W18" s="11" t="n">
+        <v>2.2873</v>
+      </c>
+      <c r="X18" s="11" t="n">
+        <v>2.296</v>
+      </c>
+      <c r="Y18" s="11" t="n">
+        <v>2.3026</v>
+      </c>
+      <c r="Z18" s="11" t="n">
+        <v>2.3071</v>
+      </c>
+      <c r="AA18" s="11" t="n">
+        <v>2.3094</v>
+      </c>
+      <c r="AB18" s="11" t="n">
+        <v>2.3095</v>
+      </c>
+      <c r="AC18" s="11" t="n">
+        <v>2.3239</v>
+      </c>
+      <c r="AD18" s="11" t="n">
+        <v>2.3363</v>
+      </c>
+      <c r="AE18" s="11" t="n">
+        <v>2.3468</v>
+      </c>
+      <c r="AF18" s="11" t="n">
+        <v>2.3553</v>
+      </c>
+      <c r="AG18" s="11" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AH18" s="11" t="n">
+        <v>2.3668</v>
+      </c>
+      <c r="AI18" s="11" t="n">
+        <v>2.3697</v>
+      </c>
+      <c r="AJ18" s="11" t="n">
+        <v>2.3706</v>
+      </c>
+      <c r="AK18" s="11" t="n">
+        <v>2.3697</v>
+      </c>
+      <c r="AL18" s="11" t="n">
+        <v>2.3668</v>
+      </c>
+      <c r="AM18" s="11" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AN18" s="11" t="n">
+        <v>2.3553</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>2.6503</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>2.5597</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>2.5438</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>2.5359</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>2.5445</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>2.5514</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>2.5402</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>2.5071</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>2.4636</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>2.4192</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>2.3797</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>2.3489</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>2.3292</v>
+      </c>
+      <c r="Q19" s="11" t="n">
+        <v>2.3177</v>
+      </c>
+      <c r="R19" s="11" t="n">
+        <v>2.3093</v>
+      </c>
+      <c r="S19" s="11" t="n">
+        <v>2.3035</v>
+      </c>
+      <c r="T19" s="11" t="n">
+        <v>2.2995</v>
+      </c>
+      <c r="U19" s="11" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="V19" s="11" t="n">
+        <v>2.2955</v>
+      </c>
+      <c r="W19" s="11" t="n">
+        <v>2.2948</v>
+      </c>
+      <c r="X19" s="11" t="n">
+        <v>2.2946</v>
+      </c>
+      <c r="Y19" s="11" t="n">
+        <v>2.2949</v>
+      </c>
+      <c r="Z19" s="11" t="n">
+        <v>2.2953</v>
+      </c>
+      <c r="AA19" s="11" t="n">
+        <v>2.2959</v>
+      </c>
+      <c r="AB19" s="11" t="n">
+        <v>2.2965</v>
+      </c>
+      <c r="AC19" s="11" t="n">
+        <v>2.2973</v>
+      </c>
+      <c r="AD19" s="11" t="n">
+        <v>2.2986</v>
+      </c>
+      <c r="AE19" s="11" t="n">
+        <v>2.3002</v>
+      </c>
+      <c r="AF19" s="11" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="AG19" s="11" t="n">
+        <v>2.3039</v>
+      </c>
+      <c r="AH19" s="11" t="n">
+        <v>2.306</v>
+      </c>
+      <c r="AI19" s="11" t="n">
+        <v>2.308</v>
+      </c>
+      <c r="AJ19" s="11" t="n">
+        <v>2.3099</v>
+      </c>
+      <c r="AK19" s="11" t="n">
+        <v>2.3118</v>
+      </c>
+      <c r="AL19" s="11" t="n">
+        <v>2.3134</v>
+      </c>
+      <c r="AM19" s="11" t="n">
+        <v>2.3149</v>
+      </c>
+      <c r="AN19" s="11" t="n">
+        <v>2.3161</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN13"/>
+  <autoFilter ref="A1:AN19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31582,7 +32338,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-08-29  (2 daily snapshots, 12 curve rows)</t>
+          <t>2026-08-28 to 2026-08-30  (3 daily snapshots, 18 curve rows)</t>
         </is>
       </c>
     </row>
@@ -31690,7 +32446,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-30 16:51 local</t>
+          <t>2026-08-30 19:21 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$8</f>
+              <f>'Daily Index'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$8</f>
+              <f>'Daily Index'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$8</f>
+              <f>'Daily Index'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$8</f>
+              <f>'Daily Index'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$8</f>
+              <f>'Daily Index'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$8</f>
+              <f>'Daily Index'!$D$2:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$9</f>
+              <f>'GPU Rental'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$9</f>
+              <f>'GPU Rental'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$9</f>
+              <f>'GPU Rental'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$9</f>
+              <f>'GPU Rental'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$9</f>
+              <f>'GPU Rental'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$9</f>
+              <f>'GPU Rental'!$D$2:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$9</f>
+              <f>'GPU Rental'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$9</f>
+              <f>'GPU Rental'!$E$2:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$9</f>
+              <f>'GPU Rental'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$9</f>
+              <f>'GPU Rental'!$F$2:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$9</f>
+              <f>'GPU Rental'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$9</f>
+              <f>'GPU Rental'!$G$2:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$9</f>
+              <f>'GPU Rental'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$9</f>
+              <f>'GPU Rental'!$H$2:$H$10</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1224,8 +1224,60 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>1.0296</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>0.5284</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>2.3298</v>
+      </c>
+      <c r="E9" s="4">
+        <f>IF(OR(B9="",B8=""),"",B9/B8-1)</f>
+        <v/>
+      </c>
+      <c r="F9" s="4">
+        <f>IF(OR(C9="",C8=""),"",C9/C8-1)</f>
+        <v/>
+      </c>
+      <c r="G9" s="4">
+        <f>IF(OR(D9="",D8=""),"",D9/D8-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>1.0018</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>2.2553</v>
+      </c>
+      <c r="E10" s="4">
+        <f>IF(OR(B10="",B9=""),"",B10/B9-1)</f>
+        <v/>
+      </c>
+      <c r="F10" s="4">
+        <f>IF(OR(C10="",C9=""),"",C10/C9-1)</f>
+        <v/>
+      </c>
+      <c r="G10" s="4">
+        <f>IF(OR(D10="",D9=""),"",D10/D9-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1236,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1737,8 +1789,62 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I10" s="4">
+        <f>IF(OR(B10="",B9=""),"",B10/B9-1)</f>
+        <v/>
+      </c>
+      <c r="J10" s="4">
+        <f>IF(OR(C10="",C9=""),"",C10/C9-1)</f>
+        <v/>
+      </c>
+      <c r="K10" s="4">
+        <f>IF(OR(D10="",D9=""),"",D10/D9-1)</f>
+        <v/>
+      </c>
+      <c r="L10" s="4">
+        <f>IF(OR(E10="",E9=""),"",E10/E9-1)</f>
+        <v/>
+      </c>
+      <c r="M10" s="4">
+        <f>IF(OR(F10="",F9=""),"",F10/F9-1)</f>
+        <v/>
+      </c>
+      <c r="N10" s="4">
+        <f>IF(OR(G10="",G9=""),"",G10/G9-1)</f>
+        <v/>
+      </c>
+      <c r="O10" s="4">
+        <f>IF(OR(H10="",H9=""),"",H10/H9-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O9"/>
+  <autoFilter ref="A1:O10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32410,7 +32516,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-08-28  (7 rows)</t>
+          <t>2026-08-22 to 2026-08-30  (9 rows)</t>
         </is>
       </c>
     </row>
@@ -32434,7 +32540,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-08-30  (8 rows)</t>
+          <t>2026-08-23 to 2026-08-31  (9 rows)</t>
         </is>
       </c>
     </row>
@@ -32446,7 +32552,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-30 19:21 local</t>
+          <t>2026-08-31 17:05 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
   </definedNames>
@@ -1855,7 +1855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AN25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4370,8 +4370,764 @@
         <v>2.3161</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>1.6027</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>1.5855</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>1.7119</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>1.635</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>1.5927</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>1.5491</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>1.5042</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>1.4255</v>
+      </c>
+      <c r="L20" s="11" t="n">
+        <v>1.3697</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>1.3369</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>1.376</v>
+      </c>
+      <c r="Q20" s="11" t="n">
+        <v>1.3914</v>
+      </c>
+      <c r="R20" s="11" t="n">
+        <v>1.4029</v>
+      </c>
+      <c r="S20" s="11" t="n">
+        <v>1.4104</v>
+      </c>
+      <c r="T20" s="11" t="n">
+        <v>1.4139</v>
+      </c>
+      <c r="U20" s="11" t="n">
+        <v>1.4135</v>
+      </c>
+      <c r="V20" s="11" t="n">
+        <v>1.4092</v>
+      </c>
+      <c r="W20" s="11" t="n">
+        <v>1.4008</v>
+      </c>
+      <c r="X20" s="11" t="n">
+        <v>1.3886</v>
+      </c>
+      <c r="Y20" s="11" t="n">
+        <v>1.3723</v>
+      </c>
+      <c r="Z20" s="11" t="n">
+        <v>1.3522</v>
+      </c>
+      <c r="AA20" s="11" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="AB20" s="11" t="n">
+        <v>1.2999</v>
+      </c>
+      <c r="AC20" s="11" t="n">
+        <v>1.2732</v>
+      </c>
+      <c r="AD20" s="11" t="n">
+        <v>1.2501</v>
+      </c>
+      <c r="AE20" s="11" t="n">
+        <v>1.2305</v>
+      </c>
+      <c r="AF20" s="11" t="n">
+        <v>1.2144</v>
+      </c>
+      <c r="AG20" s="11" t="n">
+        <v>1.202</v>
+      </c>
+      <c r="AH20" s="11" t="n">
+        <v>1.1931</v>
+      </c>
+      <c r="AI20" s="11" t="n">
+        <v>1.1877</v>
+      </c>
+      <c r="AJ20" s="11" t="n">
+        <v>1.1859</v>
+      </c>
+      <c r="AK20" s="11" t="n">
+        <v>1.1877</v>
+      </c>
+      <c r="AL20" s="11" t="n">
+        <v>1.1931</v>
+      </c>
+      <c r="AM20" s="11" t="n">
+        <v>1.202</v>
+      </c>
+      <c r="AN20" s="11" t="n">
+        <v>1.2144</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>1.6027</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>1.5393</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>1.6025</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>1.6318</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>1.6273</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>1.6161</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>1.6012</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>1.5814</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>1.5582</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>1.5352</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>1.5147</v>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>1.4981</v>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>1.4862</v>
+      </c>
+      <c r="Q21" s="11" t="n">
+        <v>1.4784</v>
+      </c>
+      <c r="R21" s="11" t="n">
+        <v>1.4726</v>
+      </c>
+      <c r="S21" s="11" t="n">
+        <v>1.4682</v>
+      </c>
+      <c r="T21" s="11" t="n">
+        <v>1.4647</v>
+      </c>
+      <c r="U21" s="11" t="n">
+        <v>1.4618</v>
+      </c>
+      <c r="V21" s="11" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="W21" s="11" t="n">
+        <v>1.4561</v>
+      </c>
+      <c r="X21" s="11" t="n">
+        <v>1.4531</v>
+      </c>
+      <c r="Y21" s="11" t="n">
+        <v>1.4497</v>
+      </c>
+      <c r="Z21" s="11" t="n">
+        <v>1.4457</v>
+      </c>
+      <c r="AA21" s="11" t="n">
+        <v>1.4411</v>
+      </c>
+      <c r="AB21" s="11" t="n">
+        <v>1.4358</v>
+      </c>
+      <c r="AC21" s="11" t="n">
+        <v>1.4298</v>
+      </c>
+      <c r="AD21" s="11" t="n">
+        <v>1.4234</v>
+      </c>
+      <c r="AE21" s="11" t="n">
+        <v>1.4166</v>
+      </c>
+      <c r="AF21" s="11" t="n">
+        <v>1.4096</v>
+      </c>
+      <c r="AG21" s="11" t="n">
+        <v>1.4027</v>
+      </c>
+      <c r="AH21" s="11" t="n">
+        <v>1.3958</v>
+      </c>
+      <c r="AI21" s="11" t="n">
+        <v>1.3892</v>
+      </c>
+      <c r="AJ21" s="11" t="n">
+        <v>1.3829</v>
+      </c>
+      <c r="AK21" s="11" t="n">
+        <v>1.3769</v>
+      </c>
+      <c r="AL21" s="11" t="n">
+        <v>1.3714</v>
+      </c>
+      <c r="AM21" s="11" t="n">
+        <v>1.3664</v>
+      </c>
+      <c r="AN21" s="11" t="n">
+        <v>1.362</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>5.6205</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>5.576</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>5.7801</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>5.5459</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>5.3292</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>5.2237</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>5.2292</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>5.1835</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>5.1349</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>5.0834</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>5.029</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>4.9717</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>4.9115</v>
+      </c>
+      <c r="Q22" s="11" t="n">
+        <v>4.7339</v>
+      </c>
+      <c r="R22" s="11" t="n">
+        <v>4.5912</v>
+      </c>
+      <c r="S22" s="11" t="n">
+        <v>4.4832</v>
+      </c>
+      <c r="T22" s="11" t="n">
+        <v>4.4099</v>
+      </c>
+      <c r="U22" s="11" t="n">
+        <v>4.3714</v>
+      </c>
+      <c r="V22" s="11" t="n">
+        <v>4.3677</v>
+      </c>
+      <c r="W22" s="11" t="n">
+        <v>4.3988</v>
+      </c>
+      <c r="X22" s="11" t="n">
+        <v>4.4646</v>
+      </c>
+      <c r="Y22" s="11" t="n">
+        <v>4.5651</v>
+      </c>
+      <c r="Z22" s="11" t="n">
+        <v>4.7005</v>
+      </c>
+      <c r="AA22" s="11" t="n">
+        <v>4.8706</v>
+      </c>
+      <c r="AB22" s="11" t="n">
+        <v>5.0754</v>
+      </c>
+      <c r="AC22" s="11" t="n">
+        <v>5.2314</v>
+      </c>
+      <c r="AD22" s="11" t="n">
+        <v>5.3666</v>
+      </c>
+      <c r="AE22" s="11" t="n">
+        <v>5.481</v>
+      </c>
+      <c r="AF22" s="11" t="n">
+        <v>5.5746</v>
+      </c>
+      <c r="AG22" s="11" t="n">
+        <v>5.6473</v>
+      </c>
+      <c r="AH22" s="11" t="n">
+        <v>5.6993</v>
+      </c>
+      <c r="AI22" s="11" t="n">
+        <v>5.7305</v>
+      </c>
+      <c r="AJ22" s="11" t="n">
+        <v>5.7409</v>
+      </c>
+      <c r="AK22" s="11" t="n">
+        <v>5.7305</v>
+      </c>
+      <c r="AL22" s="11" t="n">
+        <v>5.6993</v>
+      </c>
+      <c r="AM22" s="11" t="n">
+        <v>5.6473</v>
+      </c>
+      <c r="AN22" s="11" t="n">
+        <v>5.5746</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>5.6205</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>5.5105</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>5.6125</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>5.6415</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>5.5882</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>5.524</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>5.4729</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>5.4348</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>5.4004</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>5.3681</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>5.3369</v>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>5.3063</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>5.276</v>
+      </c>
+      <c r="Q23" s="11" t="n">
+        <v>5.2409</v>
+      </c>
+      <c r="R23" s="11" t="n">
+        <v>5.1993</v>
+      </c>
+      <c r="S23" s="11" t="n">
+        <v>5.155</v>
+      </c>
+      <c r="T23" s="11" t="n">
+        <v>5.1105</v>
+      </c>
+      <c r="U23" s="11" t="n">
+        <v>5.068</v>
+      </c>
+      <c r="V23" s="11" t="n">
+        <v>5.0291</v>
+      </c>
+      <c r="W23" s="11" t="n">
+        <v>4.9949</v>
+      </c>
+      <c r="X23" s="11" t="n">
+        <v>4.9666</v>
+      </c>
+      <c r="Y23" s="11" t="n">
+        <v>4.945</v>
+      </c>
+      <c r="Z23" s="11" t="n">
+        <v>4.9306</v>
+      </c>
+      <c r="AA23" s="11" t="n">
+        <v>4.9242</v>
+      </c>
+      <c r="AB23" s="11" t="n">
+        <v>4.9261</v>
+      </c>
+      <c r="AC23" s="11" t="n">
+        <v>4.9353</v>
+      </c>
+      <c r="AD23" s="11" t="n">
+        <v>4.9493</v>
+      </c>
+      <c r="AE23" s="11" t="n">
+        <v>4.967</v>
+      </c>
+      <c r="AF23" s="11" t="n">
+        <v>4.9871</v>
+      </c>
+      <c r="AG23" s="11" t="n">
+        <v>5.0086</v>
+      </c>
+      <c r="AH23" s="11" t="n">
+        <v>5.0309</v>
+      </c>
+      <c r="AI23" s="11" t="n">
+        <v>5.053</v>
+      </c>
+      <c r="AJ23" s="11" t="n">
+        <v>5.0744</v>
+      </c>
+      <c r="AK23" s="11" t="n">
+        <v>5.0945</v>
+      </c>
+      <c r="AL23" s="11" t="n">
+        <v>5.1128</v>
+      </c>
+      <c r="AM23" s="11" t="n">
+        <v>5.1288</v>
+      </c>
+      <c r="AN23" s="11" t="n">
+        <v>5.1423</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>2.6195</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>2.5305</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>2.4979</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>2.5143</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>2.5743</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>2.5307</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>2.3838</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>2.2045</v>
+      </c>
+      <c r="L24" s="11" t="n">
+        <v>2.0813</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>2.0141</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>2.0028</v>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>2.0476</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>2.1483</v>
+      </c>
+      <c r="Q24" s="11" t="n">
+        <v>2.1731</v>
+      </c>
+      <c r="R24" s="11" t="n">
+        <v>2.1956</v>
+      </c>
+      <c r="S24" s="11" t="n">
+        <v>2.2158</v>
+      </c>
+      <c r="T24" s="11" t="n">
+        <v>2.2337</v>
+      </c>
+      <c r="U24" s="11" t="n">
+        <v>2.2493</v>
+      </c>
+      <c r="V24" s="11" t="n">
+        <v>2.2626</v>
+      </c>
+      <c r="W24" s="11" t="n">
+        <v>2.2736</v>
+      </c>
+      <c r="X24" s="11" t="n">
+        <v>2.2823</v>
+      </c>
+      <c r="Y24" s="11" t="n">
+        <v>2.2887</v>
+      </c>
+      <c r="Z24" s="11" t="n">
+        <v>2.2928</v>
+      </c>
+      <c r="AA24" s="11" t="n">
+        <v>2.2945</v>
+      </c>
+      <c r="AB24" s="11" t="n">
+        <v>2.294</v>
+      </c>
+      <c r="AC24" s="11" t="n">
+        <v>2.3081</v>
+      </c>
+      <c r="AD24" s="11" t="n">
+        <v>2.3204</v>
+      </c>
+      <c r="AE24" s="11" t="n">
+        <v>2.3308</v>
+      </c>
+      <c r="AF24" s="11" t="n">
+        <v>2.3392</v>
+      </c>
+      <c r="AG24" s="11" t="n">
+        <v>2.3458</v>
+      </c>
+      <c r="AH24" s="11" t="n">
+        <v>2.3505</v>
+      </c>
+      <c r="AI24" s="11" t="n">
+        <v>2.3534</v>
+      </c>
+      <c r="AJ24" s="11" t="n">
+        <v>2.3543</v>
+      </c>
+      <c r="AK24" s="11" t="n">
+        <v>2.3534</v>
+      </c>
+      <c r="AL24" s="11" t="n">
+        <v>2.3505</v>
+      </c>
+      <c r="AM24" s="11" t="n">
+        <v>2.3458</v>
+      </c>
+      <c r="AN24" s="11" t="n">
+        <v>2.3392</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>2.6195</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>2.5427</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>2.5264</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>2.5183</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>2.5269</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>2.5338</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>2.5225</v>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>2.4892</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>2.4453</v>
+      </c>
+      <c r="M25" s="11" t="n">
+        <v>2.4006</v>
+      </c>
+      <c r="N25" s="11" t="n">
+        <v>2.3609</v>
+      </c>
+      <c r="O25" s="11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P25" s="11" t="n">
+        <v>2.3103</v>
+      </c>
+      <c r="Q25" s="11" t="n">
+        <v>2.2988</v>
+      </c>
+      <c r="R25" s="11" t="n">
+        <v>2.2906</v>
+      </c>
+      <c r="S25" s="11" t="n">
+        <v>2.285</v>
+      </c>
+      <c r="T25" s="11" t="n">
+        <v>2.2812</v>
+      </c>
+      <c r="U25" s="11" t="n">
+        <v>2.2789</v>
+      </c>
+      <c r="V25" s="11" t="n">
+        <v>2.2776</v>
+      </c>
+      <c r="W25" s="11" t="n">
+        <v>2.2771</v>
+      </c>
+      <c r="X25" s="11" t="n">
+        <v>2.2772</v>
+      </c>
+      <c r="Y25" s="11" t="n">
+        <v>2.2776</v>
+      </c>
+      <c r="Z25" s="11" t="n">
+        <v>2.2782</v>
+      </c>
+      <c r="AA25" s="11" t="n">
+        <v>2.2789</v>
+      </c>
+      <c r="AB25" s="11" t="n">
+        <v>2.2795</v>
+      </c>
+      <c r="AC25" s="11" t="n">
+        <v>2.2804</v>
+      </c>
+      <c r="AD25" s="11" t="n">
+        <v>2.2817</v>
+      </c>
+      <c r="AE25" s="11" t="n">
+        <v>2.2833</v>
+      </c>
+      <c r="AF25" s="11" t="n">
+        <v>2.2852</v>
+      </c>
+      <c r="AG25" s="11" t="n">
+        <v>2.2872</v>
+      </c>
+      <c r="AH25" s="11" t="n">
+        <v>2.2892</v>
+      </c>
+      <c r="AI25" s="11" t="n">
+        <v>2.2912</v>
+      </c>
+      <c r="AJ25" s="11" t="n">
+        <v>2.2932</v>
+      </c>
+      <c r="AK25" s="11" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AL25" s="11" t="n">
+        <v>2.2967</v>
+      </c>
+      <c r="AM25" s="11" t="n">
+        <v>2.2982</v>
+      </c>
+      <c r="AN25" s="11" t="n">
+        <v>2.2994</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN19"/>
+  <autoFilter ref="A1:AN25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32444,7 +33200,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-08-30  (3 daily snapshots, 18 curve rows)</t>
+          <t>2026-08-28 to 2026-08-31  (4 daily snapshots, 24 curve rows)</t>
         </is>
       </c>
     </row>
@@ -32552,7 +33308,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 17:05 local</t>
+          <t>2026-08-31 21:30 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$10</f>
+              <f>'Daily Index'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$10</f>
+              <f>'Daily Index'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$10</f>
+              <f>'Daily Index'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$10</f>
+              <f>'Daily Index'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$10</f>
+              <f>'Daily Index'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$10</f>
+              <f>'Daily Index'!$D$2:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1276,8 +1276,34 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>0.9665</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>0.5179</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>2.1539</v>
+      </c>
+      <c r="E11" s="4">
+        <f>IF(OR(B11="",B10=""),"",B11/B10-1)</f>
+        <v/>
+      </c>
+      <c r="F11" s="4">
+        <f>IF(OR(C11="",C10=""),"",C11/C10-1)</f>
+        <v/>
+      </c>
+      <c r="G11" s="4">
+        <f>IF(OR(D11="",D10=""),"",D11/D10-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33272,7 +33298,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-08-30  (9 rows)</t>
+          <t>2026-08-22 to 2026-08-31  (10 rows)</t>
         </is>
       </c>
     </row>
@@ -33308,7 +33334,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 21:30 local</t>
+          <t>2026-09-01 14:10 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
   </definedNames>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$10</f>
+              <f>'GPU Rental'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$10</f>
+              <f>'GPU Rental'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$10</f>
+              <f>'GPU Rental'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$10</f>
+              <f>'GPU Rental'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$10</f>
+              <f>'GPU Rental'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$10</f>
+              <f>'GPU Rental'!$D$2:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$10</f>
+              <f>'GPU Rental'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$10</f>
+              <f>'GPU Rental'!$E$2:$E$11</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$10</f>
+              <f>'GPU Rental'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$10</f>
+              <f>'GPU Rental'!$F$2:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$10</f>
+              <f>'GPU Rental'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$10</f>
+              <f>'GPU Rental'!$G$2:$G$11</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$10</f>
+              <f>'GPU Rental'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$10</f>
+              <f>'GPU Rental'!$H$2:$H$11</f>
             </numRef>
           </val>
         </ser>
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1869,8 +1869,62 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I11" s="4">
+        <f>IF(OR(B11="",B10=""),"",B11/B10-1)</f>
+        <v/>
+      </c>
+      <c r="J11" s="4">
+        <f>IF(OR(C11="",C10=""),"",C11/C10-1)</f>
+        <v/>
+      </c>
+      <c r="K11" s="4">
+        <f>IF(OR(D11="",D10=""),"",D11/D10-1)</f>
+        <v/>
+      </c>
+      <c r="L11" s="4">
+        <f>IF(OR(E11="",E10=""),"",E11/E10-1)</f>
+        <v/>
+      </c>
+      <c r="M11" s="4">
+        <f>IF(OR(F11="",F10=""),"",F11/F10-1)</f>
+        <v/>
+      </c>
+      <c r="N11" s="4">
+        <f>IF(OR(G11="",G10=""),"",G11/G10-1)</f>
+        <v/>
+      </c>
+      <c r="O11" s="4">
+        <f>IF(OR(H11="",H10=""),"",H11/H10-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:O11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1881,7 +1935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN25"/>
+  <dimension ref="A1:AN31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5152,8 +5206,764 @@
         <v>2.2994</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>1.6034</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>1.5863</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>1.7205</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>1.6405</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>1.5962</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>1.5519</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>1.5076</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>1.4291</v>
+      </c>
+      <c r="L26" s="11" t="n">
+        <v>1.3734</v>
+      </c>
+      <c r="M26" s="11" t="n">
+        <v>1.3405</v>
+      </c>
+      <c r="N26" s="11" t="n">
+        <v>1.3306</v>
+      </c>
+      <c r="O26" s="11" t="n">
+        <v>1.3436</v>
+      </c>
+      <c r="P26" s="11" t="n">
+        <v>1.3795</v>
+      </c>
+      <c r="Q26" s="11" t="n">
+        <v>1.3948</v>
+      </c>
+      <c r="R26" s="11" t="n">
+        <v>1.4061</v>
+      </c>
+      <c r="S26" s="11" t="n">
+        <v>1.4136</v>
+      </c>
+      <c r="T26" s="11" t="n">
+        <v>1.4171</v>
+      </c>
+      <c r="U26" s="11" t="n">
+        <v>1.4166</v>
+      </c>
+      <c r="V26" s="11" t="n">
+        <v>1.4122</v>
+      </c>
+      <c r="W26" s="11" t="n">
+        <v>1.4039</v>
+      </c>
+      <c r="X26" s="11" t="n">
+        <v>1.3917</v>
+      </c>
+      <c r="Y26" s="11" t="n">
+        <v>1.3754</v>
+      </c>
+      <c r="Z26" s="11" t="n">
+        <v>1.3553</v>
+      </c>
+      <c r="AA26" s="11" t="n">
+        <v>1.3312</v>
+      </c>
+      <c r="AB26" s="11" t="n">
+        <v>1.3032</v>
+      </c>
+      <c r="AC26" s="11" t="n">
+        <v>1.2765</v>
+      </c>
+      <c r="AD26" s="11" t="n">
+        <v>1.2534</v>
+      </c>
+      <c r="AE26" s="11" t="n">
+        <v>1.2338</v>
+      </c>
+      <c r="AF26" s="11" t="n">
+        <v>1.2178</v>
+      </c>
+      <c r="AG26" s="11" t="n">
+        <v>1.2053</v>
+      </c>
+      <c r="AH26" s="11" t="n">
+        <v>1.1964</v>
+      </c>
+      <c r="AI26" s="11" t="n">
+        <v>1.1911</v>
+      </c>
+      <c r="AJ26" s="11" t="n">
+        <v>1.1893</v>
+      </c>
+      <c r="AK26" s="11" t="n">
+        <v>1.1911</v>
+      </c>
+      <c r="AL26" s="11" t="n">
+        <v>1.1964</v>
+      </c>
+      <c r="AM26" s="11" t="n">
+        <v>1.2053</v>
+      </c>
+      <c r="AN26" s="11" t="n">
+        <v>1.2178</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>1.6034</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>1.537</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>1.6042</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>1.6356</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>1.6312</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>1.6198</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>1.6048</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>1.585</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>1.5618</v>
+      </c>
+      <c r="M27" s="11" t="n">
+        <v>1.5388</v>
+      </c>
+      <c r="N27" s="11" t="n">
+        <v>1.5183</v>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>1.5017</v>
+      </c>
+      <c r="P27" s="11" t="n">
+        <v>1.4898</v>
+      </c>
+      <c r="Q27" s="11" t="n">
+        <v>1.482</v>
+      </c>
+      <c r="R27" s="11" t="n">
+        <v>1.4762</v>
+      </c>
+      <c r="S27" s="11" t="n">
+        <v>1.4718</v>
+      </c>
+      <c r="T27" s="11" t="n">
+        <v>1.4683</v>
+      </c>
+      <c r="U27" s="11" t="n">
+        <v>1.4653</v>
+      </c>
+      <c r="V27" s="11" t="n">
+        <v>1.4624</v>
+      </c>
+      <c r="W27" s="11" t="n">
+        <v>1.4596</v>
+      </c>
+      <c r="X27" s="11" t="n">
+        <v>1.4565</v>
+      </c>
+      <c r="Y27" s="11" t="n">
+        <v>1.4531</v>
+      </c>
+      <c r="Z27" s="11" t="n">
+        <v>1.4491</v>
+      </c>
+      <c r="AA27" s="11" t="n">
+        <v>1.4445</v>
+      </c>
+      <c r="AB27" s="11" t="n">
+        <v>1.4392</v>
+      </c>
+      <c r="AC27" s="11" t="n">
+        <v>1.4332</v>
+      </c>
+      <c r="AD27" s="11" t="n">
+        <v>1.4267</v>
+      </c>
+      <c r="AE27" s="11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF27" s="11" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="AG27" s="11" t="n">
+        <v>1.4061</v>
+      </c>
+      <c r="AH27" s="11" t="n">
+        <v>1.3992</v>
+      </c>
+      <c r="AI27" s="11" t="n">
+        <v>1.3926</v>
+      </c>
+      <c r="AJ27" s="11" t="n">
+        <v>1.3862</v>
+      </c>
+      <c r="AK27" s="11" t="n">
+        <v>1.3803</v>
+      </c>
+      <c r="AL27" s="11" t="n">
+        <v>1.3748</v>
+      </c>
+      <c r="AM27" s="11" t="n">
+        <v>1.3698</v>
+      </c>
+      <c r="AN27" s="11" t="n">
+        <v>1.3654</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>5.6184</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>5.6089</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>5.7136</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>5.5578</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>5.4249</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>5.2823</v>
+      </c>
+      <c r="K28" s="11" t="n">
+        <v>5.1928</v>
+      </c>
+      <c r="L28" s="11" t="n">
+        <v>5.1155</v>
+      </c>
+      <c r="M28" s="11" t="n">
+        <v>5.0502</v>
+      </c>
+      <c r="N28" s="11" t="n">
+        <v>4.997</v>
+      </c>
+      <c r="O28" s="11" t="n">
+        <v>4.9559</v>
+      </c>
+      <c r="P28" s="11" t="n">
+        <v>4.9269</v>
+      </c>
+      <c r="Q28" s="11" t="n">
+        <v>4.7771</v>
+      </c>
+      <c r="R28" s="11" t="n">
+        <v>4.6567</v>
+      </c>
+      <c r="S28" s="11" t="n">
+        <v>4.5656</v>
+      </c>
+      <c r="T28" s="11" t="n">
+        <v>4.5038</v>
+      </c>
+      <c r="U28" s="11" t="n">
+        <v>4.4713</v>
+      </c>
+      <c r="V28" s="11" t="n">
+        <v>4.4681</v>
+      </c>
+      <c r="W28" s="11" t="n">
+        <v>4.4942</v>
+      </c>
+      <c r="X28" s="11" t="n">
+        <v>4.5497</v>
+      </c>
+      <c r="Y28" s="11" t="n">
+        <v>4.6345</v>
+      </c>
+      <c r="Z28" s="11" t="n">
+        <v>4.7486</v>
+      </c>
+      <c r="AA28" s="11" t="n">
+        <v>4.892</v>
+      </c>
+      <c r="AB28" s="11" t="n">
+        <v>5.0647</v>
+      </c>
+      <c r="AC28" s="11" t="n">
+        <v>5.1962</v>
+      </c>
+      <c r="AD28" s="11" t="n">
+        <v>5.3101</v>
+      </c>
+      <c r="AE28" s="11" t="n">
+        <v>5.4065</v>
+      </c>
+      <c r="AF28" s="11" t="n">
+        <v>5.4854</v>
+      </c>
+      <c r="AG28" s="11" t="n">
+        <v>5.5467</v>
+      </c>
+      <c r="AH28" s="11" t="n">
+        <v>5.5906</v>
+      </c>
+      <c r="AI28" s="11" t="n">
+        <v>5.6169</v>
+      </c>
+      <c r="AJ28" s="11" t="n">
+        <v>5.6256</v>
+      </c>
+      <c r="AK28" s="11" t="n">
+        <v>5.6169</v>
+      </c>
+      <c r="AL28" s="11" t="n">
+        <v>5.5906</v>
+      </c>
+      <c r="AM28" s="11" t="n">
+        <v>5.5467</v>
+      </c>
+      <c r="AN28" s="11" t="n">
+        <v>5.4854</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>5.6184</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>5.5783</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>5.6306</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>5.6395</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>5.6016</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>5.5564</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>5.5144</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>5.4747</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>5.4345</v>
+      </c>
+      <c r="M29" s="11" t="n">
+        <v>5.3953</v>
+      </c>
+      <c r="N29" s="11" t="n">
+        <v>5.358</v>
+      </c>
+      <c r="O29" s="11" t="n">
+        <v>5.3233</v>
+      </c>
+      <c r="P29" s="11" t="n">
+        <v>5.2914</v>
+      </c>
+      <c r="Q29" s="11" t="n">
+        <v>5.2574</v>
+      </c>
+      <c r="R29" s="11" t="n">
+        <v>5.2186</v>
+      </c>
+      <c r="S29" s="11" t="n">
+        <v>5.1779</v>
+      </c>
+      <c r="T29" s="11" t="n">
+        <v>5.1376</v>
+      </c>
+      <c r="U29" s="11" t="n">
+        <v>5.0992</v>
+      </c>
+      <c r="V29" s="11" t="n">
+        <v>5.0641</v>
+      </c>
+      <c r="W29" s="11" t="n">
+        <v>5.0333</v>
+      </c>
+      <c r="X29" s="11" t="n">
+        <v>5.0076</v>
+      </c>
+      <c r="Y29" s="11" t="n">
+        <v>4.9877</v>
+      </c>
+      <c r="Z29" s="11" t="n">
+        <v>4.9741</v>
+      </c>
+      <c r="AA29" s="11" t="n">
+        <v>4.9673</v>
+      </c>
+      <c r="AB29" s="11" t="n">
+        <v>4.9677</v>
+      </c>
+      <c r="AC29" s="11" t="n">
+        <v>4.9742</v>
+      </c>
+      <c r="AD29" s="11" t="n">
+        <v>4.985</v>
+      </c>
+      <c r="AE29" s="11" t="n">
+        <v>4.9989</v>
+      </c>
+      <c r="AF29" s="11" t="n">
+        <v>5.0149</v>
+      </c>
+      <c r="AG29" s="11" t="n">
+        <v>5.0323</v>
+      </c>
+      <c r="AH29" s="11" t="n">
+        <v>5.0502</v>
+      </c>
+      <c r="AI29" s="11" t="n">
+        <v>5.0681</v>
+      </c>
+      <c r="AJ29" s="11" t="n">
+        <v>5.0854</v>
+      </c>
+      <c r="AK29" s="11" t="n">
+        <v>5.1017</v>
+      </c>
+      <c r="AL29" s="11" t="n">
+        <v>5.1165</v>
+      </c>
+      <c r="AM29" s="11" t="n">
+        <v>5.1295</v>
+      </c>
+      <c r="AN29" s="11" t="n">
+        <v>5.1403</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>2.6254</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>2.5392</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>2.4921</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>2.5142</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>2.5758</v>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>2.5353</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>2.3926</v>
+      </c>
+      <c r="K30" s="11" t="n">
+        <v>2.2222</v>
+      </c>
+      <c r="L30" s="11" t="n">
+        <v>2.1043</v>
+      </c>
+      <c r="M30" s="11" t="n">
+        <v>2.039</v>
+      </c>
+      <c r="N30" s="11" t="n">
+        <v>2.0262</v>
+      </c>
+      <c r="O30" s="11" t="n">
+        <v>2.0658</v>
+      </c>
+      <c r="P30" s="11" t="n">
+        <v>2.158</v>
+      </c>
+      <c r="Q30" s="11" t="n">
+        <v>2.1762</v>
+      </c>
+      <c r="R30" s="11" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="S30" s="11" t="n">
+        <v>2.2084</v>
+      </c>
+      <c r="T30" s="11" t="n">
+        <v>2.2225</v>
+      </c>
+      <c r="U30" s="11" t="n">
+        <v>2.2352</v>
+      </c>
+      <c r="V30" s="11" t="n">
+        <v>2.2466</v>
+      </c>
+      <c r="W30" s="11" t="n">
+        <v>2.2567</v>
+      </c>
+      <c r="X30" s="11" t="n">
+        <v>2.2654</v>
+      </c>
+      <c r="Y30" s="11" t="n">
+        <v>2.2728</v>
+      </c>
+      <c r="Z30" s="11" t="n">
+        <v>2.2788</v>
+      </c>
+      <c r="AA30" s="11" t="n">
+        <v>2.2834</v>
+      </c>
+      <c r="AB30" s="11" t="n">
+        <v>2.2867</v>
+      </c>
+      <c r="AC30" s="11" t="n">
+        <v>2.3018</v>
+      </c>
+      <c r="AD30" s="11" t="n">
+        <v>2.3149</v>
+      </c>
+      <c r="AE30" s="11" t="n">
+        <v>2.3259</v>
+      </c>
+      <c r="AF30" s="11" t="n">
+        <v>2.3349</v>
+      </c>
+      <c r="AG30" s="11" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AH30" s="11" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="AI30" s="11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ30" s="11" t="n">
+        <v>2.351</v>
+      </c>
+      <c r="AK30" s="11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AL30" s="11" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="AM30" s="11" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AN30" s="11" t="n">
+        <v>2.3349</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>2.6254</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>2.5569</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>2.5334</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>2.5214</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>2.5294</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>2.5364</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>2.5257</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>2.4939</v>
+      </c>
+      <c r="L31" s="11" t="n">
+        <v>2.452</v>
+      </c>
+      <c r="M31" s="11" t="n">
+        <v>2.4093</v>
+      </c>
+      <c r="N31" s="11" t="n">
+        <v>2.3712</v>
+      </c>
+      <c r="O31" s="11" t="n">
+        <v>2.3412</v>
+      </c>
+      <c r="P31" s="11" t="n">
+        <v>2.3217</v>
+      </c>
+      <c r="Q31" s="11" t="n">
+        <v>2.3098</v>
+      </c>
+      <c r="R31" s="11" t="n">
+        <v>2.3009</v>
+      </c>
+      <c r="S31" s="11" t="n">
+        <v>2.2942</v>
+      </c>
+      <c r="T31" s="11" t="n">
+        <v>2.2893</v>
+      </c>
+      <c r="U31" s="11" t="n">
+        <v>2.2858</v>
+      </c>
+      <c r="V31" s="11" t="n">
+        <v>2.2833</v>
+      </c>
+      <c r="W31" s="11" t="n">
+        <v>2.2816</v>
+      </c>
+      <c r="X31" s="11" t="n">
+        <v>2.2806</v>
+      </c>
+      <c r="Y31" s="11" t="n">
+        <v>2.2801</v>
+      </c>
+      <c r="Z31" s="11" t="n">
+        <v>2.2799</v>
+      </c>
+      <c r="AA31" s="11" t="n">
+        <v>2.2799</v>
+      </c>
+      <c r="AB31" s="11" t="n">
+        <v>2.2801</v>
+      </c>
+      <c r="AC31" s="11" t="n">
+        <v>2.2807</v>
+      </c>
+      <c r="AD31" s="11" t="n">
+        <v>2.2818</v>
+      </c>
+      <c r="AE31" s="11" t="n">
+        <v>2.2832</v>
+      </c>
+      <c r="AF31" s="11" t="n">
+        <v>2.2849</v>
+      </c>
+      <c r="AG31" s="11" t="n">
+        <v>2.2868</v>
+      </c>
+      <c r="AH31" s="11" t="n">
+        <v>2.2887</v>
+      </c>
+      <c r="AI31" s="11" t="n">
+        <v>2.2906</v>
+      </c>
+      <c r="AJ31" s="11" t="n">
+        <v>2.2925</v>
+      </c>
+      <c r="AK31" s="11" t="n">
+        <v>2.2943</v>
+      </c>
+      <c r="AL31" s="11" t="n">
+        <v>2.2959</v>
+      </c>
+      <c r="AM31" s="11" t="n">
+        <v>2.2973</v>
+      </c>
+      <c r="AN31" s="11" t="n">
+        <v>2.2984</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN25"/>
+  <autoFilter ref="A1:AN31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33226,7 +34036,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-08-31  (4 daily snapshots, 24 curve rows)</t>
+          <t>2026-08-28 to 2026-09-01  (5 daily snapshots, 30 curve rows)</t>
         </is>
       </c>
     </row>
@@ -33322,7 +34132,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-08-31  (9 rows)</t>
+          <t>2026-08-23 to 2026-09-01  (10 rows)</t>
         </is>
       </c>
     </row>
@@ -33334,7 +34144,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 14:10 local</t>
+          <t>2026-09-01 19:26 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,9 +16,9 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
   </definedNames>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$11</f>
+              <f>'Daily Index'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$11</f>
+              <f>'Daily Index'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$11</f>
+              <f>'Daily Index'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$11</f>
+              <f>'Daily Index'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$11</f>
+              <f>'Daily Index'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$11</f>
+              <f>'Daily Index'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$11</f>
+              <f>'GPU Rental'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$11</f>
+              <f>'GPU Rental'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$11</f>
+              <f>'GPU Rental'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$11</f>
+              <f>'GPU Rental'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$11</f>
+              <f>'GPU Rental'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$11</f>
+              <f>'GPU Rental'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$11</f>
+              <f>'GPU Rental'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$11</f>
+              <f>'GPU Rental'!$E$2:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$11</f>
+              <f>'GPU Rental'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$11</f>
+              <f>'GPU Rental'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$11</f>
+              <f>'GPU Rental'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$11</f>
+              <f>'GPU Rental'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$11</f>
+              <f>'GPU Rental'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$11</f>
+              <f>'GPU Rental'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1302,8 +1302,34 @@
         <v/>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>0.9673</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>0.5185999999999999</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>2.1526</v>
+      </c>
+      <c r="E12" s="4">
+        <f>IF(OR(B12="",B11=""),"",B12/B11-1)</f>
+        <v/>
+      </c>
+      <c r="F12" s="4">
+        <f>IF(OR(C12="",C11=""),"",C12/C11-1)</f>
+        <v/>
+      </c>
+      <c r="G12" s="4">
+        <f>IF(OR(D12="",D11=""),"",D12/D11-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1314,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1923,8 +1949,62 @@
         <v/>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I12" s="4">
+        <f>IF(OR(B12="",B11=""),"",B12/B11-1)</f>
+        <v/>
+      </c>
+      <c r="J12" s="4">
+        <f>IF(OR(C12="",C11=""),"",C12/C11-1)</f>
+        <v/>
+      </c>
+      <c r="K12" s="4">
+        <f>IF(OR(D12="",D11=""),"",D12/D11-1)</f>
+        <v/>
+      </c>
+      <c r="L12" s="4">
+        <f>IF(OR(E12="",E11=""),"",E12/E11-1)</f>
+        <v/>
+      </c>
+      <c r="M12" s="4">
+        <f>IF(OR(F12="",F11=""),"",F12/F11-1)</f>
+        <v/>
+      </c>
+      <c r="N12" s="4">
+        <f>IF(OR(G12="",G11=""),"",G12/G11-1)</f>
+        <v/>
+      </c>
+      <c r="O12" s="4">
+        <f>IF(OR(H12="",H11=""),"",H12/H11-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1935,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN31"/>
+  <dimension ref="A1:AN37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5962,8 +6042,764 @@
         <v>2.2984</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>1.6107</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>1.6007</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>1.7283</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>1.6486</v>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>1.6027</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>1.5582</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>1.515</v>
+      </c>
+      <c r="K32" s="11" t="n">
+        <v>1.4376</v>
+      </c>
+      <c r="L32" s="11" t="n">
+        <v>1.3825</v>
+      </c>
+      <c r="M32" s="11" t="n">
+        <v>1.3499</v>
+      </c>
+      <c r="N32" s="11" t="n">
+        <v>1.3396</v>
+      </c>
+      <c r="O32" s="11" t="n">
+        <v>1.3517</v>
+      </c>
+      <c r="P32" s="11" t="n">
+        <v>1.3863</v>
+      </c>
+      <c r="Q32" s="11" t="n">
+        <v>1.4002</v>
+      </c>
+      <c r="R32" s="11" t="n">
+        <v>1.4105</v>
+      </c>
+      <c r="S32" s="11" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="T32" s="11" t="n">
+        <v>1.4198</v>
+      </c>
+      <c r="U32" s="11" t="n">
+        <v>1.4189</v>
+      </c>
+      <c r="V32" s="11" t="n">
+        <v>1.4142</v>
+      </c>
+      <c r="W32" s="11" t="n">
+        <v>1.4058</v>
+      </c>
+      <c r="X32" s="11" t="n">
+        <v>1.3937</v>
+      </c>
+      <c r="Y32" s="11" t="n">
+        <v>1.3778</v>
+      </c>
+      <c r="Z32" s="11" t="n">
+        <v>1.3582</v>
+      </c>
+      <c r="AA32" s="11" t="n">
+        <v>1.3349</v>
+      </c>
+      <c r="AB32" s="11" t="n">
+        <v>1.3078</v>
+      </c>
+      <c r="AC32" s="11" t="n">
+        <v>1.2816</v>
+      </c>
+      <c r="AD32" s="11" t="n">
+        <v>1.2588</v>
+      </c>
+      <c r="AE32" s="11" t="n">
+        <v>1.2396</v>
+      </c>
+      <c r="AF32" s="11" t="n">
+        <v>1.2238</v>
+      </c>
+      <c r="AG32" s="11" t="n">
+        <v>1.2116</v>
+      </c>
+      <c r="AH32" s="11" t="n">
+        <v>1.2028</v>
+      </c>
+      <c r="AI32" s="11" t="n">
+        <v>1.1976</v>
+      </c>
+      <c r="AJ32" s="11" t="n">
+        <v>1.1958</v>
+      </c>
+      <c r="AK32" s="11" t="n">
+        <v>1.1976</v>
+      </c>
+      <c r="AL32" s="11" t="n">
+        <v>1.2028</v>
+      </c>
+      <c r="AM32" s="11" t="n">
+        <v>1.2116</v>
+      </c>
+      <c r="AN32" s="11" t="n">
+        <v>1.2238</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>1.6107</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>1.5541</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1.6179</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>1.6472</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>1.6418</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>1.6295</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>1.5941</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <v>1.5708</v>
+      </c>
+      <c r="M33" s="11" t="n">
+        <v>1.5479</v>
+      </c>
+      <c r="N33" s="11" t="n">
+        <v>1.5274</v>
+      </c>
+      <c r="O33" s="11" t="n">
+        <v>1.5107</v>
+      </c>
+      <c r="P33" s="11" t="n">
+        <v>1.4987</v>
+      </c>
+      <c r="Q33" s="11" t="n">
+        <v>1.4906</v>
+      </c>
+      <c r="R33" s="11" t="n">
+        <v>1.4846</v>
+      </c>
+      <c r="S33" s="11" t="n">
+        <v>1.4799</v>
+      </c>
+      <c r="T33" s="11" t="n">
+        <v>1.4761</v>
+      </c>
+      <c r="U33" s="11" t="n">
+        <v>1.4727</v>
+      </c>
+      <c r="V33" s="11" t="n">
+        <v>1.4696</v>
+      </c>
+      <c r="W33" s="11" t="n">
+        <v>1.4665</v>
+      </c>
+      <c r="X33" s="11" t="n">
+        <v>1.4632</v>
+      </c>
+      <c r="Y33" s="11" t="n">
+        <v>1.4595</v>
+      </c>
+      <c r="Z33" s="11" t="n">
+        <v>1.4554</v>
+      </c>
+      <c r="AA33" s="11" t="n">
+        <v>1.4506</v>
+      </c>
+      <c r="AB33" s="11" t="n">
+        <v>1.4453</v>
+      </c>
+      <c r="AC33" s="11" t="n">
+        <v>1.4392</v>
+      </c>
+      <c r="AD33" s="11" t="n">
+        <v>1.4327</v>
+      </c>
+      <c r="AE33" s="11" t="n">
+        <v>1.4259</v>
+      </c>
+      <c r="AF33" s="11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="AG33" s="11" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="AH33" s="11" t="n">
+        <v>1.4052</v>
+      </c>
+      <c r="AI33" s="11" t="n">
+        <v>1.3986</v>
+      </c>
+      <c r="AJ33" s="11" t="n">
+        <v>1.3922</v>
+      </c>
+      <c r="AK33" s="11" t="n">
+        <v>1.3863</v>
+      </c>
+      <c r="AL33" s="11" t="n">
+        <v>1.3808</v>
+      </c>
+      <c r="AM33" s="11" t="n">
+        <v>1.3759</v>
+      </c>
+      <c r="AN33" s="11" t="n">
+        <v>1.3715</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>5.6412</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>5.5723</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>5.8513</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>5.5858</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>5.3481</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>5.2363</v>
+      </c>
+      <c r="J34" s="11" t="n">
+        <v>5.2506</v>
+      </c>
+      <c r="K34" s="11" t="n">
+        <v>5.2076</v>
+      </c>
+      <c r="L34" s="11" t="n">
+        <v>5.1608</v>
+      </c>
+      <c r="M34" s="11" t="n">
+        <v>5.1101</v>
+      </c>
+      <c r="N34" s="11" t="n">
+        <v>5.0556</v>
+      </c>
+      <c r="O34" s="11" t="n">
+        <v>4.9973</v>
+      </c>
+      <c r="P34" s="11" t="n">
+        <v>4.9352</v>
+      </c>
+      <c r="Q34" s="11" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="R34" s="11" t="n">
+        <v>4.6119</v>
+      </c>
+      <c r="S34" s="11" t="n">
+        <v>4.5029</v>
+      </c>
+      <c r="T34" s="11" t="n">
+        <v>4.4289</v>
+      </c>
+      <c r="U34" s="11" t="n">
+        <v>4.3901</v>
+      </c>
+      <c r="V34" s="11" t="n">
+        <v>4.3863</v>
+      </c>
+      <c r="W34" s="11" t="n">
+        <v>4.4177</v>
+      </c>
+      <c r="X34" s="11" t="n">
+        <v>4.4841</v>
+      </c>
+      <c r="Y34" s="11" t="n">
+        <v>4.5856</v>
+      </c>
+      <c r="Z34" s="11" t="n">
+        <v>4.7223</v>
+      </c>
+      <c r="AA34" s="11" t="n">
+        <v>4.894</v>
+      </c>
+      <c r="AB34" s="11" t="n">
+        <v>5.1008</v>
+      </c>
+      <c r="AC34" s="11" t="n">
+        <v>5.2582</v>
+      </c>
+      <c r="AD34" s="11" t="n">
+        <v>5.3947</v>
+      </c>
+      <c r="AE34" s="11" t="n">
+        <v>5.5102</v>
+      </c>
+      <c r="AF34" s="11" t="n">
+        <v>5.6046</v>
+      </c>
+      <c r="AG34" s="11" t="n">
+        <v>5.6781</v>
+      </c>
+      <c r="AH34" s="11" t="n">
+        <v>5.7306</v>
+      </c>
+      <c r="AI34" s="11" t="n">
+        <v>5.7621</v>
+      </c>
+      <c r="AJ34" s="11" t="n">
+        <v>5.7726</v>
+      </c>
+      <c r="AK34" s="11" t="n">
+        <v>5.7621</v>
+      </c>
+      <c r="AL34" s="11" t="n">
+        <v>5.7306</v>
+      </c>
+      <c r="AM34" s="11" t="n">
+        <v>5.6781</v>
+      </c>
+      <c r="AN34" s="11" t="n">
+        <v>5.6046</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>5.6412</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>5.4782</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>5.6177</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>5.6664</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>5.6139</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>5.5475</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <v>5.4951</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>5.4571</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <v>5.423</v>
+      </c>
+      <c r="M35" s="11" t="n">
+        <v>5.3911</v>
+      </c>
+      <c r="N35" s="11" t="n">
+        <v>5.3603</v>
+      </c>
+      <c r="O35" s="11" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="P35" s="11" t="n">
+        <v>5.2997</v>
+      </c>
+      <c r="Q35" s="11" t="n">
+        <v>5.2646</v>
+      </c>
+      <c r="R35" s="11" t="n">
+        <v>5.2229</v>
+      </c>
+      <c r="S35" s="11" t="n">
+        <v>5.1783</v>
+      </c>
+      <c r="T35" s="11" t="n">
+        <v>5.1336</v>
+      </c>
+      <c r="U35" s="11" t="n">
+        <v>5.0908</v>
+      </c>
+      <c r="V35" s="11" t="n">
+        <v>5.0516</v>
+      </c>
+      <c r="W35" s="11" t="n">
+        <v>5.0173</v>
+      </c>
+      <c r="X35" s="11" t="n">
+        <v>4.9888</v>
+      </c>
+      <c r="Y35" s="11" t="n">
+        <v>4.9671</v>
+      </c>
+      <c r="Z35" s="11" t="n">
+        <v>4.9527</v>
+      </c>
+      <c r="AA35" s="11" t="n">
+        <v>4.9463</v>
+      </c>
+      <c r="AB35" s="11" t="n">
+        <v>4.9483</v>
+      </c>
+      <c r="AC35" s="11" t="n">
+        <v>4.9576</v>
+      </c>
+      <c r="AD35" s="11" t="n">
+        <v>4.9719</v>
+      </c>
+      <c r="AE35" s="11" t="n">
+        <v>4.9897</v>
+      </c>
+      <c r="AF35" s="11" t="n">
+        <v>5.0101</v>
+      </c>
+      <c r="AG35" s="11" t="n">
+        <v>5.0319</v>
+      </c>
+      <c r="AH35" s="11" t="n">
+        <v>5.0544</v>
+      </c>
+      <c r="AI35" s="11" t="n">
+        <v>5.0768</v>
+      </c>
+      <c r="AJ35" s="11" t="n">
+        <v>5.0984</v>
+      </c>
+      <c r="AK35" s="11" t="n">
+        <v>5.1187</v>
+      </c>
+      <c r="AL35" s="11" t="n">
+        <v>5.1372</v>
+      </c>
+      <c r="AM35" s="11" t="n">
+        <v>5.1535</v>
+      </c>
+      <c r="AN35" s="11" t="n">
+        <v>5.1671</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>2.6368</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>2.5492</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>2.4928</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>2.5188</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>2.5854</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>2.5434</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>2.393</v>
+      </c>
+      <c r="K36" s="11" t="n">
+        <v>2.2125</v>
+      </c>
+      <c r="L36" s="11" t="n">
+        <v>2.0883</v>
+      </c>
+      <c r="M36" s="11" t="n">
+        <v>2.0202</v>
+      </c>
+      <c r="N36" s="11" t="n">
+        <v>2.0082</v>
+      </c>
+      <c r="O36" s="11" t="n">
+        <v>2.0525</v>
+      </c>
+      <c r="P36" s="11" t="n">
+        <v>2.1529</v>
+      </c>
+      <c r="Q36" s="11" t="n">
+        <v>2.177</v>
+      </c>
+      <c r="R36" s="11" t="n">
+        <v>2.1988</v>
+      </c>
+      <c r="S36" s="11" t="n">
+        <v>2.2184</v>
+      </c>
+      <c r="T36" s="11" t="n">
+        <v>2.2357</v>
+      </c>
+      <c r="U36" s="11" t="n">
+        <v>2.2507</v>
+      </c>
+      <c r="V36" s="11" t="n">
+        <v>2.2635</v>
+      </c>
+      <c r="W36" s="11" t="n">
+        <v>2.274</v>
+      </c>
+      <c r="X36" s="11" t="n">
+        <v>2.2822</v>
+      </c>
+      <c r="Y36" s="11" t="n">
+        <v>2.2882</v>
+      </c>
+      <c r="Z36" s="11" t="n">
+        <v>2.2919</v>
+      </c>
+      <c r="AA36" s="11" t="n">
+        <v>2.2934</v>
+      </c>
+      <c r="AB36" s="11" t="n">
+        <v>2.2925</v>
+      </c>
+      <c r="AC36" s="11" t="n">
+        <v>2.3059</v>
+      </c>
+      <c r="AD36" s="11" t="n">
+        <v>2.3174</v>
+      </c>
+      <c r="AE36" s="11" t="n">
+        <v>2.3272</v>
+      </c>
+      <c r="AF36" s="11" t="n">
+        <v>2.3352</v>
+      </c>
+      <c r="AG36" s="11" t="n">
+        <v>2.3414</v>
+      </c>
+      <c r="AH36" s="11" t="n">
+        <v>2.3459</v>
+      </c>
+      <c r="AI36" s="11" t="n">
+        <v>2.3485</v>
+      </c>
+      <c r="AJ36" s="11" t="n">
+        <v>2.3494</v>
+      </c>
+      <c r="AK36" s="11" t="n">
+        <v>2.3485</v>
+      </c>
+      <c r="AL36" s="11" t="n">
+        <v>2.3459</v>
+      </c>
+      <c r="AM36" s="11" t="n">
+        <v>2.3414</v>
+      </c>
+      <c r="AN36" s="11" t="n">
+        <v>2.3352</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>2.6368</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>2.5705</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>2.5423</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>2.5278</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>2.5362</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>2.5436</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>2.5326</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>2.4991</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>2.4549</v>
+      </c>
+      <c r="M37" s="11" t="n">
+        <v>2.4099</v>
+      </c>
+      <c r="N37" s="11" t="n">
+        <v>2.3698</v>
+      </c>
+      <c r="O37" s="11" t="n">
+        <v>2.3385</v>
+      </c>
+      <c r="P37" s="11" t="n">
+        <v>2.3185</v>
+      </c>
+      <c r="Q37" s="11" t="n">
+        <v>2.3067</v>
+      </c>
+      <c r="R37" s="11" t="n">
+        <v>2.2982</v>
+      </c>
+      <c r="S37" s="11" t="n">
+        <v>2.2923</v>
+      </c>
+      <c r="T37" s="11" t="n">
+        <v>2.2882</v>
+      </c>
+      <c r="U37" s="11" t="n">
+        <v>2.2856</v>
+      </c>
+      <c r="V37" s="11" t="n">
+        <v>2.284</v>
+      </c>
+      <c r="W37" s="11" t="n">
+        <v>2.2832</v>
+      </c>
+      <c r="X37" s="11" t="n">
+        <v>2.283</v>
+      </c>
+      <c r="Y37" s="11" t="n">
+        <v>2.2831</v>
+      </c>
+      <c r="Z37" s="11" t="n">
+        <v>2.2834</v>
+      </c>
+      <c r="AA37" s="11" t="n">
+        <v>2.2838</v>
+      </c>
+      <c r="AB37" s="11" t="n">
+        <v>2.2842</v>
+      </c>
+      <c r="AC37" s="11" t="n">
+        <v>2.2848</v>
+      </c>
+      <c r="AD37" s="11" t="n">
+        <v>2.2858</v>
+      </c>
+      <c r="AE37" s="11" t="n">
+        <v>2.2872</v>
+      </c>
+      <c r="AF37" s="11" t="n">
+        <v>2.2888</v>
+      </c>
+      <c r="AG37" s="11" t="n">
+        <v>2.2905</v>
+      </c>
+      <c r="AH37" s="11" t="n">
+        <v>2.2923</v>
+      </c>
+      <c r="AI37" s="11" t="n">
+        <v>2.294</v>
+      </c>
+      <c r="AJ37" s="11" t="n">
+        <v>2.2958</v>
+      </c>
+      <c r="AK37" s="11" t="n">
+        <v>2.2974</v>
+      </c>
+      <c r="AL37" s="11" t="n">
+        <v>2.2988</v>
+      </c>
+      <c r="AM37" s="11" t="n">
+        <v>2.3001</v>
+      </c>
+      <c r="AN37" s="11" t="n">
+        <v>2.3012</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN31"/>
+  <autoFilter ref="A1:AN37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34036,7 +34872,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-01  (5 daily snapshots, 30 curve rows)</t>
+          <t>2026-08-28 to 2026-09-02  (6 daily snapshots, 36 curve rows)</t>
         </is>
       </c>
     </row>
@@ -34108,7 +34944,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-08-31  (10 rows)</t>
+          <t>2026-08-22 to 2026-09-01  (11 rows)</t>
         </is>
       </c>
     </row>
@@ -34132,7 +34968,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-01  (10 rows)</t>
+          <t>2026-08-23 to 2026-09-02  (11 rows)</t>
         </is>
       </c>
     </row>
@@ -34144,7 +34980,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 19:26 local</t>
+          <t>2026-09-02 19:25 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$12</f>
+              <f>'Daily Index'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$12</f>
+              <f>'Daily Index'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$12</f>
+              <f>'Daily Index'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$12</f>
+              <f>'Daily Index'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$12</f>
+              <f>'Daily Index'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$12</f>
+              <f>'Daily Index'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1328,8 +1328,30 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="4">
+        <f>IF(OR(B13="",B12=""),"",B13/B12-1)</f>
+        <v/>
+      </c>
+      <c r="F13" s="4">
+        <f>IF(OR(C13="",C12=""),"",C13/C12-1)</f>
+        <v/>
+      </c>
+      <c r="G13" s="4">
+        <f>IF(OR(D13="",D12=""),"",D13/D12-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34944,7 +34966,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-01  (11 rows)</t>
+          <t>2026-08-22 to 2026-09-02  (12 rows)</t>
         </is>
       </c>
     </row>
@@ -34980,7 +35002,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 19:25 local</t>
+          <t>2026-09-03 13:37 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
   </definedNames>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$12</f>
+              <f>'GPU Rental'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$12</f>
+              <f>'GPU Rental'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$12</f>
+              <f>'GPU Rental'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$12</f>
+              <f>'GPU Rental'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$12</f>
+              <f>'GPU Rental'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$12</f>
+              <f>'GPU Rental'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$12</f>
+              <f>'GPU Rental'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$12</f>
+              <f>'GPU Rental'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$12</f>
+              <f>'GPU Rental'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$12</f>
+              <f>'GPU Rental'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$12</f>
+              <f>'GPU Rental'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$12</f>
+              <f>'GPU Rental'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$12</f>
+              <f>'GPU Rental'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$12</f>
+              <f>'GPU Rental'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -1362,7 +1362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2025,8 +2025,62 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I13" s="4">
+        <f>IF(OR(B13="",B12=""),"",B13/B12-1)</f>
+        <v/>
+      </c>
+      <c r="J13" s="4">
+        <f>IF(OR(C13="",C12=""),"",C13/C12-1)</f>
+        <v/>
+      </c>
+      <c r="K13" s="4">
+        <f>IF(OR(D13="",D12=""),"",D13/D12-1)</f>
+        <v/>
+      </c>
+      <c r="L13" s="4">
+        <f>IF(OR(E13="",E12=""),"",E13/E12-1)</f>
+        <v/>
+      </c>
+      <c r="M13" s="4">
+        <f>IF(OR(F13="",F12=""),"",F13/F12-1)</f>
+        <v/>
+      </c>
+      <c r="N13" s="4">
+        <f>IF(OR(G13="",G12=""),"",G13/G12-1)</f>
+        <v/>
+      </c>
+      <c r="O13" s="4">
+        <f>IF(OR(H13="",H12=""),"",H13/H12-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O12"/>
+  <autoFilter ref="A1:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2037,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AN43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6820,8 +6874,764 @@
         <v>2.3012</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>1.6089</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>1.5914</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>1.7148</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>1.6349</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>1.5877</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>1.5428</v>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>1.5001</v>
+      </c>
+      <c r="K38" s="11" t="n">
+        <v>1.4229</v>
+      </c>
+      <c r="L38" s="11" t="n">
+        <v>1.3679</v>
+      </c>
+      <c r="M38" s="11" t="n">
+        <v>1.3352</v>
+      </c>
+      <c r="N38" s="11" t="n">
+        <v>1.3248</v>
+      </c>
+      <c r="O38" s="11" t="n">
+        <v>1.3366</v>
+      </c>
+      <c r="P38" s="11" t="n">
+        <v>1.3706</v>
+      </c>
+      <c r="Q38" s="11" t="n">
+        <v>1.384</v>
+      </c>
+      <c r="R38" s="11" t="n">
+        <v>1.3937</v>
+      </c>
+      <c r="S38" s="11" t="n">
+        <v>1.3998</v>
+      </c>
+      <c r="T38" s="11" t="n">
+        <v>1.4023</v>
+      </c>
+      <c r="U38" s="11" t="n">
+        <v>1.4012</v>
+      </c>
+      <c r="V38" s="11" t="n">
+        <v>1.3964</v>
+      </c>
+      <c r="W38" s="11" t="n">
+        <v>1.388</v>
+      </c>
+      <c r="X38" s="11" t="n">
+        <v>1.3759</v>
+      </c>
+      <c r="Y38" s="11" t="n">
+        <v>1.3603</v>
+      </c>
+      <c r="Z38" s="11" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="AA38" s="11" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="AB38" s="11" t="n">
+        <v>1.2914</v>
+      </c>
+      <c r="AC38" s="11" t="n">
+        <v>1.2655</v>
+      </c>
+      <c r="AD38" s="11" t="n">
+        <v>1.2429</v>
+      </c>
+      <c r="AE38" s="11" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="AF38" s="11" t="n">
+        <v>1.2083</v>
+      </c>
+      <c r="AG38" s="11" t="n">
+        <v>1.1961</v>
+      </c>
+      <c r="AH38" s="11" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AI38" s="11" t="n">
+        <v>1.1823</v>
+      </c>
+      <c r="AJ38" s="11" t="n">
+        <v>1.1806</v>
+      </c>
+      <c r="AK38" s="11" t="n">
+        <v>1.1823</v>
+      </c>
+      <c r="AL38" s="11" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AM38" s="11" t="n">
+        <v>1.1961</v>
+      </c>
+      <c r="AN38" s="11" t="n">
+        <v>1.2083</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>1.6089</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>1.5467</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>1.6084</v>
+      </c>
+      <c r="G39" s="11" t="n">
+        <v>1.6362</v>
+      </c>
+      <c r="H39" s="11" t="n">
+        <v>1.6299</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>1.6169</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <v>1.5808</v>
+      </c>
+      <c r="L39" s="11" t="n">
+        <v>1.5574</v>
+      </c>
+      <c r="M39" s="11" t="n">
+        <v>1.5343</v>
+      </c>
+      <c r="N39" s="11" t="n">
+        <v>1.5137</v>
+      </c>
+      <c r="O39" s="11" t="n">
+        <v>1.4969</v>
+      </c>
+      <c r="P39" s="11" t="n">
+        <v>1.4848</v>
+      </c>
+      <c r="Q39" s="11" t="n">
+        <v>1.4766</v>
+      </c>
+      <c r="R39" s="11" t="n">
+        <v>1.4703</v>
+      </c>
+      <c r="S39" s="11" t="n">
+        <v>1.4654</v>
+      </c>
+      <c r="T39" s="11" t="n">
+        <v>1.4614</v>
+      </c>
+      <c r="U39" s="11" t="n">
+        <v>1.4579</v>
+      </c>
+      <c r="V39" s="11" t="n">
+        <v>1.4547</v>
+      </c>
+      <c r="W39" s="11" t="n">
+        <v>1.4514</v>
+      </c>
+      <c r="X39" s="11" t="n">
+        <v>1.4479</v>
+      </c>
+      <c r="Y39" s="11" t="n">
+        <v>1.4442</v>
+      </c>
+      <c r="Z39" s="11" t="n">
+        <v>1.4399</v>
+      </c>
+      <c r="AA39" s="11" t="n">
+        <v>1.4351</v>
+      </c>
+      <c r="AB39" s="11" t="n">
+        <v>1.4297</v>
+      </c>
+      <c r="AC39" s="11" t="n">
+        <v>1.4236</v>
+      </c>
+      <c r="AD39" s="11" t="n">
+        <v>1.4171</v>
+      </c>
+      <c r="AE39" s="11" t="n">
+        <v>1.4103</v>
+      </c>
+      <c r="AF39" s="11" t="n">
+        <v>1.4034</v>
+      </c>
+      <c r="AG39" s="11" t="n">
+        <v>1.3964</v>
+      </c>
+      <c r="AH39" s="11" t="n">
+        <v>1.3896</v>
+      </c>
+      <c r="AI39" s="11" t="n">
+        <v>1.383</v>
+      </c>
+      <c r="AJ39" s="11" t="n">
+        <v>1.3767</v>
+      </c>
+      <c r="AK39" s="11" t="n">
+        <v>1.3707</v>
+      </c>
+      <c r="AL39" s="11" t="n">
+        <v>1.3653</v>
+      </c>
+      <c r="AM39" s="11" t="n">
+        <v>1.3603</v>
+      </c>
+      <c r="AN39" s="11" t="n">
+        <v>1.3559</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>5.6442</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>5.6708</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>5.7627</v>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>5.5753</v>
+      </c>
+      <c r="H40" s="11" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>5.2935</v>
+      </c>
+      <c r="J40" s="11" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="K40" s="11" t="n">
+        <v>5.2364</v>
+      </c>
+      <c r="L40" s="11" t="n">
+        <v>5.1852</v>
+      </c>
+      <c r="M40" s="11" t="n">
+        <v>5.1325</v>
+      </c>
+      <c r="N40" s="11" t="n">
+        <v>5.0782</v>
+      </c>
+      <c r="O40" s="11" t="n">
+        <v>5.0224</v>
+      </c>
+      <c r="P40" s="11" t="n">
+        <v>4.965</v>
+      </c>
+      <c r="Q40" s="11" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="R40" s="11" t="n">
+        <v>4.6493</v>
+      </c>
+      <c r="S40" s="11" t="n">
+        <v>4.5428</v>
+      </c>
+      <c r="T40" s="11" t="n">
+        <v>4.4706</v>
+      </c>
+      <c r="U40" s="11" t="n">
+        <v>4.4327</v>
+      </c>
+      <c r="V40" s="11" t="n">
+        <v>4.429</v>
+      </c>
+      <c r="W40" s="11" t="n">
+        <v>4.4596</v>
+      </c>
+      <c r="X40" s="11" t="n">
+        <v>4.5245</v>
+      </c>
+      <c r="Y40" s="11" t="n">
+        <v>4.6236</v>
+      </c>
+      <c r="Z40" s="11" t="n">
+        <v>4.757</v>
+      </c>
+      <c r="AA40" s="11" t="n">
+        <v>4.9246</v>
+      </c>
+      <c r="AB40" s="11" t="n">
+        <v>5.1266</v>
+      </c>
+      <c r="AC40" s="11" t="n">
+        <v>5.2803</v>
+      </c>
+      <c r="AD40" s="11" t="n">
+        <v>5.4135</v>
+      </c>
+      <c r="AE40" s="11" t="n">
+        <v>5.5263</v>
+      </c>
+      <c r="AF40" s="11" t="n">
+        <v>5.6185</v>
+      </c>
+      <c r="AG40" s="11" t="n">
+        <v>5.6902</v>
+      </c>
+      <c r="AH40" s="11" t="n">
+        <v>5.7415</v>
+      </c>
+      <c r="AI40" s="11" t="n">
+        <v>5.7722</v>
+      </c>
+      <c r="AJ40" s="11" t="n">
+        <v>5.7825</v>
+      </c>
+      <c r="AK40" s="11" t="n">
+        <v>5.7722</v>
+      </c>
+      <c r="AL40" s="11" t="n">
+        <v>5.7415</v>
+      </c>
+      <c r="AM40" s="11" t="n">
+        <v>5.6902</v>
+      </c>
+      <c r="AN40" s="11" t="n">
+        <v>5.6185</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>5.6442</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>5.6481</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>5.6941</v>
+      </c>
+      <c r="G41" s="11" t="n">
+        <v>5.6935</v>
+      </c>
+      <c r="H41" s="11" t="n">
+        <v>5.6389</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="J41" s="11" t="n">
+        <v>5.5287</v>
+      </c>
+      <c r="K41" s="11" t="n">
+        <v>5.4905</v>
+      </c>
+      <c r="L41" s="11" t="n">
+        <v>5.4556</v>
+      </c>
+      <c r="M41" s="11" t="n">
+        <v>5.4226</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>5.3909</v>
+      </c>
+      <c r="O41" s="11" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="P41" s="11" t="n">
+        <v>5.3295</v>
+      </c>
+      <c r="Q41" s="11" t="n">
+        <v>5.2945</v>
+      </c>
+      <c r="R41" s="11" t="n">
+        <v>5.2532</v>
+      </c>
+      <c r="S41" s="11" t="n">
+        <v>5.2092</v>
+      </c>
+      <c r="T41" s="11" t="n">
+        <v>5.1651</v>
+      </c>
+      <c r="U41" s="11" t="n">
+        <v>5.123</v>
+      </c>
+      <c r="V41" s="11" t="n">
+        <v>5.0844</v>
+      </c>
+      <c r="W41" s="11" t="n">
+        <v>5.0505</v>
+      </c>
+      <c r="X41" s="11" t="n">
+        <v>5.0225</v>
+      </c>
+      <c r="Y41" s="11" t="n">
+        <v>5.001</v>
+      </c>
+      <c r="Z41" s="11" t="n">
+        <v>4.9867</v>
+      </c>
+      <c r="AA41" s="11" t="n">
+        <v>4.9803</v>
+      </c>
+      <c r="AB41" s="11" t="n">
+        <v>4.982</v>
+      </c>
+      <c r="AC41" s="11" t="n">
+        <v>4.991</v>
+      </c>
+      <c r="AD41" s="11" t="n">
+        <v>5.0047</v>
+      </c>
+      <c r="AE41" s="11" t="n">
+        <v>5.022</v>
+      </c>
+      <c r="AF41" s="11" t="n">
+        <v>5.0417</v>
+      </c>
+      <c r="AG41" s="11" t="n">
+        <v>5.0629</v>
+      </c>
+      <c r="AH41" s="11" t="n">
+        <v>5.0847</v>
+      </c>
+      <c r="AI41" s="11" t="n">
+        <v>5.1065</v>
+      </c>
+      <c r="AJ41" s="11" t="n">
+        <v>5.1275</v>
+      </c>
+      <c r="AK41" s="11" t="n">
+        <v>5.1472</v>
+      </c>
+      <c r="AL41" s="11" t="n">
+        <v>5.1652</v>
+      </c>
+      <c r="AM41" s="11" t="n">
+        <v>5.181</v>
+      </c>
+      <c r="AN41" s="11" t="n">
+        <v>5.1942</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>2.6648</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>2.6004</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>2.486</v>
+      </c>
+      <c r="G42" s="11" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="H42" s="11" t="n">
+        <v>2.6175</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>2.5784</v>
+      </c>
+      <c r="J42" s="11" t="n">
+        <v>2.4179</v>
+      </c>
+      <c r="K42" s="11" t="n">
+        <v>2.2308</v>
+      </c>
+      <c r="L42" s="11" t="n">
+        <v>2.1019</v>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>2.0312</v>
+      </c>
+      <c r="N42" s="11" t="n">
+        <v>2.0187</v>
+      </c>
+      <c r="O42" s="11" t="n">
+        <v>2.0643</v>
+      </c>
+      <c r="P42" s="11" t="n">
+        <v>2.1682</v>
+      </c>
+      <c r="Q42" s="11" t="n">
+        <v>2.1942</v>
+      </c>
+      <c r="R42" s="11" t="n">
+        <v>2.2175</v>
+      </c>
+      <c r="S42" s="11" t="n">
+        <v>2.2382</v>
+      </c>
+      <c r="T42" s="11" t="n">
+        <v>2.2561</v>
+      </c>
+      <c r="U42" s="11" t="n">
+        <v>2.2713</v>
+      </c>
+      <c r="V42" s="11" t="n">
+        <v>2.2839</v>
+      </c>
+      <c r="W42" s="11" t="n">
+        <v>2.2938</v>
+      </c>
+      <c r="X42" s="11" t="n">
+        <v>2.3009</v>
+      </c>
+      <c r="Y42" s="11" t="n">
+        <v>2.3054</v>
+      </c>
+      <c r="Z42" s="11" t="n">
+        <v>2.3072</v>
+      </c>
+      <c r="AA42" s="11" t="n">
+        <v>2.3063</v>
+      </c>
+      <c r="AB42" s="11" t="n">
+        <v>2.3027</v>
+      </c>
+      <c r="AC42" s="11" t="n">
+        <v>2.3137</v>
+      </c>
+      <c r="AD42" s="11" t="n">
+        <v>2.3231</v>
+      </c>
+      <c r="AE42" s="11" t="n">
+        <v>2.3311</v>
+      </c>
+      <c r="AF42" s="11" t="n">
+        <v>2.3377</v>
+      </c>
+      <c r="AG42" s="11" t="n">
+        <v>2.3428</v>
+      </c>
+      <c r="AH42" s="11" t="n">
+        <v>2.3464</v>
+      </c>
+      <c r="AI42" s="11" t="n">
+        <v>2.3486</v>
+      </c>
+      <c r="AJ42" s="11" t="n">
+        <v>2.3493</v>
+      </c>
+      <c r="AK42" s="11" t="n">
+        <v>2.3486</v>
+      </c>
+      <c r="AL42" s="11" t="n">
+        <v>2.3464</v>
+      </c>
+      <c r="AM42" s="11" t="n">
+        <v>2.3428</v>
+      </c>
+      <c r="AN42" s="11" t="n">
+        <v>2.3377</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>2.6648</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>2.644</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>2.5868</v>
+      </c>
+      <c r="G43" s="11" t="n">
+        <v>2.5568</v>
+      </c>
+      <c r="H43" s="11" t="n">
+        <v>2.5642</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>2.573</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>2.5622</v>
+      </c>
+      <c r="K43" s="11" t="n">
+        <v>2.5275</v>
+      </c>
+      <c r="L43" s="11" t="n">
+        <v>2.4818</v>
+      </c>
+      <c r="M43" s="11" t="n">
+        <v>2.4351</v>
+      </c>
+      <c r="N43" s="11" t="n">
+        <v>2.3936</v>
+      </c>
+      <c r="O43" s="11" t="n">
+        <v>2.3611</v>
+      </c>
+      <c r="P43" s="11" t="n">
+        <v>2.3403</v>
+      </c>
+      <c r="Q43" s="11" t="n">
+        <v>2.3281</v>
+      </c>
+      <c r="R43" s="11" t="n">
+        <v>2.3194</v>
+      </c>
+      <c r="S43" s="11" t="n">
+        <v>2.3133</v>
+      </c>
+      <c r="T43" s="11" t="n">
+        <v>2.3092</v>
+      </c>
+      <c r="U43" s="11" t="n">
+        <v>2.3065</v>
+      </c>
+      <c r="V43" s="11" t="n">
+        <v>2.3049</v>
+      </c>
+      <c r="W43" s="11" t="n">
+        <v>2.3041</v>
+      </c>
+      <c r="X43" s="11" t="n">
+        <v>2.3038</v>
+      </c>
+      <c r="Y43" s="11" t="n">
+        <v>2.3038</v>
+      </c>
+      <c r="Z43" s="11" t="n">
+        <v>2.3039</v>
+      </c>
+      <c r="AA43" s="11" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="AB43" s="11" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="AC43" s="11" t="n">
+        <v>2.3042</v>
+      </c>
+      <c r="AD43" s="11" t="n">
+        <v>2.3048</v>
+      </c>
+      <c r="AE43" s="11" t="n">
+        <v>2.3056</v>
+      </c>
+      <c r="AF43" s="11" t="n">
+        <v>2.3066</v>
+      </c>
+      <c r="AG43" s="11" t="n">
+        <v>2.3078</v>
+      </c>
+      <c r="AH43" s="11" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="AI43" s="11" t="n">
+        <v>2.3103</v>
+      </c>
+      <c r="AJ43" s="11" t="n">
+        <v>2.3115</v>
+      </c>
+      <c r="AK43" s="11" t="n">
+        <v>2.3126</v>
+      </c>
+      <c r="AL43" s="11" t="n">
+        <v>2.3137</v>
+      </c>
+      <c r="AM43" s="11" t="n">
+        <v>2.3145</v>
+      </c>
+      <c r="AN43" s="11" t="n">
+        <v>2.3153</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN37"/>
+  <autoFilter ref="A1:AN43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34894,7 +35704,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-02  (6 daily snapshots, 36 curve rows)</t>
+          <t>2026-08-28 to 2026-09-03  (7 daily snapshots, 42 curve rows)</t>
         </is>
       </c>
     </row>
@@ -34990,7 +35800,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-02  (11 rows)</t>
+          <t>2026-08-23 to 2026-09-03  (12 rows)</t>
         </is>
       </c>
     </row>
@@ -35002,7 +35812,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 13:37 local</t>
+          <t>2026-09-03 19:19 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,9 +16,9 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
   </definedNames>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$13</f>
+              <f>'Daily Index'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$13</f>
+              <f>'Daily Index'!$B$2:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$13</f>
+              <f>'Daily Index'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$13</f>
+              <f>'Daily Index'!$C$2:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$13</f>
+              <f>'Daily Index'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$13</f>
+              <f>'Daily Index'!$D$2:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$13</f>
+              <f>'GPU Rental'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$13</f>
+              <f>'GPU Rental'!$B$2:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$13</f>
+              <f>'GPU Rental'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$13</f>
+              <f>'GPU Rental'!$C$2:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$13</f>
+              <f>'GPU Rental'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$13</f>
+              <f>'GPU Rental'!$D$2:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$13</f>
+              <f>'GPU Rental'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$13</f>
+              <f>'GPU Rental'!$E$2:$E$14</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$13</f>
+              <f>'GPU Rental'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$13</f>
+              <f>'GPU Rental'!$F$2:$F$14</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$13</f>
+              <f>'GPU Rental'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$13</f>
+              <f>'GPU Rental'!$G$2:$G$14</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$13</f>
+              <f>'GPU Rental'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$13</f>
+              <f>'GPU Rental'!$H$2:$H$14</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1350,8 +1350,34 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>0.9735</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>0.5281</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>1.9825</v>
+      </c>
+      <c r="E14" s="4">
+        <f>IF(OR(B14="",B13=""),"",B14/B13-1)</f>
+        <v/>
+      </c>
+      <c r="F14" s="4">
+        <f>IF(OR(C14="",C13=""),"",C14/C13-1)</f>
+        <v/>
+      </c>
+      <c r="G14" s="4">
+        <f>IF(OR(D14="",D13=""),"",D14/D13-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1362,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2079,8 +2105,62 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I14" s="4">
+        <f>IF(OR(B14="",B13=""),"",B14/B13-1)</f>
+        <v/>
+      </c>
+      <c r="J14" s="4">
+        <f>IF(OR(C14="",C13=""),"",C14/C13-1)</f>
+        <v/>
+      </c>
+      <c r="K14" s="4">
+        <f>IF(OR(D14="",D13=""),"",D14/D13-1)</f>
+        <v/>
+      </c>
+      <c r="L14" s="4">
+        <f>IF(OR(E14="",E13=""),"",E14/E13-1)</f>
+        <v/>
+      </c>
+      <c r="M14" s="4">
+        <f>IF(OR(F14="",F13=""),"",F14/F13-1)</f>
+        <v/>
+      </c>
+      <c r="N14" s="4">
+        <f>IF(OR(G14="",G13=""),"",G14/G13-1)</f>
+        <v/>
+      </c>
+      <c r="O14" s="4">
+        <f>IF(OR(H14="",H13=""),"",H14/H13-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2091,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN43"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7630,8 +7710,764 @@
         <v>2.3153</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="10" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>1.6119</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>1.5915</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>1.7191</v>
+      </c>
+      <c r="G44" s="11" t="n">
+        <v>1.6378</v>
+      </c>
+      <c r="H44" s="11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>1.5449</v>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>1.5023</v>
+      </c>
+      <c r="K44" s="11" t="n">
+        <v>1.4249</v>
+      </c>
+      <c r="L44" s="11" t="n">
+        <v>1.3699</v>
+      </c>
+      <c r="M44" s="11" t="n">
+        <v>1.3372</v>
+      </c>
+      <c r="N44" s="11" t="n">
+        <v>1.3268</v>
+      </c>
+      <c r="O44" s="11" t="n">
+        <v>1.3386</v>
+      </c>
+      <c r="P44" s="11" t="n">
+        <v>1.3728</v>
+      </c>
+      <c r="Q44" s="11" t="n">
+        <v>1.3863</v>
+      </c>
+      <c r="R44" s="11" t="n">
+        <v>1.3962</v>
+      </c>
+      <c r="S44" s="11" t="n">
+        <v>1.4024</v>
+      </c>
+      <c r="T44" s="11" t="n">
+        <v>1.4049</v>
+      </c>
+      <c r="U44" s="11" t="n">
+        <v>1.4038</v>
+      </c>
+      <c r="V44" s="11" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="W44" s="11" t="n">
+        <v>1.3906</v>
+      </c>
+      <c r="X44" s="11" t="n">
+        <v>1.3786</v>
+      </c>
+      <c r="Y44" s="11" t="n">
+        <v>1.3629</v>
+      </c>
+      <c r="Z44" s="11" t="n">
+        <v>1.3435</v>
+      </c>
+      <c r="AA44" s="11" t="n">
+        <v>1.3205</v>
+      </c>
+      <c r="AB44" s="11" t="n">
+        <v>1.2939</v>
+      </c>
+      <c r="AC44" s="11" t="n">
+        <v>1.2678</v>
+      </c>
+      <c r="AD44" s="11" t="n">
+        <v>1.2453</v>
+      </c>
+      <c r="AE44" s="11" t="n">
+        <v>1.2262</v>
+      </c>
+      <c r="AF44" s="11" t="n">
+        <v>1.2106</v>
+      </c>
+      <c r="AG44" s="11" t="n">
+        <v>1.1984</v>
+      </c>
+      <c r="AH44" s="11" t="n">
+        <v>1.1898</v>
+      </c>
+      <c r="AI44" s="11" t="n">
+        <v>1.1846</v>
+      </c>
+      <c r="AJ44" s="11" t="n">
+        <v>1.1828</v>
+      </c>
+      <c r="AK44" s="11" t="n">
+        <v>1.1846</v>
+      </c>
+      <c r="AL44" s="11" t="n">
+        <v>1.1898</v>
+      </c>
+      <c r="AM44" s="11" t="n">
+        <v>1.1984</v>
+      </c>
+      <c r="AN44" s="11" t="n">
+        <v>1.2106</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>1.6119</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>1.5451</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>1.6089</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>1.6379</v>
+      </c>
+      <c r="H45" s="11" t="n">
+        <v>1.6319</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>1.6189</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>1.603</v>
+      </c>
+      <c r="K45" s="11" t="n">
+        <v>1.5828</v>
+      </c>
+      <c r="L45" s="11" t="n">
+        <v>1.5594</v>
+      </c>
+      <c r="M45" s="11" t="n">
+        <v>1.5363</v>
+      </c>
+      <c r="N45" s="11" t="n">
+        <v>1.5157</v>
+      </c>
+      <c r="O45" s="11" t="n">
+        <v>1.4989</v>
+      </c>
+      <c r="P45" s="11" t="n">
+        <v>1.4868</v>
+      </c>
+      <c r="Q45" s="11" t="n">
+        <v>1.4786</v>
+      </c>
+      <c r="R45" s="11" t="n">
+        <v>1.4724</v>
+      </c>
+      <c r="S45" s="11" t="n">
+        <v>1.4675</v>
+      </c>
+      <c r="T45" s="11" t="n">
+        <v>1.4635</v>
+      </c>
+      <c r="U45" s="11" t="n">
+        <v>1.4601</v>
+      </c>
+      <c r="V45" s="11" t="n">
+        <v>1.4568</v>
+      </c>
+      <c r="W45" s="11" t="n">
+        <v>1.4536</v>
+      </c>
+      <c r="X45" s="11" t="n">
+        <v>1.4502</v>
+      </c>
+      <c r="Y45" s="11" t="n">
+        <v>1.4464</v>
+      </c>
+      <c r="Z45" s="11" t="n">
+        <v>1.4422</v>
+      </c>
+      <c r="AA45" s="11" t="n">
+        <v>1.4374</v>
+      </c>
+      <c r="AB45" s="11" t="n">
+        <v>1.432</v>
+      </c>
+      <c r="AC45" s="11" t="n">
+        <v>1.4259</v>
+      </c>
+      <c r="AD45" s="11" t="n">
+        <v>1.4194</v>
+      </c>
+      <c r="AE45" s="11" t="n">
+        <v>1.4126</v>
+      </c>
+      <c r="AF45" s="11" t="n">
+        <v>1.4056</v>
+      </c>
+      <c r="AG45" s="11" t="n">
+        <v>1.3987</v>
+      </c>
+      <c r="AH45" s="11" t="n">
+        <v>1.3919</v>
+      </c>
+      <c r="AI45" s="11" t="n">
+        <v>1.3853</v>
+      </c>
+      <c r="AJ45" s="11" t="n">
+        <v>1.3789</v>
+      </c>
+      <c r="AK45" s="11" t="n">
+        <v>1.373</v>
+      </c>
+      <c r="AL45" s="11" t="n">
+        <v>1.3675</v>
+      </c>
+      <c r="AM45" s="11" t="n">
+        <v>1.3626</v>
+      </c>
+      <c r="AN45" s="11" t="n">
+        <v>1.3582</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>5.6419</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>5.6116</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>5.8103</v>
+      </c>
+      <c r="G46" s="11" t="n">
+        <v>5.5783</v>
+      </c>
+      <c r="H46" s="11" t="n">
+        <v>5.3631</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>5.2579</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>5.2628</v>
+      </c>
+      <c r="K46" s="11" t="n">
+        <v>5.217</v>
+      </c>
+      <c r="L46" s="11" t="n">
+        <v>5.1683</v>
+      </c>
+      <c r="M46" s="11" t="n">
+        <v>5.1167</v>
+      </c>
+      <c r="N46" s="11" t="n">
+        <v>5.0623</v>
+      </c>
+      <c r="O46" s="11" t="n">
+        <v>5.0051</v>
+      </c>
+      <c r="P46" s="11" t="n">
+        <v>4.945</v>
+      </c>
+      <c r="Q46" s="11" t="n">
+        <v>4.7676</v>
+      </c>
+      <c r="R46" s="11" t="n">
+        <v>4.625</v>
+      </c>
+      <c r="S46" s="11" t="n">
+        <v>4.5171</v>
+      </c>
+      <c r="T46" s="11" t="n">
+        <v>4.4439</v>
+      </c>
+      <c r="U46" s="11" t="n">
+        <v>4.4054</v>
+      </c>
+      <c r="V46" s="11" t="n">
+        <v>4.4017</v>
+      </c>
+      <c r="W46" s="11" t="n">
+        <v>4.4328</v>
+      </c>
+      <c r="X46" s="11" t="n">
+        <v>4.4985</v>
+      </c>
+      <c r="Y46" s="11" t="n">
+        <v>4.599</v>
+      </c>
+      <c r="Z46" s="11" t="n">
+        <v>4.7342</v>
+      </c>
+      <c r="AA46" s="11" t="n">
+        <v>4.9042</v>
+      </c>
+      <c r="AB46" s="11" t="n">
+        <v>5.1089</v>
+      </c>
+      <c r="AC46" s="11" t="n">
+        <v>5.2647</v>
+      </c>
+      <c r="AD46" s="11" t="n">
+        <v>5.3998</v>
+      </c>
+      <c r="AE46" s="11" t="n">
+        <v>5.5141</v>
+      </c>
+      <c r="AF46" s="11" t="n">
+        <v>5.6076</v>
+      </c>
+      <c r="AG46" s="11" t="n">
+        <v>5.6804</v>
+      </c>
+      <c r="AH46" s="11" t="n">
+        <v>5.7323</v>
+      </c>
+      <c r="AI46" s="11" t="n">
+        <v>5.7635</v>
+      </c>
+      <c r="AJ46" s="11" t="n">
+        <v>5.7739</v>
+      </c>
+      <c r="AK46" s="11" t="n">
+        <v>5.7635</v>
+      </c>
+      <c r="AL46" s="11" t="n">
+        <v>5.7323</v>
+      </c>
+      <c r="AM46" s="11" t="n">
+        <v>5.6804</v>
+      </c>
+      <c r="AN46" s="11" t="n">
+        <v>5.6076</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>5.6419</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>5.5481</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>5.6475</v>
+      </c>
+      <c r="G47" s="11" t="n">
+        <v>5.675</v>
+      </c>
+      <c r="H47" s="11" t="n">
+        <v>5.6217</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>5.5576</v>
+      </c>
+      <c r="J47" s="11" t="n">
+        <v>5.5065</v>
+      </c>
+      <c r="K47" s="11" t="n">
+        <v>5.4685</v>
+      </c>
+      <c r="L47" s="11" t="n">
+        <v>5.434</v>
+      </c>
+      <c r="M47" s="11" t="n">
+        <v>5.4017</v>
+      </c>
+      <c r="N47" s="11" t="n">
+        <v>5.3705</v>
+      </c>
+      <c r="O47" s="11" t="n">
+        <v>5.3399</v>
+      </c>
+      <c r="P47" s="11" t="n">
+        <v>5.3095</v>
+      </c>
+      <c r="Q47" s="11" t="n">
+        <v>5.2744</v>
+      </c>
+      <c r="R47" s="11" t="n">
+        <v>5.2329</v>
+      </c>
+      <c r="S47" s="11" t="n">
+        <v>5.1886</v>
+      </c>
+      <c r="T47" s="11" t="n">
+        <v>5.1442</v>
+      </c>
+      <c r="U47" s="11" t="n">
+        <v>5.1017</v>
+      </c>
+      <c r="V47" s="11" t="n">
+        <v>5.0627</v>
+      </c>
+      <c r="W47" s="11" t="n">
+        <v>5.0286</v>
+      </c>
+      <c r="X47" s="11" t="n">
+        <v>5.0003</v>
+      </c>
+      <c r="Y47" s="11" t="n">
+        <v>4.9787</v>
+      </c>
+      <c r="Z47" s="11" t="n">
+        <v>4.9644</v>
+      </c>
+      <c r="AA47" s="11" t="n">
+        <v>4.9579</v>
+      </c>
+      <c r="AB47" s="11" t="n">
+        <v>4.9598</v>
+      </c>
+      <c r="AC47" s="11" t="n">
+        <v>4.969</v>
+      </c>
+      <c r="AD47" s="11" t="n">
+        <v>4.983</v>
+      </c>
+      <c r="AE47" s="11" t="n">
+        <v>5.0006</v>
+      </c>
+      <c r="AF47" s="11" t="n">
+        <v>5.0207</v>
+      </c>
+      <c r="AG47" s="11" t="n">
+        <v>5.0423</v>
+      </c>
+      <c r="AH47" s="11" t="n">
+        <v>5.0644</v>
+      </c>
+      <c r="AI47" s="11" t="n">
+        <v>5.0865</v>
+      </c>
+      <c r="AJ47" s="11" t="n">
+        <v>5.1079</v>
+      </c>
+      <c r="AK47" s="11" t="n">
+        <v>5.128</v>
+      </c>
+      <c r="AL47" s="11" t="n">
+        <v>5.1463</v>
+      </c>
+      <c r="AM47" s="11" t="n">
+        <v>5.1623</v>
+      </c>
+      <c r="AN47" s="11" t="n">
+        <v>5.1758</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>2.6633</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>2.5973</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>2.4783</v>
+      </c>
+      <c r="G48" s="11" t="n">
+        <v>2.5318</v>
+      </c>
+      <c r="H48" s="11" t="n">
+        <v>2.6203</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>2.5813</v>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>2.4151</v>
+      </c>
+      <c r="K48" s="11" t="n">
+        <v>2.2212</v>
+      </c>
+      <c r="L48" s="11" t="n">
+        <v>2.0882</v>
+      </c>
+      <c r="M48" s="11" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="N48" s="11" t="n">
+        <v>2.0047</v>
+      </c>
+      <c r="O48" s="11" t="n">
+        <v>2.0542</v>
+      </c>
+      <c r="P48" s="11" t="n">
+        <v>2.1646</v>
+      </c>
+      <c r="Q48" s="11" t="n">
+        <v>2.1952</v>
+      </c>
+      <c r="R48" s="11" t="n">
+        <v>2.2226</v>
+      </c>
+      <c r="S48" s="11" t="n">
+        <v>2.2467</v>
+      </c>
+      <c r="T48" s="11" t="n">
+        <v>2.2674</v>
+      </c>
+      <c r="U48" s="11" t="n">
+        <v>2.2849</v>
+      </c>
+      <c r="V48" s="11" t="n">
+        <v>2.299</v>
+      </c>
+      <c r="W48" s="11" t="n">
+        <v>2.3098</v>
+      </c>
+      <c r="X48" s="11" t="n">
+        <v>2.3173</v>
+      </c>
+      <c r="Y48" s="11" t="n">
+        <v>2.3215</v>
+      </c>
+      <c r="Z48" s="11" t="n">
+        <v>2.3224</v>
+      </c>
+      <c r="AA48" s="11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB48" s="11" t="n">
+        <v>2.3142</v>
+      </c>
+      <c r="AC48" s="11" t="n">
+        <v>2.3252</v>
+      </c>
+      <c r="AD48" s="11" t="n">
+        <v>2.3347</v>
+      </c>
+      <c r="AE48" s="11" t="n">
+        <v>2.3427</v>
+      </c>
+      <c r="AF48" s="11" t="n">
+        <v>2.3493</v>
+      </c>
+      <c r="AG48" s="11" t="n">
+        <v>2.3544</v>
+      </c>
+      <c r="AH48" s="11" t="n">
+        <v>2.3581</v>
+      </c>
+      <c r="AI48" s="11" t="n">
+        <v>2.3603</v>
+      </c>
+      <c r="AJ48" s="11" t="n">
+        <v>2.361</v>
+      </c>
+      <c r="AK48" s="11" t="n">
+        <v>2.3603</v>
+      </c>
+      <c r="AL48" s="11" t="n">
+        <v>2.3581</v>
+      </c>
+      <c r="AM48" s="11" t="n">
+        <v>2.3544</v>
+      </c>
+      <c r="AN48" s="11" t="n">
+        <v>2.3493</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>2.6633</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>2.6424</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>2.5829</v>
+      </c>
+      <c r="G49" s="11" t="n">
+        <v>2.5522</v>
+      </c>
+      <c r="H49" s="11" t="n">
+        <v>2.5608</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>2.5709</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>2.5606</v>
+      </c>
+      <c r="K49" s="11" t="n">
+        <v>2.5252</v>
+      </c>
+      <c r="L49" s="11" t="n">
+        <v>2.4783</v>
+      </c>
+      <c r="M49" s="11" t="n">
+        <v>2.4303</v>
+      </c>
+      <c r="N49" s="11" t="n">
+        <v>2.3878</v>
+      </c>
+      <c r="O49" s="11" t="n">
+        <v>2.3548</v>
+      </c>
+      <c r="P49" s="11" t="n">
+        <v>2.3339</v>
+      </c>
+      <c r="Q49" s="11" t="n">
+        <v>2.3221</v>
+      </c>
+      <c r="R49" s="11" t="n">
+        <v>2.314</v>
+      </c>
+      <c r="S49" s="11" t="n">
+        <v>2.3088</v>
+      </c>
+      <c r="T49" s="11" t="n">
+        <v>2.3055</v>
+      </c>
+      <c r="U49" s="11" t="n">
+        <v>2.3038</v>
+      </c>
+      <c r="V49" s="11" t="n">
+        <v>2.3032</v>
+      </c>
+      <c r="W49" s="11" t="n">
+        <v>2.3033</v>
+      </c>
+      <c r="X49" s="11" t="n">
+        <v>2.3038</v>
+      </c>
+      <c r="Y49" s="11" t="n">
+        <v>2.3045</v>
+      </c>
+      <c r="Z49" s="11" t="n">
+        <v>2.3054</v>
+      </c>
+      <c r="AA49" s="11" t="n">
+        <v>2.3061</v>
+      </c>
+      <c r="AB49" s="11" t="n">
+        <v>2.3065</v>
+      </c>
+      <c r="AC49" s="11" t="n">
+        <v>2.3071</v>
+      </c>
+      <c r="AD49" s="11" t="n">
+        <v>2.3079</v>
+      </c>
+      <c r="AE49" s="11" t="n">
+        <v>2.3091</v>
+      </c>
+      <c r="AF49" s="11" t="n">
+        <v>2.3104</v>
+      </c>
+      <c r="AG49" s="11" t="n">
+        <v>2.3118</v>
+      </c>
+      <c r="AH49" s="11" t="n">
+        <v>2.3133</v>
+      </c>
+      <c r="AI49" s="11" t="n">
+        <v>2.3148</v>
+      </c>
+      <c r="AJ49" s="11" t="n">
+        <v>2.3162</v>
+      </c>
+      <c r="AK49" s="11" t="n">
+        <v>2.3176</v>
+      </c>
+      <c r="AL49" s="11" t="n">
+        <v>2.3188</v>
+      </c>
+      <c r="AM49" s="11" t="n">
+        <v>2.3199</v>
+      </c>
+      <c r="AN49" s="11" t="n">
+        <v>2.3208</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN43"/>
+  <autoFilter ref="A1:AN49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35704,7 +36540,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-03  (7 daily snapshots, 42 curve rows)</t>
+          <t>2026-08-28 to 2026-09-04  (8 daily snapshots, 48 curve rows)</t>
         </is>
       </c>
     </row>
@@ -35776,7 +36612,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-02  (12 rows)</t>
+          <t>2026-08-22 to 2026-09-03  (13 rows)</t>
         </is>
       </c>
     </row>
@@ -35800,7 +36636,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-03  (12 rows)</t>
+          <t>2026-08-23 to 2026-09-04  (13 rows)</t>
         </is>
       </c>
     </row>
@@ -35812,7 +36648,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 19:19 local</t>
+          <t>2026-09-04 19:01 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
   </definedNames>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$14</f>
+              <f>'GPU Rental'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$14</f>
+              <f>'GPU Rental'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$14</f>
+              <f>'GPU Rental'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$14</f>
+              <f>'GPU Rental'!$C$2:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$14</f>
+              <f>'GPU Rental'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$14</f>
+              <f>'GPU Rental'!$D$2:$D$15</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$14</f>
+              <f>'GPU Rental'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$14</f>
+              <f>'GPU Rental'!$E$2:$E$15</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$14</f>
+              <f>'GPU Rental'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$14</f>
+              <f>'GPU Rental'!$F$2:$F$15</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$14</f>
+              <f>'GPU Rental'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$14</f>
+              <f>'GPU Rental'!$G$2:$G$15</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$14</f>
+              <f>'GPU Rental'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$14</f>
+              <f>'GPU Rental'!$H$2:$H$15</f>
             </numRef>
           </val>
         </ser>
@@ -1388,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2159,8 +2159,62 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I15" s="4">
+        <f>IF(OR(B15="",B14=""),"",B15/B14-1)</f>
+        <v/>
+      </c>
+      <c r="J15" s="4">
+        <f>IF(OR(C15="",C14=""),"",C15/C14-1)</f>
+        <v/>
+      </c>
+      <c r="K15" s="4">
+        <f>IF(OR(D15="",D14=""),"",D15/D14-1)</f>
+        <v/>
+      </c>
+      <c r="L15" s="4">
+        <f>IF(OR(E15="",E14=""),"",E15/E14-1)</f>
+        <v/>
+      </c>
+      <c r="M15" s="4">
+        <f>IF(OR(F15="",F14=""),"",F15/F14-1)</f>
+        <v/>
+      </c>
+      <c r="N15" s="4">
+        <f>IF(OR(G15="",G14=""),"",G15/G14-1)</f>
+        <v/>
+      </c>
+      <c r="O15" s="4">
+        <f>IF(OR(H15="",H14=""),"",H15/H14-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O14"/>
+  <autoFilter ref="A1:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2171,7 +2225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN49"/>
+  <dimension ref="A1:AN55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8466,8 +8520,764 @@
         <v>2.3208</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="10" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>1.5977</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>1.7315</v>
+      </c>
+      <c r="G50" s="11" t="n">
+        <v>1.6487</v>
+      </c>
+      <c r="H50" s="11" t="n">
+        <v>1.6006</v>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>1.5552</v>
+      </c>
+      <c r="J50" s="11" t="n">
+        <v>1.5125</v>
+      </c>
+      <c r="K50" s="11" t="n">
+        <v>1.4347</v>
+      </c>
+      <c r="L50" s="11" t="n">
+        <v>1.3794</v>
+      </c>
+      <c r="M50" s="11" t="n">
+        <v>1.3466</v>
+      </c>
+      <c r="N50" s="11" t="n">
+        <v>1.3364</v>
+      </c>
+      <c r="O50" s="11" t="n">
+        <v>1.3486</v>
+      </c>
+      <c r="P50" s="11" t="n">
+        <v>1.3833</v>
+      </c>
+      <c r="Q50" s="11" t="n">
+        <v>1.3974</v>
+      </c>
+      <c r="R50" s="11" t="n">
+        <v>1.4077</v>
+      </c>
+      <c r="S50" s="11" t="n">
+        <v>1.4143</v>
+      </c>
+      <c r="T50" s="11" t="n">
+        <v>1.4171</v>
+      </c>
+      <c r="U50" s="11" t="n">
+        <v>1.4162</v>
+      </c>
+      <c r="V50" s="11" t="n">
+        <v>1.4116</v>
+      </c>
+      <c r="W50" s="11" t="n">
+        <v>1.4032</v>
+      </c>
+      <c r="X50" s="11" t="n">
+        <v>1.3911</v>
+      </c>
+      <c r="Y50" s="11" t="n">
+        <v>1.3752</v>
+      </c>
+      <c r="Z50" s="11" t="n">
+        <v>1.3556</v>
+      </c>
+      <c r="AA50" s="11" t="n">
+        <v>1.3323</v>
+      </c>
+      <c r="AB50" s="11" t="n">
+        <v>1.3052</v>
+      </c>
+      <c r="AC50" s="11" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="AD50" s="11" t="n">
+        <v>1.2563</v>
+      </c>
+      <c r="AE50" s="11" t="n">
+        <v>1.2371</v>
+      </c>
+      <c r="AF50" s="11" t="n">
+        <v>1.2214</v>
+      </c>
+      <c r="AG50" s="11" t="n">
+        <v>1.2091</v>
+      </c>
+      <c r="AH50" s="11" t="n">
+        <v>1.2004</v>
+      </c>
+      <c r="AI50" s="11" t="n">
+        <v>1.1951</v>
+      </c>
+      <c r="AJ50" s="11" t="n">
+        <v>1.1934</v>
+      </c>
+      <c r="AK50" s="11" t="n">
+        <v>1.1951</v>
+      </c>
+      <c r="AL50" s="11" t="n">
+        <v>1.2004</v>
+      </c>
+      <c r="AM50" s="11" t="n">
+        <v>1.2091</v>
+      </c>
+      <c r="AN50" s="11" t="n">
+        <v>1.2214</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>1.5488</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>1.6157</v>
+      </c>
+      <c r="G51" s="11" t="n">
+        <v>1.6465</v>
+      </c>
+      <c r="H51" s="11" t="n">
+        <v>1.641</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>1.6283</v>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>1.6126</v>
+      </c>
+      <c r="K51" s="11" t="n">
+        <v>1.5924</v>
+      </c>
+      <c r="L51" s="11" t="n">
+        <v>1.569</v>
+      </c>
+      <c r="M51" s="11" t="n">
+        <v>1.5459</v>
+      </c>
+      <c r="N51" s="11" t="n">
+        <v>1.5253</v>
+      </c>
+      <c r="O51" s="11" t="n">
+        <v>1.5085</v>
+      </c>
+      <c r="P51" s="11" t="n">
+        <v>1.4965</v>
+      </c>
+      <c r="Q51" s="11" t="n">
+        <v>1.4883</v>
+      </c>
+      <c r="R51" s="11" t="n">
+        <v>1.4822</v>
+      </c>
+      <c r="S51" s="11" t="n">
+        <v>1.4775</v>
+      </c>
+      <c r="T51" s="11" t="n">
+        <v>1.4737</v>
+      </c>
+      <c r="U51" s="11" t="n">
+        <v>1.4703</v>
+      </c>
+      <c r="V51" s="11" t="n">
+        <v>1.4672</v>
+      </c>
+      <c r="W51" s="11" t="n">
+        <v>1.4641</v>
+      </c>
+      <c r="X51" s="11" t="n">
+        <v>1.4607</v>
+      </c>
+      <c r="Y51" s="11" t="n">
+        <v>1.4571</v>
+      </c>
+      <c r="Z51" s="11" t="n">
+        <v>1.4529</v>
+      </c>
+      <c r="AA51" s="11" t="n">
+        <v>1.4482</v>
+      </c>
+      <c r="AB51" s="11" t="n">
+        <v>1.4428</v>
+      </c>
+      <c r="AC51" s="11" t="n">
+        <v>1.4368</v>
+      </c>
+      <c r="AD51" s="11" t="n">
+        <v>1.4302</v>
+      </c>
+      <c r="AE51" s="11" t="n">
+        <v>1.4234</v>
+      </c>
+      <c r="AF51" s="11" t="n">
+        <v>1.4165</v>
+      </c>
+      <c r="AG51" s="11" t="n">
+        <v>1.4095</v>
+      </c>
+      <c r="AH51" s="11" t="n">
+        <v>1.4027</v>
+      </c>
+      <c r="AI51" s="11" t="n">
+        <v>1.3961</v>
+      </c>
+      <c r="AJ51" s="11" t="n">
+        <v>1.3898</v>
+      </c>
+      <c r="AK51" s="11" t="n">
+        <v>1.3838</v>
+      </c>
+      <c r="AL51" s="11" t="n">
+        <v>1.3784</v>
+      </c>
+      <c r="AM51" s="11" t="n">
+        <v>1.3734</v>
+      </c>
+      <c r="AN51" s="11" t="n">
+        <v>1.369</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>5.6614</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>5.6764</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>5.7577</v>
+      </c>
+      <c r="G52" s="11" t="n">
+        <v>5.6629</v>
+      </c>
+      <c r="H52" s="11" t="n">
+        <v>5.6141</v>
+      </c>
+      <c r="I52" s="11" t="n">
+        <v>5.532</v>
+      </c>
+      <c r="J52" s="11" t="n">
+        <v>5.4165</v>
+      </c>
+      <c r="K52" s="11" t="n">
+        <v>5.2704</v>
+      </c>
+      <c r="L52" s="11" t="n">
+        <v>5.1558</v>
+      </c>
+      <c r="M52" s="11" t="n">
+        <v>5.0727</v>
+      </c>
+      <c r="N52" s="11" t="n">
+        <v>5.0211</v>
+      </c>
+      <c r="O52" s="11" t="n">
+        <v>5.001</v>
+      </c>
+      <c r="P52" s="11" t="n">
+        <v>5.0123</v>
+      </c>
+      <c r="Q52" s="11" t="n">
+        <v>4.8984</v>
+      </c>
+      <c r="R52" s="11" t="n">
+        <v>4.8069</v>
+      </c>
+      <c r="S52" s="11" t="n">
+        <v>4.7376</v>
+      </c>
+      <c r="T52" s="11" t="n">
+        <v>4.6906</v>
+      </c>
+      <c r="U52" s="11" t="n">
+        <v>4.6658</v>
+      </c>
+      <c r="V52" s="11" t="n">
+        <v>4.6633</v>
+      </c>
+      <c r="W52" s="11" t="n">
+        <v>4.6831</v>
+      </c>
+      <c r="X52" s="11" t="n">
+        <v>4.7252</v>
+      </c>
+      <c r="Y52" s="11" t="n">
+        <v>4.7896</v>
+      </c>
+      <c r="Z52" s="11" t="n">
+        <v>4.8762</v>
+      </c>
+      <c r="AA52" s="11" t="n">
+        <v>4.9851</v>
+      </c>
+      <c r="AB52" s="11" t="n">
+        <v>5.1163</v>
+      </c>
+      <c r="AC52" s="11" t="n">
+        <v>5.2161</v>
+      </c>
+      <c r="AD52" s="11" t="n">
+        <v>5.3025</v>
+      </c>
+      <c r="AE52" s="11" t="n">
+        <v>5.3757</v>
+      </c>
+      <c r="AF52" s="11" t="n">
+        <v>5.4356</v>
+      </c>
+      <c r="AG52" s="11" t="n">
+        <v>5.4821</v>
+      </c>
+      <c r="AH52" s="11" t="n">
+        <v>5.5154</v>
+      </c>
+      <c r="AI52" s="11" t="n">
+        <v>5.5354</v>
+      </c>
+      <c r="AJ52" s="11" t="n">
+        <v>5.542</v>
+      </c>
+      <c r="AK52" s="11" t="n">
+        <v>5.5354</v>
+      </c>
+      <c r="AL52" s="11" t="n">
+        <v>5.5154</v>
+      </c>
+      <c r="AM52" s="11" t="n">
+        <v>5.4821</v>
+      </c>
+      <c r="AN52" s="11" t="n">
+        <v>5.4356</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>5.6614</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>5.6505</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>5.6911</v>
+      </c>
+      <c r="G53" s="11" t="n">
+        <v>5.7024</v>
+      </c>
+      <c r="H53" s="11" t="n">
+        <v>5.6871</v>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>5.6649</v>
+      </c>
+      <c r="J53" s="11" t="n">
+        <v>5.6336</v>
+      </c>
+      <c r="K53" s="11" t="n">
+        <v>5.5917</v>
+      </c>
+      <c r="L53" s="11" t="n">
+        <v>5.5441</v>
+      </c>
+      <c r="M53" s="11" t="n">
+        <v>5.496</v>
+      </c>
+      <c r="N53" s="11" t="n">
+        <v>5.4509</v>
+      </c>
+      <c r="O53" s="11" t="n">
+        <v>5.4106</v>
+      </c>
+      <c r="P53" s="11" t="n">
+        <v>5.3768</v>
+      </c>
+      <c r="Q53" s="11" t="n">
+        <v>5.3442</v>
+      </c>
+      <c r="R53" s="11" t="n">
+        <v>5.309</v>
+      </c>
+      <c r="S53" s="11" t="n">
+        <v>5.273</v>
+      </c>
+      <c r="T53" s="11" t="n">
+        <v>5.238</v>
+      </c>
+      <c r="U53" s="11" t="n">
+        <v>5.205</v>
+      </c>
+      <c r="V53" s="11" t="n">
+        <v>5.1748</v>
+      </c>
+      <c r="W53" s="11" t="n">
+        <v>5.1483</v>
+      </c>
+      <c r="X53" s="11" t="n">
+        <v>5.126</v>
+      </c>
+      <c r="Y53" s="11" t="n">
+        <v>5.1084</v>
+      </c>
+      <c r="Z53" s="11" t="n">
+        <v>5.0958</v>
+      </c>
+      <c r="AA53" s="11" t="n">
+        <v>5.0885</v>
+      </c>
+      <c r="AB53" s="11" t="n">
+        <v>5.0869</v>
+      </c>
+      <c r="AC53" s="11" t="n">
+        <v>5.0901</v>
+      </c>
+      <c r="AD53" s="11" t="n">
+        <v>5.0966</v>
+      </c>
+      <c r="AE53" s="11" t="n">
+        <v>5.1057</v>
+      </c>
+      <c r="AF53" s="11" t="n">
+        <v>5.1164</v>
+      </c>
+      <c r="AG53" s="11" t="n">
+        <v>5.1283</v>
+      </c>
+      <c r="AH53" s="11" t="n">
+        <v>5.1406</v>
+      </c>
+      <c r="AI53" s="11" t="n">
+        <v>5.1531</v>
+      </c>
+      <c r="AJ53" s="11" t="n">
+        <v>5.1652</v>
+      </c>
+      <c r="AK53" s="11" t="n">
+        <v>5.1765</v>
+      </c>
+      <c r="AL53" s="11" t="n">
+        <v>5.1868</v>
+      </c>
+      <c r="AM53" s="11" t="n">
+        <v>5.1958</v>
+      </c>
+      <c r="AN53" s="11" t="n">
+        <v>5.2031</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>2.6477</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>2.5697</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>2.4521</v>
+      </c>
+      <c r="G54" s="11" t="n">
+        <v>2.5051</v>
+      </c>
+      <c r="H54" s="11" t="n">
+        <v>2.5931</v>
+      </c>
+      <c r="I54" s="11" t="n">
+        <v>2.5542</v>
+      </c>
+      <c r="J54" s="11" t="n">
+        <v>2.3885</v>
+      </c>
+      <c r="K54" s="11" t="n">
+        <v>2.1954</v>
+      </c>
+      <c r="L54" s="11" t="n">
+        <v>2.0629</v>
+      </c>
+      <c r="M54" s="11" t="n">
+        <v>1.9909</v>
+      </c>
+      <c r="N54" s="11" t="n">
+        <v>1.9795</v>
+      </c>
+      <c r="O54" s="11" t="n">
+        <v>2.0287</v>
+      </c>
+      <c r="P54" s="11" t="n">
+        <v>2.1385</v>
+      </c>
+      <c r="Q54" s="11" t="n">
+        <v>2.1687</v>
+      </c>
+      <c r="R54" s="11" t="n">
+        <v>2.1958</v>
+      </c>
+      <c r="S54" s="11" t="n">
+        <v>2.2195</v>
+      </c>
+      <c r="T54" s="11" t="n">
+        <v>2.2401</v>
+      </c>
+      <c r="U54" s="11" t="n">
+        <v>2.2573</v>
+      </c>
+      <c r="V54" s="11" t="n">
+        <v>2.2714</v>
+      </c>
+      <c r="W54" s="11" t="n">
+        <v>2.2822</v>
+      </c>
+      <c r="X54" s="11" t="n">
+        <v>2.2897</v>
+      </c>
+      <c r="Y54" s="11" t="n">
+        <v>2.2941</v>
+      </c>
+      <c r="Z54" s="11" t="n">
+        <v>2.2951</v>
+      </c>
+      <c r="AA54" s="11" t="n">
+        <v>2.293</v>
+      </c>
+      <c r="AB54" s="11" t="n">
+        <v>2.2876</v>
+      </c>
+      <c r="AC54" s="11" t="n">
+        <v>2.2987</v>
+      </c>
+      <c r="AD54" s="11" t="n">
+        <v>2.3083</v>
+      </c>
+      <c r="AE54" s="11" t="n">
+        <v>2.3165</v>
+      </c>
+      <c r="AF54" s="11" t="n">
+        <v>2.3232</v>
+      </c>
+      <c r="AG54" s="11" t="n">
+        <v>2.3284</v>
+      </c>
+      <c r="AH54" s="11" t="n">
+        <v>2.3321</v>
+      </c>
+      <c r="AI54" s="11" t="n">
+        <v>2.3343</v>
+      </c>
+      <c r="AJ54" s="11" t="n">
+        <v>2.3351</v>
+      </c>
+      <c r="AK54" s="11" t="n">
+        <v>2.3343</v>
+      </c>
+      <c r="AL54" s="11" t="n">
+        <v>2.3321</v>
+      </c>
+      <c r="AM54" s="11" t="n">
+        <v>2.3284</v>
+      </c>
+      <c r="AN54" s="11" t="n">
+        <v>2.3232</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>2.6477</v>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>2.6142</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>2.5555</v>
+      </c>
+      <c r="G55" s="11" t="n">
+        <v>2.5251</v>
+      </c>
+      <c r="H55" s="11" t="n">
+        <v>2.5338</v>
+      </c>
+      <c r="I55" s="11" t="n">
+        <v>2.5438</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>2.5335</v>
+      </c>
+      <c r="K55" s="11" t="n">
+        <v>2.4983</v>
+      </c>
+      <c r="L55" s="11" t="n">
+        <v>2.4515</v>
+      </c>
+      <c r="M55" s="11" t="n">
+        <v>2.4038</v>
+      </c>
+      <c r="N55" s="11" t="n">
+        <v>2.3614</v>
+      </c>
+      <c r="O55" s="11" t="n">
+        <v>2.3285</v>
+      </c>
+      <c r="P55" s="11" t="n">
+        <v>2.3077</v>
+      </c>
+      <c r="Q55" s="11" t="n">
+        <v>2.2958</v>
+      </c>
+      <c r="R55" s="11" t="n">
+        <v>2.2877</v>
+      </c>
+      <c r="S55" s="11" t="n">
+        <v>2.2824</v>
+      </c>
+      <c r="T55" s="11" t="n">
+        <v>2.2791</v>
+      </c>
+      <c r="U55" s="11" t="n">
+        <v>2.2774</v>
+      </c>
+      <c r="V55" s="11" t="n">
+        <v>2.2767</v>
+      </c>
+      <c r="W55" s="11" t="n">
+        <v>2.2767</v>
+      </c>
+      <c r="X55" s="11" t="n">
+        <v>2.2772</v>
+      </c>
+      <c r="Y55" s="11" t="n">
+        <v>2.2779</v>
+      </c>
+      <c r="Z55" s="11" t="n">
+        <v>2.2786</v>
+      </c>
+      <c r="AA55" s="11" t="n">
+        <v>2.2793</v>
+      </c>
+      <c r="AB55" s="11" t="n">
+        <v>2.2798</v>
+      </c>
+      <c r="AC55" s="11" t="n">
+        <v>2.2803</v>
+      </c>
+      <c r="AD55" s="11" t="n">
+        <v>2.2812</v>
+      </c>
+      <c r="AE55" s="11" t="n">
+        <v>2.2824</v>
+      </c>
+      <c r="AF55" s="11" t="n">
+        <v>2.2837</v>
+      </c>
+      <c r="AG55" s="11" t="n">
+        <v>2.2852</v>
+      </c>
+      <c r="AH55" s="11" t="n">
+        <v>2.2867</v>
+      </c>
+      <c r="AI55" s="11" t="n">
+        <v>2.2882</v>
+      </c>
+      <c r="AJ55" s="11" t="n">
+        <v>2.2897</v>
+      </c>
+      <c r="AK55" s="11" t="n">
+        <v>2.291</v>
+      </c>
+      <c r="AL55" s="11" t="n">
+        <v>2.2923</v>
+      </c>
+      <c r="AM55" s="11" t="n">
+        <v>2.2934</v>
+      </c>
+      <c r="AN55" s="11" t="n">
+        <v>2.2943</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN49"/>
+  <autoFilter ref="A1:AN55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36540,7 +37350,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-04  (8 daily snapshots, 48 curve rows)</t>
+          <t>2026-08-28 to 2026-09-05  (9 daily snapshots, 54 curve rows)</t>
         </is>
       </c>
     </row>
@@ -36636,7 +37446,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-04  (13 rows)</t>
+          <t>2026-08-23 to 2026-09-05  (14 rows)</t>
         </is>
       </c>
     </row>
@@ -36648,7 +37458,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-04 19:01 local</t>
+          <t>2026-09-05 18:23 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$14</f>
+              <f>'Daily Index'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$14</f>
+              <f>'Daily Index'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$14</f>
+              <f>'Daily Index'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$14</f>
+              <f>'Daily Index'!$C$2:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$14</f>
+              <f>'Daily Index'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$14</f>
+              <f>'Daily Index'!$D$2:$D$15</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1376,8 +1376,34 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>0.9735</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>0.5281</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>1.9738</v>
+      </c>
+      <c r="E15" s="4">
+        <f>IF(OR(B15="",B14=""),"",B15/B14-1)</f>
+        <v/>
+      </c>
+      <c r="F15" s="4">
+        <f>IF(OR(C15="",C14=""),"",C15/C14-1)</f>
+        <v/>
+      </c>
+      <c r="G15" s="4">
+        <f>IF(OR(D15="",D14=""),"",D15/D14-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37422,7 +37448,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-03  (13 rows)</t>
+          <t>2026-08-22 to 2026-09-04  (14 rows)</t>
         </is>
       </c>
     </row>
@@ -37458,7 +37484,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-05 18:23 local</t>
+          <t>2026-09-06 05:58 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,9 +16,9 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
   </definedNames>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$15</f>
+              <f>'Daily Index'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$15</f>
+              <f>'Daily Index'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$15</f>
+              <f>'Daily Index'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$15</f>
+              <f>'Daily Index'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$15</f>
+              <f>'Daily Index'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$15</f>
+              <f>'Daily Index'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$15</f>
+              <f>'GPU Rental'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$15</f>
+              <f>'GPU Rental'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$15</f>
+              <f>'GPU Rental'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$15</f>
+              <f>'GPU Rental'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$15</f>
+              <f>'GPU Rental'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$15</f>
+              <f>'GPU Rental'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$15</f>
+              <f>'GPU Rental'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$15</f>
+              <f>'GPU Rental'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$15</f>
+              <f>'GPU Rental'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$15</f>
+              <f>'GPU Rental'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$15</f>
+              <f>'GPU Rental'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$15</f>
+              <f>'GPU Rental'!$G$2:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$15</f>
+              <f>'GPU Rental'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$15</f>
+              <f>'GPU Rental'!$H$2:$H$16</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1402,8 +1402,34 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>0.9861</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>0.5338000000000001</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>1.9822</v>
+      </c>
+      <c r="E16" s="4">
+        <f>IF(OR(B16="",B15=""),"",B16/B15-1)</f>
+        <v/>
+      </c>
+      <c r="F16" s="4">
+        <f>IF(OR(C16="",C15=""),"",C16/C15-1)</f>
+        <v/>
+      </c>
+      <c r="G16" s="4">
+        <f>IF(OR(D16="",D15=""),"",D16/D15-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1414,7 +1440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2239,8 +2265,62 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I16" s="4">
+        <f>IF(OR(B16="",B15=""),"",B16/B15-1)</f>
+        <v/>
+      </c>
+      <c r="J16" s="4">
+        <f>IF(OR(C16="",C15=""),"",C16/C15-1)</f>
+        <v/>
+      </c>
+      <c r="K16" s="4">
+        <f>IF(OR(D16="",D15=""),"",D16/D15-1)</f>
+        <v/>
+      </c>
+      <c r="L16" s="4">
+        <f>IF(OR(E16="",E15=""),"",E16/E15-1)</f>
+        <v/>
+      </c>
+      <c r="M16" s="4">
+        <f>IF(OR(F16="",F15=""),"",F16/F15-1)</f>
+        <v/>
+      </c>
+      <c r="N16" s="4">
+        <f>IF(OR(G16="",G15=""),"",G16/G15-1)</f>
+        <v/>
+      </c>
+      <c r="O16" s="4">
+        <f>IF(OR(H16="",H15=""),"",H16/H15-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O15"/>
+  <autoFilter ref="A1:O16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2251,7 +2331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN55"/>
+  <dimension ref="A1:AN61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9302,8 +9382,764 @@
         <v>2.2943</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>1.6131</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>1.5958</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>1.7291</v>
+      </c>
+      <c r="G56" s="11" t="n">
+        <v>1.6463</v>
+      </c>
+      <c r="H56" s="11" t="n">
+        <v>1.5981</v>
+      </c>
+      <c r="I56" s="11" t="n">
+        <v>1.5528</v>
+      </c>
+      <c r="J56" s="11" t="n">
+        <v>1.5101</v>
+      </c>
+      <c r="K56" s="11" t="n">
+        <v>1.4324</v>
+      </c>
+      <c r="L56" s="11" t="n">
+        <v>1.3772</v>
+      </c>
+      <c r="M56" s="11" t="n">
+        <v>1.3444</v>
+      </c>
+      <c r="N56" s="11" t="n">
+        <v>1.3341</v>
+      </c>
+      <c r="O56" s="11" t="n">
+        <v>1.3463</v>
+      </c>
+      <c r="P56" s="11" t="n">
+        <v>1.3809</v>
+      </c>
+      <c r="Q56" s="11" t="n">
+        <v>1.3948</v>
+      </c>
+      <c r="R56" s="11" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="S56" s="11" t="n">
+        <v>1.4115</v>
+      </c>
+      <c r="T56" s="11" t="n">
+        <v>1.4143</v>
+      </c>
+      <c r="U56" s="11" t="n">
+        <v>1.4134</v>
+      </c>
+      <c r="V56" s="11" t="n">
+        <v>1.4087</v>
+      </c>
+      <c r="W56" s="11" t="n">
+        <v>1.4003</v>
+      </c>
+      <c r="X56" s="11" t="n">
+        <v>1.3882</v>
+      </c>
+      <c r="Y56" s="11" t="n">
+        <v>1.3724</v>
+      </c>
+      <c r="Z56" s="11" t="n">
+        <v>1.3529</v>
+      </c>
+      <c r="AA56" s="11" t="n">
+        <v>1.3296</v>
+      </c>
+      <c r="AB56" s="11" t="n">
+        <v>1.3027</v>
+      </c>
+      <c r="AC56" s="11" t="n">
+        <v>1.2765</v>
+      </c>
+      <c r="AD56" s="11" t="n">
+        <v>1.2538</v>
+      </c>
+      <c r="AE56" s="11" t="n">
+        <v>1.2346</v>
+      </c>
+      <c r="AF56" s="11" t="n">
+        <v>1.2189</v>
+      </c>
+      <c r="AG56" s="11" t="n">
+        <v>1.2067</v>
+      </c>
+      <c r="AH56" s="11" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="AI56" s="11" t="n">
+        <v>1.1928</v>
+      </c>
+      <c r="AJ56" s="11" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="AK56" s="11" t="n">
+        <v>1.1928</v>
+      </c>
+      <c r="AL56" s="11" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="AM56" s="11" t="n">
+        <v>1.2067</v>
+      </c>
+      <c r="AN56" s="11" t="n">
+        <v>1.2189</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>1.6131</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>1.5471</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>1.6138</v>
+      </c>
+      <c r="G57" s="11" t="n">
+        <v>1.6444</v>
+      </c>
+      <c r="H57" s="11" t="n">
+        <v>1.6388</v>
+      </c>
+      <c r="I57" s="11" t="n">
+        <v>1.6261</v>
+      </c>
+      <c r="J57" s="11" t="n">
+        <v>1.6103</v>
+      </c>
+      <c r="K57" s="11" t="n">
+        <v>1.5902</v>
+      </c>
+      <c r="L57" s="11" t="n">
+        <v>1.5667</v>
+      </c>
+      <c r="M57" s="11" t="n">
+        <v>1.5437</v>
+      </c>
+      <c r="N57" s="11" t="n">
+        <v>1.523</v>
+      </c>
+      <c r="O57" s="11" t="n">
+        <v>1.5062</v>
+      </c>
+      <c r="P57" s="11" t="n">
+        <v>1.4942</v>
+      </c>
+      <c r="Q57" s="11" t="n">
+        <v>1.486</v>
+      </c>
+      <c r="R57" s="11" t="n">
+        <v>1.4799</v>
+      </c>
+      <c r="S57" s="11" t="n">
+        <v>1.4752</v>
+      </c>
+      <c r="T57" s="11" t="n">
+        <v>1.4713</v>
+      </c>
+      <c r="U57" s="11" t="n">
+        <v>1.4679</v>
+      </c>
+      <c r="V57" s="11" t="n">
+        <v>1.4648</v>
+      </c>
+      <c r="W57" s="11" t="n">
+        <v>1.4616</v>
+      </c>
+      <c r="X57" s="11" t="n">
+        <v>1.4583</v>
+      </c>
+      <c r="Y57" s="11" t="n">
+        <v>1.4546</v>
+      </c>
+      <c r="Z57" s="11" t="n">
+        <v>1.4504</v>
+      </c>
+      <c r="AA57" s="11" t="n">
+        <v>1.4457</v>
+      </c>
+      <c r="AB57" s="11" t="n">
+        <v>1.4403</v>
+      </c>
+      <c r="AC57" s="11" t="n">
+        <v>1.4343</v>
+      </c>
+      <c r="AD57" s="11" t="n">
+        <v>1.4277</v>
+      </c>
+      <c r="AE57" s="11" t="n">
+        <v>1.4209</v>
+      </c>
+      <c r="AF57" s="11" t="n">
+        <v>1.414</v>
+      </c>
+      <c r="AG57" s="11" t="n">
+        <v>1.407</v>
+      </c>
+      <c r="AH57" s="11" t="n">
+        <v>1.4002</v>
+      </c>
+      <c r="AI57" s="11" t="n">
+        <v>1.3936</v>
+      </c>
+      <c r="AJ57" s="11" t="n">
+        <v>1.3873</v>
+      </c>
+      <c r="AK57" s="11" t="n">
+        <v>1.3814</v>
+      </c>
+      <c r="AL57" s="11" t="n">
+        <v>1.3759</v>
+      </c>
+      <c r="AM57" s="11" t="n">
+        <v>1.3709</v>
+      </c>
+      <c r="AN57" s="11" t="n">
+        <v>1.3665</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>5.6572</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>5.6452</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>5.7836</v>
+      </c>
+      <c r="G58" s="11" t="n">
+        <v>5.6514</v>
+      </c>
+      <c r="H58" s="11" t="n">
+        <v>5.5661</v>
+      </c>
+      <c r="I58" s="11" t="n">
+        <v>5.4773</v>
+      </c>
+      <c r="J58" s="11" t="n">
+        <v>5.3848</v>
+      </c>
+      <c r="K58" s="11" t="n">
+        <v>5.2555</v>
+      </c>
+      <c r="L58" s="11" t="n">
+        <v>5.152</v>
+      </c>
+      <c r="M58" s="11" t="n">
+        <v>5.0741</v>
+      </c>
+      <c r="N58" s="11" t="n">
+        <v>5.022</v>
+      </c>
+      <c r="O58" s="11" t="n">
+        <v>4.9957</v>
+      </c>
+      <c r="P58" s="11" t="n">
+        <v>4.995</v>
+      </c>
+      <c r="Q58" s="11" t="n">
+        <v>4.8705</v>
+      </c>
+      <c r="R58" s="11" t="n">
+        <v>4.7704</v>
+      </c>
+      <c r="S58" s="11" t="n">
+        <v>4.6946</v>
+      </c>
+      <c r="T58" s="11" t="n">
+        <v>4.6432</v>
+      </c>
+      <c r="U58" s="11" t="n">
+        <v>4.6162</v>
+      </c>
+      <c r="V58" s="11" t="n">
+        <v>4.6135</v>
+      </c>
+      <c r="W58" s="11" t="n">
+        <v>4.6352</v>
+      </c>
+      <c r="X58" s="11" t="n">
+        <v>4.6812</v>
+      </c>
+      <c r="Y58" s="11" t="n">
+        <v>4.7516</v>
+      </c>
+      <c r="Z58" s="11" t="n">
+        <v>4.8464</v>
+      </c>
+      <c r="AA58" s="11" t="n">
+        <v>4.9655</v>
+      </c>
+      <c r="AB58" s="11" t="n">
+        <v>5.1091</v>
+      </c>
+      <c r="AC58" s="11" t="n">
+        <v>5.2182</v>
+      </c>
+      <c r="AD58" s="11" t="n">
+        <v>5.3129</v>
+      </c>
+      <c r="AE58" s="11" t="n">
+        <v>5.3929</v>
+      </c>
+      <c r="AF58" s="11" t="n">
+        <v>5.4584</v>
+      </c>
+      <c r="AG58" s="11" t="n">
+        <v>5.5094</v>
+      </c>
+      <c r="AH58" s="11" t="n">
+        <v>5.5458</v>
+      </c>
+      <c r="AI58" s="11" t="n">
+        <v>5.5676</v>
+      </c>
+      <c r="AJ58" s="11" t="n">
+        <v>5.5749</v>
+      </c>
+      <c r="AK58" s="11" t="n">
+        <v>5.5676</v>
+      </c>
+      <c r="AL58" s="11" t="n">
+        <v>5.5458</v>
+      </c>
+      <c r="AM58" s="11" t="n">
+        <v>5.5094</v>
+      </c>
+      <c r="AN58" s="11" t="n">
+        <v>5.4584</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>5.6572</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>5.5985</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>5.6677</v>
+      </c>
+      <c r="G59" s="11" t="n">
+        <v>5.6918</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>5.6711</v>
+      </c>
+      <c r="I59" s="11" t="n">
+        <v>5.6413</v>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>5.6063</v>
+      </c>
+      <c r="K59" s="11" t="n">
+        <v>5.5651</v>
+      </c>
+      <c r="L59" s="11" t="n">
+        <v>5.5197</v>
+      </c>
+      <c r="M59" s="11" t="n">
+        <v>5.4743</v>
+      </c>
+      <c r="N59" s="11" t="n">
+        <v>5.4314</v>
+      </c>
+      <c r="O59" s="11" t="n">
+        <v>5.3928</v>
+      </c>
+      <c r="P59" s="11" t="n">
+        <v>5.3595</v>
+      </c>
+      <c r="Q59" s="11" t="n">
+        <v>5.3265</v>
+      </c>
+      <c r="R59" s="11" t="n">
+        <v>5.2902</v>
+      </c>
+      <c r="S59" s="11" t="n">
+        <v>5.2529</v>
+      </c>
+      <c r="T59" s="11" t="n">
+        <v>5.2163</v>
+      </c>
+      <c r="U59" s="11" t="n">
+        <v>5.1817</v>
+      </c>
+      <c r="V59" s="11" t="n">
+        <v>5.1501</v>
+      </c>
+      <c r="W59" s="11" t="n">
+        <v>5.1223</v>
+      </c>
+      <c r="X59" s="11" t="n">
+        <v>5.099</v>
+      </c>
+      <c r="Y59" s="11" t="n">
+        <v>5.0807</v>
+      </c>
+      <c r="Z59" s="11" t="n">
+        <v>5.0678</v>
+      </c>
+      <c r="AA59" s="11" t="n">
+        <v>5.0607</v>
+      </c>
+      <c r="AB59" s="11" t="n">
+        <v>5.0596</v>
+      </c>
+      <c r="AC59" s="11" t="n">
+        <v>5.0638</v>
+      </c>
+      <c r="AD59" s="11" t="n">
+        <v>5.0716</v>
+      </c>
+      <c r="AE59" s="11" t="n">
+        <v>5.0821</v>
+      </c>
+      <c r="AF59" s="11" t="n">
+        <v>5.0944</v>
+      </c>
+      <c r="AG59" s="11" t="n">
+        <v>5.1079</v>
+      </c>
+      <c r="AH59" s="11" t="n">
+        <v>5.1219</v>
+      </c>
+      <c r="AI59" s="11" t="n">
+        <v>5.136</v>
+      </c>
+      <c r="AJ59" s="11" t="n">
+        <v>5.1496</v>
+      </c>
+      <c r="AK59" s="11" t="n">
+        <v>5.1624</v>
+      </c>
+      <c r="AL59" s="11" t="n">
+        <v>5.1741</v>
+      </c>
+      <c r="AM59" s="11" t="n">
+        <v>5.1842</v>
+      </c>
+      <c r="AN59" s="11" t="n">
+        <v>5.1925</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>2.6459</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>2.5557</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>2.4745</v>
+      </c>
+      <c r="G60" s="11" t="n">
+        <v>2.5141</v>
+      </c>
+      <c r="H60" s="11" t="n">
+        <v>2.5937</v>
+      </c>
+      <c r="I60" s="11" t="n">
+        <v>2.5529</v>
+      </c>
+      <c r="J60" s="11" t="n">
+        <v>2.3919</v>
+      </c>
+      <c r="K60" s="11" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="L60" s="11" t="n">
+        <v>2.0694</v>
+      </c>
+      <c r="M60" s="11" t="n">
+        <v>1.9987</v>
+      </c>
+      <c r="N60" s="11" t="n">
+        <v>1.9882</v>
+      </c>
+      <c r="O60" s="11" t="n">
+        <v>2.0381</v>
+      </c>
+      <c r="P60" s="11" t="n">
+        <v>2.1482</v>
+      </c>
+      <c r="Q60" s="11" t="n">
+        <v>2.1792</v>
+      </c>
+      <c r="R60" s="11" t="n">
+        <v>2.207</v>
+      </c>
+      <c r="S60" s="11" t="n">
+        <v>2.2315</v>
+      </c>
+      <c r="T60" s="11" t="n">
+        <v>2.2528</v>
+      </c>
+      <c r="U60" s="11" t="n">
+        <v>2.2709</v>
+      </c>
+      <c r="V60" s="11" t="n">
+        <v>2.2857</v>
+      </c>
+      <c r="W60" s="11" t="n">
+        <v>2.2974</v>
+      </c>
+      <c r="X60" s="11" t="n">
+        <v>2.3058</v>
+      </c>
+      <c r="Y60" s="11" t="n">
+        <v>2.311</v>
+      </c>
+      <c r="Z60" s="11" t="n">
+        <v>2.313</v>
+      </c>
+      <c r="AA60" s="11" t="n">
+        <v>2.3117</v>
+      </c>
+      <c r="AB60" s="11" t="n">
+        <v>2.3072</v>
+      </c>
+      <c r="AC60" s="11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD60" s="11" t="n">
+        <v>2.3311</v>
+      </c>
+      <c r="AE60" s="11" t="n">
+        <v>2.3404</v>
+      </c>
+      <c r="AF60" s="11" t="n">
+        <v>2.3481</v>
+      </c>
+      <c r="AG60" s="11" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="AH60" s="11" t="n">
+        <v>2.3583</v>
+      </c>
+      <c r="AI60" s="11" t="n">
+        <v>2.3608</v>
+      </c>
+      <c r="AJ60" s="11" t="n">
+        <v>2.3617</v>
+      </c>
+      <c r="AK60" s="11" t="n">
+        <v>2.3608</v>
+      </c>
+      <c r="AL60" s="11" t="n">
+        <v>2.3583</v>
+      </c>
+      <c r="AM60" s="11" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="AN60" s="11" t="n">
+        <v>2.3481</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>2.6459</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>2.5863</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>2.5457</v>
+      </c>
+      <c r="G61" s="11" t="n">
+        <v>2.5252</v>
+      </c>
+      <c r="H61" s="11" t="n">
+        <v>2.5349</v>
+      </c>
+      <c r="I61" s="11" t="n">
+        <v>2.5446</v>
+      </c>
+      <c r="J61" s="11" t="n">
+        <v>2.5342</v>
+      </c>
+      <c r="K61" s="11" t="n">
+        <v>2.4995</v>
+      </c>
+      <c r="L61" s="11" t="n">
+        <v>2.4533</v>
+      </c>
+      <c r="M61" s="11" t="n">
+        <v>2.4061</v>
+      </c>
+      <c r="N61" s="11" t="n">
+        <v>2.3644</v>
+      </c>
+      <c r="O61" s="11" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="P61" s="11" t="n">
+        <v>2.3117</v>
+      </c>
+      <c r="Q61" s="11" t="n">
+        <v>2.3003</v>
+      </c>
+      <c r="R61" s="11" t="n">
+        <v>2.2927</v>
+      </c>
+      <c r="S61" s="11" t="n">
+        <v>2.2878</v>
+      </c>
+      <c r="T61" s="11" t="n">
+        <v>2.2849</v>
+      </c>
+      <c r="U61" s="11" t="n">
+        <v>2.2836</v>
+      </c>
+      <c r="V61" s="11" t="n">
+        <v>2.2833</v>
+      </c>
+      <c r="W61" s="11" t="n">
+        <v>2.2838</v>
+      </c>
+      <c r="X61" s="11" t="n">
+        <v>2.2847</v>
+      </c>
+      <c r="Y61" s="11" t="n">
+        <v>2.2858</v>
+      </c>
+      <c r="Z61" s="11" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AA61" s="11" t="n">
+        <v>2.2881</v>
+      </c>
+      <c r="AB61" s="11" t="n">
+        <v>2.289</v>
+      </c>
+      <c r="AC61" s="11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD61" s="11" t="n">
+        <v>2.2914</v>
+      </c>
+      <c r="AE61" s="11" t="n">
+        <v>2.293</v>
+      </c>
+      <c r="AF61" s="11" t="n">
+        <v>2.2949</v>
+      </c>
+      <c r="AG61" s="11" t="n">
+        <v>2.2968</v>
+      </c>
+      <c r="AH61" s="11" t="n">
+        <v>2.2988</v>
+      </c>
+      <c r="AI61" s="11" t="n">
+        <v>2.3008</v>
+      </c>
+      <c r="AJ61" s="11" t="n">
+        <v>2.3027</v>
+      </c>
+      <c r="AK61" s="11" t="n">
+        <v>2.3044</v>
+      </c>
+      <c r="AL61" s="11" t="n">
+        <v>2.3061</v>
+      </c>
+      <c r="AM61" s="11" t="n">
+        <v>2.3075</v>
+      </c>
+      <c r="AN61" s="11" t="n">
+        <v>2.3087</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN55"/>
+  <autoFilter ref="A1:AN61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37376,7 +38212,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-05  (9 daily snapshots, 54 curve rows)</t>
+          <t>2026-08-28 to 2026-09-06  (10 daily snapshots, 60 curve rows)</t>
         </is>
       </c>
     </row>
@@ -37448,7 +38284,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-04  (14 rows)</t>
+          <t>2026-08-22 to 2026-09-05  (15 rows)</t>
         </is>
       </c>
     </row>
@@ -37472,7 +38308,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-05  (14 rows)</t>
+          <t>2026-08-23 to 2026-09-06  (15 rows)</t>
         </is>
       </c>
     </row>
@@ -37484,7 +38320,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-06 05:58 local</t>
+          <t>2026-09-06 18:24 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,9 +16,9 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
   </definedNames>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$16</f>
+              <f>'Daily Index'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$16</f>
+              <f>'Daily Index'!$B$2:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$16</f>
+              <f>'Daily Index'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$16</f>
+              <f>'Daily Index'!$C$2:$C$17</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$16</f>
+              <f>'Daily Index'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$16</f>
+              <f>'Daily Index'!$D$2:$D$17</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$16</f>
+              <f>'GPU Rental'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$16</f>
+              <f>'GPU Rental'!$B$2:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$16</f>
+              <f>'GPU Rental'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$16</f>
+              <f>'GPU Rental'!$C$2:$C$17</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$16</f>
+              <f>'GPU Rental'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$16</f>
+              <f>'GPU Rental'!$D$2:$D$17</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$16</f>
+              <f>'GPU Rental'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$16</f>
+              <f>'GPU Rental'!$E$2:$E$17</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$16</f>
+              <f>'GPU Rental'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$16</f>
+              <f>'GPU Rental'!$F$2:$F$17</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$16</f>
+              <f>'GPU Rental'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$16</f>
+              <f>'GPU Rental'!$G$2:$G$17</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$16</f>
+              <f>'GPU Rental'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$16</f>
+              <f>'GPU Rental'!$H$2:$H$17</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1428,8 +1428,34 @@
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>0.5374</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>1.9319</v>
+      </c>
+      <c r="E17" s="4">
+        <f>IF(OR(B17="",B16=""),"",B17/B16-1)</f>
+        <v/>
+      </c>
+      <c r="F17" s="4">
+        <f>IF(OR(C17="",C16=""),"",C17/C16-1)</f>
+        <v/>
+      </c>
+      <c r="G17" s="4">
+        <f>IF(OR(D17="",D16=""),"",D17/D16-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:G17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1440,7 +1466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2319,8 +2345,62 @@
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I17" s="4">
+        <f>IF(OR(B17="",B16=""),"",B17/B16-1)</f>
+        <v/>
+      </c>
+      <c r="J17" s="4">
+        <f>IF(OR(C17="",C16=""),"",C17/C16-1)</f>
+        <v/>
+      </c>
+      <c r="K17" s="4">
+        <f>IF(OR(D17="",D16=""),"",D17/D16-1)</f>
+        <v/>
+      </c>
+      <c r="L17" s="4">
+        <f>IF(OR(E17="",E16=""),"",E17/E16-1)</f>
+        <v/>
+      </c>
+      <c r="M17" s="4">
+        <f>IF(OR(F17="",F16=""),"",F17/F16-1)</f>
+        <v/>
+      </c>
+      <c r="N17" s="4">
+        <f>IF(OR(G17="",G16=""),"",G17/G16-1)</f>
+        <v/>
+      </c>
+      <c r="O17" s="4">
+        <f>IF(OR(H17="",H16=""),"",H17/H16-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O16"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2331,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN61"/>
+  <dimension ref="A1:AN67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10138,8 +10218,764 @@
         <v>2.3087</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="10" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>1.5905</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>1.5831</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>1.7093</v>
+      </c>
+      <c r="G62" s="11" t="n">
+        <v>1.6291</v>
+      </c>
+      <c r="H62" s="11" t="n">
+        <v>1.5825</v>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>1.5376</v>
+      </c>
+      <c r="J62" s="11" t="n">
+        <v>1.4945</v>
+      </c>
+      <c r="K62" s="11" t="n">
+        <v>1.4169</v>
+      </c>
+      <c r="L62" s="11" t="n">
+        <v>1.3617</v>
+      </c>
+      <c r="M62" s="11" t="n">
+        <v>1.3289</v>
+      </c>
+      <c r="N62" s="11" t="n">
+        <v>1.3186</v>
+      </c>
+      <c r="O62" s="11" t="n">
+        <v>1.3307</v>
+      </c>
+      <c r="P62" s="11" t="n">
+        <v>1.3653</v>
+      </c>
+      <c r="Q62" s="11" t="n">
+        <v>1.3792</v>
+      </c>
+      <c r="R62" s="11" t="n">
+        <v>1.3894</v>
+      </c>
+      <c r="S62" s="11" t="n">
+        <v>1.3959</v>
+      </c>
+      <c r="T62" s="11" t="n">
+        <v>1.3987</v>
+      </c>
+      <c r="U62" s="11" t="n">
+        <v>1.3977</v>
+      </c>
+      <c r="V62" s="11" t="n">
+        <v>1.3931</v>
+      </c>
+      <c r="W62" s="11" t="n">
+        <v>1.3847</v>
+      </c>
+      <c r="X62" s="11" t="n">
+        <v>1.3726</v>
+      </c>
+      <c r="Y62" s="11" t="n">
+        <v>1.3568</v>
+      </c>
+      <c r="Z62" s="11" t="n">
+        <v>1.3372</v>
+      </c>
+      <c r="AA62" s="11" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="AB62" s="11" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="AC62" s="11" t="n">
+        <v>1.2608</v>
+      </c>
+      <c r="AD62" s="11" t="n">
+        <v>1.2381</v>
+      </c>
+      <c r="AE62" s="11" t="n">
+        <v>1.2189</v>
+      </c>
+      <c r="AF62" s="11" t="n">
+        <v>1.2032</v>
+      </c>
+      <c r="AG62" s="11" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="AH62" s="11" t="n">
+        <v>1.1823</v>
+      </c>
+      <c r="AI62" s="11" t="n">
+        <v>1.1771</v>
+      </c>
+      <c r="AJ62" s="11" t="n">
+        <v>1.1753</v>
+      </c>
+      <c r="AK62" s="11" t="n">
+        <v>1.1771</v>
+      </c>
+      <c r="AL62" s="11" t="n">
+        <v>1.1823</v>
+      </c>
+      <c r="AM62" s="11" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="AN62" s="11" t="n">
+        <v>1.2032</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>1.5905</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>1.5372</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>1.6003</v>
+      </c>
+      <c r="G63" s="11" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="H63" s="11" t="n">
+        <v>1.6232</v>
+      </c>
+      <c r="I63" s="11" t="n">
+        <v>1.6105</v>
+      </c>
+      <c r="J63" s="11" t="n">
+        <v>1.5948</v>
+      </c>
+      <c r="K63" s="11" t="n">
+        <v>1.5746</v>
+      </c>
+      <c r="L63" s="11" t="n">
+        <v>1.5512</v>
+      </c>
+      <c r="M63" s="11" t="n">
+        <v>1.5281</v>
+      </c>
+      <c r="N63" s="11" t="n">
+        <v>1.5075</v>
+      </c>
+      <c r="O63" s="11" t="n">
+        <v>1.4907</v>
+      </c>
+      <c r="P63" s="11" t="n">
+        <v>1.4787</v>
+      </c>
+      <c r="Q63" s="11" t="n">
+        <v>1.4705</v>
+      </c>
+      <c r="R63" s="11" t="n">
+        <v>1.4644</v>
+      </c>
+      <c r="S63" s="11" t="n">
+        <v>1.4596</v>
+      </c>
+      <c r="T63" s="11" t="n">
+        <v>1.4557</v>
+      </c>
+      <c r="U63" s="11" t="n">
+        <v>1.4524</v>
+      </c>
+      <c r="V63" s="11" t="n">
+        <v>1.4492</v>
+      </c>
+      <c r="W63" s="11" t="n">
+        <v>1.4461</v>
+      </c>
+      <c r="X63" s="11" t="n">
+        <v>1.4427</v>
+      </c>
+      <c r="Y63" s="11" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="Z63" s="11" t="n">
+        <v>1.4348</v>
+      </c>
+      <c r="AA63" s="11" t="n">
+        <v>1.4301</v>
+      </c>
+      <c r="AB63" s="11" t="n">
+        <v>1.4247</v>
+      </c>
+      <c r="AC63" s="11" t="n">
+        <v>1.4187</v>
+      </c>
+      <c r="AD63" s="11" t="n">
+        <v>1.4122</v>
+      </c>
+      <c r="AE63" s="11" t="n">
+        <v>1.4053</v>
+      </c>
+      <c r="AF63" s="11" t="n">
+        <v>1.3984</v>
+      </c>
+      <c r="AG63" s="11" t="n">
+        <v>1.3914</v>
+      </c>
+      <c r="AH63" s="11" t="n">
+        <v>1.3846</v>
+      </c>
+      <c r="AI63" s="11" t="n">
+        <v>1.378</v>
+      </c>
+      <c r="AJ63" s="11" t="n">
+        <v>1.3717</v>
+      </c>
+      <c r="AK63" s="11" t="n">
+        <v>1.3657</v>
+      </c>
+      <c r="AL63" s="11" t="n">
+        <v>1.3603</v>
+      </c>
+      <c r="AM63" s="11" t="n">
+        <v>1.3553</v>
+      </c>
+      <c r="AN63" s="11" t="n">
+        <v>1.3509</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>5.6931</v>
+      </c>
+      <c r="E64" s="11" t="n">
+        <v>5.6916</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>5.8148</v>
+      </c>
+      <c r="G64" s="11" t="n">
+        <v>5.6783</v>
+      </c>
+      <c r="H64" s="11" t="n">
+        <v>5.5812</v>
+      </c>
+      <c r="I64" s="11" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="J64" s="11" t="n">
+        <v>5.4106</v>
+      </c>
+      <c r="K64" s="11" t="n">
+        <v>5.2924</v>
+      </c>
+      <c r="L64" s="11" t="n">
+        <v>5.1961</v>
+      </c>
+      <c r="M64" s="11" t="n">
+        <v>5.1218</v>
+      </c>
+      <c r="N64" s="11" t="n">
+        <v>5.0694</v>
+      </c>
+      <c r="O64" s="11" t="n">
+        <v>5.0389</v>
+      </c>
+      <c r="P64" s="11" t="n">
+        <v>5.0304</v>
+      </c>
+      <c r="Q64" s="11" t="n">
+        <v>4.8989</v>
+      </c>
+      <c r="R64" s="11" t="n">
+        <v>4.7931</v>
+      </c>
+      <c r="S64" s="11" t="n">
+        <v>4.713</v>
+      </c>
+      <c r="T64" s="11" t="n">
+        <v>4.6587</v>
+      </c>
+      <c r="U64" s="11" t="n">
+        <v>4.6302</v>
+      </c>
+      <c r="V64" s="11" t="n">
+        <v>4.6273</v>
+      </c>
+      <c r="W64" s="11" t="n">
+        <v>4.6503</v>
+      </c>
+      <c r="X64" s="11" t="n">
+        <v>4.6989</v>
+      </c>
+      <c r="Y64" s="11" t="n">
+        <v>4.7733</v>
+      </c>
+      <c r="Z64" s="11" t="n">
+        <v>4.8735</v>
+      </c>
+      <c r="AA64" s="11" t="n">
+        <v>4.9994</v>
+      </c>
+      <c r="AB64" s="11" t="n">
+        <v>5.151</v>
+      </c>
+      <c r="AC64" s="11" t="n">
+        <v>5.2664</v>
+      </c>
+      <c r="AD64" s="11" t="n">
+        <v>5.3664</v>
+      </c>
+      <c r="AE64" s="11" t="n">
+        <v>5.451</v>
+      </c>
+      <c r="AF64" s="11" t="n">
+        <v>5.5202</v>
+      </c>
+      <c r="AG64" s="11" t="n">
+        <v>5.5741</v>
+      </c>
+      <c r="AH64" s="11" t="n">
+        <v>5.6125</v>
+      </c>
+      <c r="AI64" s="11" t="n">
+        <v>5.6356</v>
+      </c>
+      <c r="AJ64" s="11" t="n">
+        <v>5.6433</v>
+      </c>
+      <c r="AK64" s="11" t="n">
+        <v>5.6356</v>
+      </c>
+      <c r="AL64" s="11" t="n">
+        <v>5.6125</v>
+      </c>
+      <c r="AM64" s="11" t="n">
+        <v>5.5741</v>
+      </c>
+      <c r="AN64" s="11" t="n">
+        <v>5.5202</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>5.6931</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>5.6517</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>5.7133</v>
+      </c>
+      <c r="G65" s="11" t="n">
+        <v>5.7316</v>
+      </c>
+      <c r="H65" s="11" t="n">
+        <v>5.706</v>
+      </c>
+      <c r="I65" s="11" t="n">
+        <v>5.672</v>
+      </c>
+      <c r="J65" s="11" t="n">
+        <v>5.6351</v>
+      </c>
+      <c r="K65" s="11" t="n">
+        <v>5.5943</v>
+      </c>
+      <c r="L65" s="11" t="n">
+        <v>5.5503</v>
+      </c>
+      <c r="M65" s="11" t="n">
+        <v>5.5066</v>
+      </c>
+      <c r="N65" s="11" t="n">
+        <v>5.4653</v>
+      </c>
+      <c r="O65" s="11" t="n">
+        <v>5.4278</v>
+      </c>
+      <c r="P65" s="11" t="n">
+        <v>5.3949</v>
+      </c>
+      <c r="Q65" s="11" t="n">
+        <v>5.3616</v>
+      </c>
+      <c r="R65" s="11" t="n">
+        <v>5.3246</v>
+      </c>
+      <c r="S65" s="11" t="n">
+        <v>5.2864</v>
+      </c>
+      <c r="T65" s="11" t="n">
+        <v>5.2487</v>
+      </c>
+      <c r="U65" s="11" t="n">
+        <v>5.2131</v>
+      </c>
+      <c r="V65" s="11" t="n">
+        <v>5.1805</v>
+      </c>
+      <c r="W65" s="11" t="n">
+        <v>5.1519</v>
+      </c>
+      <c r="X65" s="11" t="n">
+        <v>5.1279</v>
+      </c>
+      <c r="Y65" s="11" t="n">
+        <v>5.1091</v>
+      </c>
+      <c r="Z65" s="11" t="n">
+        <v>5.096</v>
+      </c>
+      <c r="AA65" s="11" t="n">
+        <v>5.089</v>
+      </c>
+      <c r="AB65" s="11" t="n">
+        <v>5.0883</v>
+      </c>
+      <c r="AC65" s="11" t="n">
+        <v>5.0932</v>
+      </c>
+      <c r="AD65" s="11" t="n">
+        <v>5.1018</v>
+      </c>
+      <c r="AE65" s="11" t="n">
+        <v>5.1133</v>
+      </c>
+      <c r="AF65" s="11" t="n">
+        <v>5.1266</v>
+      </c>
+      <c r="AG65" s="11" t="n">
+        <v>5.1411</v>
+      </c>
+      <c r="AH65" s="11" t="n">
+        <v>5.1563</v>
+      </c>
+      <c r="AI65" s="11" t="n">
+        <v>5.1714</v>
+      </c>
+      <c r="AJ65" s="11" t="n">
+        <v>5.1861</v>
+      </c>
+      <c r="AK65" s="11" t="n">
+        <v>5.1998</v>
+      </c>
+      <c r="AL65" s="11" t="n">
+        <v>5.2123</v>
+      </c>
+      <c r="AM65" s="11" t="n">
+        <v>5.2233</v>
+      </c>
+      <c r="AN65" s="11" t="n">
+        <v>5.2323</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="E66" s="11" t="n">
+        <v>2.5477</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>2.4614</v>
+      </c>
+      <c r="G66" s="11" t="n">
+        <v>2.5028</v>
+      </c>
+      <c r="H66" s="11" t="n">
+        <v>2.5835</v>
+      </c>
+      <c r="I66" s="11" t="n">
+        <v>2.5431</v>
+      </c>
+      <c r="J66" s="11" t="n">
+        <v>2.3818</v>
+      </c>
+      <c r="K66" s="11" t="n">
+        <v>2.1909</v>
+      </c>
+      <c r="L66" s="11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M66" s="11" t="n">
+        <v>1.9892</v>
+      </c>
+      <c r="N66" s="11" t="n">
+        <v>1.9785</v>
+      </c>
+      <c r="O66" s="11" t="n">
+        <v>2.0278</v>
+      </c>
+      <c r="P66" s="11" t="n">
+        <v>2.1372</v>
+      </c>
+      <c r="Q66" s="11" t="n">
+        <v>2.1675</v>
+      </c>
+      <c r="R66" s="11" t="n">
+        <v>2.1947</v>
+      </c>
+      <c r="S66" s="11" t="n">
+        <v>2.2187</v>
+      </c>
+      <c r="T66" s="11" t="n">
+        <v>2.2396</v>
+      </c>
+      <c r="U66" s="11" t="n">
+        <v>2.2573</v>
+      </c>
+      <c r="V66" s="11" t="n">
+        <v>2.2718</v>
+      </c>
+      <c r="W66" s="11" t="n">
+        <v>2.2833</v>
+      </c>
+      <c r="X66" s="11" t="n">
+        <v>2.2915</v>
+      </c>
+      <c r="Y66" s="11" t="n">
+        <v>2.2967</v>
+      </c>
+      <c r="Z66" s="11" t="n">
+        <v>2.2987</v>
+      </c>
+      <c r="AA66" s="11" t="n">
+        <v>2.2975</v>
+      </c>
+      <c r="AB66" s="11" t="n">
+        <v>2.2932</v>
+      </c>
+      <c r="AC66" s="11" t="n">
+        <v>2.3058</v>
+      </c>
+      <c r="AD66" s="11" t="n">
+        <v>2.3166</v>
+      </c>
+      <c r="AE66" s="11" t="n">
+        <v>2.3259</v>
+      </c>
+      <c r="AF66" s="11" t="n">
+        <v>2.3334</v>
+      </c>
+      <c r="AG66" s="11" t="n">
+        <v>2.3393</v>
+      </c>
+      <c r="AH66" s="11" t="n">
+        <v>2.3435</v>
+      </c>
+      <c r="AI66" s="11" t="n">
+        <v>2.346</v>
+      </c>
+      <c r="AJ66" s="11" t="n">
+        <v>2.3468</v>
+      </c>
+      <c r="AK66" s="11" t="n">
+        <v>2.346</v>
+      </c>
+      <c r="AL66" s="11" t="n">
+        <v>2.3435</v>
+      </c>
+      <c r="AM66" s="11" t="n">
+        <v>2.3393</v>
+      </c>
+      <c r="AN66" s="11" t="n">
+        <v>2.3334</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>2.5802</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="G67" s="11" t="n">
+        <v>2.5152</v>
+      </c>
+      <c r="H67" s="11" t="n">
+        <v>2.5247</v>
+      </c>
+      <c r="I67" s="11" t="n">
+        <v>2.5344</v>
+      </c>
+      <c r="J67" s="11" t="n">
+        <v>2.5241</v>
+      </c>
+      <c r="K67" s="11" t="n">
+        <v>2.4894</v>
+      </c>
+      <c r="L67" s="11" t="n">
+        <v>2.4433</v>
+      </c>
+      <c r="M67" s="11" t="n">
+        <v>2.3962</v>
+      </c>
+      <c r="N67" s="11" t="n">
+        <v>2.3545</v>
+      </c>
+      <c r="O67" s="11" t="n">
+        <v>2.3221</v>
+      </c>
+      <c r="P67" s="11" t="n">
+        <v>2.3017</v>
+      </c>
+      <c r="Q67" s="11" t="n">
+        <v>2.2902</v>
+      </c>
+      <c r="R67" s="11" t="n">
+        <v>2.2825</v>
+      </c>
+      <c r="S67" s="11" t="n">
+        <v>2.2774</v>
+      </c>
+      <c r="T67" s="11" t="n">
+        <v>2.2744</v>
+      </c>
+      <c r="U67" s="11" t="n">
+        <v>2.2729</v>
+      </c>
+      <c r="V67" s="11" t="n">
+        <v>2.2725</v>
+      </c>
+      <c r="W67" s="11" t="n">
+        <v>2.2727</v>
+      </c>
+      <c r="X67" s="11" t="n">
+        <v>2.2735</v>
+      </c>
+      <c r="Y67" s="11" t="n">
+        <v>2.2745</v>
+      </c>
+      <c r="Z67" s="11" t="n">
+        <v>2.2756</v>
+      </c>
+      <c r="AA67" s="11" t="n">
+        <v>2.2765</v>
+      </c>
+      <c r="AB67" s="11" t="n">
+        <v>2.2773</v>
+      </c>
+      <c r="AC67" s="11" t="n">
+        <v>2.2782</v>
+      </c>
+      <c r="AD67" s="11" t="n">
+        <v>2.2795</v>
+      </c>
+      <c r="AE67" s="11" t="n">
+        <v>2.2811</v>
+      </c>
+      <c r="AF67" s="11" t="n">
+        <v>2.2828</v>
+      </c>
+      <c r="AG67" s="11" t="n">
+        <v>2.2846</v>
+      </c>
+      <c r="AH67" s="11" t="n">
+        <v>2.2865</v>
+      </c>
+      <c r="AI67" s="11" t="n">
+        <v>2.2884</v>
+      </c>
+      <c r="AJ67" s="11" t="n">
+        <v>2.2902</v>
+      </c>
+      <c r="AK67" s="11" t="n">
+        <v>2.2919</v>
+      </c>
+      <c r="AL67" s="11" t="n">
+        <v>2.2935</v>
+      </c>
+      <c r="AM67" s="11" t="n">
+        <v>2.2949</v>
+      </c>
+      <c r="AN67" s="11" t="n">
+        <v>2.296</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN61"/>
+  <autoFilter ref="A1:AN67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -38212,7 +39048,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-06  (10 daily snapshots, 60 curve rows)</t>
+          <t>2026-08-28 to 2026-09-07  (11 daily snapshots, 66 curve rows)</t>
         </is>
       </c>
     </row>
@@ -38284,7 +39120,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-05  (15 rows)</t>
+          <t>2026-08-22 to 2026-09-06  (16 rows)</t>
         </is>
       </c>
     </row>
@@ -38308,7 +39144,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-06  (15 rows)</t>
+          <t>2026-08-23 to 2026-09-07  (16 rows)</t>
         </is>
       </c>
     </row>
@@ -38320,7 +39156,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-06 18:24 local</t>
+          <t>2026-09-07 20:00 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$17</f>
+              <f>'Daily Index'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$17</f>
+              <f>'Daily Index'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$17</f>
+              <f>'Daily Index'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$17</f>
+              <f>'Daily Index'!$C$2:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$17</f>
+              <f>'Daily Index'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$17</f>
+              <f>'Daily Index'!$D$2:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1454,8 +1454,30 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="4">
+        <f>IF(OR(B18="",B17=""),"",B18/B17-1)</f>
+        <v/>
+      </c>
+      <c r="F18" s="4">
+        <f>IF(OR(C18="",C17=""),"",C18/C17-1)</f>
+        <v/>
+      </c>
+      <c r="G18" s="4">
+        <f>IF(OR(D18="",D17=""),"",D18/D17-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39120,7 +39142,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-06  (16 rows)</t>
+          <t>2026-08-22 to 2026-09-07  (17 rows)</t>
         </is>
       </c>
     </row>
@@ -39156,7 +39178,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-07 20:00 local</t>
+          <t>2026-09-08 13:40 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
   </definedNames>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$17</f>
+              <f>'GPU Rental'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$17</f>
+              <f>'GPU Rental'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$17</f>
+              <f>'GPU Rental'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$17</f>
+              <f>'GPU Rental'!$C$2:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$17</f>
+              <f>'GPU Rental'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$17</f>
+              <f>'GPU Rental'!$D$2:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$17</f>
+              <f>'GPU Rental'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$17</f>
+              <f>'GPU Rental'!$E$2:$E$18</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$17</f>
+              <f>'GPU Rental'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$17</f>
+              <f>'GPU Rental'!$F$2:$F$18</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$17</f>
+              <f>'GPU Rental'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$17</f>
+              <f>'GPU Rental'!$G$2:$G$18</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$17</f>
+              <f>'GPU Rental'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$17</f>
+              <f>'GPU Rental'!$H$2:$H$18</f>
             </numRef>
           </val>
         </ser>
@@ -1488,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2421,8 +2421,62 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I18" s="4">
+        <f>IF(OR(B18="",B17=""),"",B18/B17-1)</f>
+        <v/>
+      </c>
+      <c r="J18" s="4">
+        <f>IF(OR(C18="",C17=""),"",C18/C17-1)</f>
+        <v/>
+      </c>
+      <c r="K18" s="4">
+        <f>IF(OR(D18="",D17=""),"",D18/D17-1)</f>
+        <v/>
+      </c>
+      <c r="L18" s="4">
+        <f>IF(OR(E18="",E17=""),"",E18/E17-1)</f>
+        <v/>
+      </c>
+      <c r="M18" s="4">
+        <f>IF(OR(F18="",F17=""),"",F18/F17-1)</f>
+        <v/>
+      </c>
+      <c r="N18" s="4">
+        <f>IF(OR(G18="",G17=""),"",G18/G17-1)</f>
+        <v/>
+      </c>
+      <c r="O18" s="4">
+        <f>IF(OR(H18="",H17=""),"",H18/H17-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2433,7 +2487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN67"/>
+  <dimension ref="A1:AN73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10996,8 +11050,764 @@
         <v>2.296</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="10" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>1.6099</v>
+      </c>
+      <c r="E68" s="11" t="n">
+        <v>1.6035</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>1.7208</v>
+      </c>
+      <c r="G68" s="11" t="n">
+        <v>1.6455</v>
+      </c>
+      <c r="H68" s="11" t="n">
+        <v>1.6028</v>
+      </c>
+      <c r="I68" s="11" t="n">
+        <v>1.5591</v>
+      </c>
+      <c r="J68" s="11" t="n">
+        <v>1.5143</v>
+      </c>
+      <c r="K68" s="11" t="n">
+        <v>1.436</v>
+      </c>
+      <c r="L68" s="11" t="n">
+        <v>1.3803</v>
+      </c>
+      <c r="M68" s="11" t="n">
+        <v>1.3475</v>
+      </c>
+      <c r="N68" s="11" t="n">
+        <v>1.3374</v>
+      </c>
+      <c r="O68" s="11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P68" s="11" t="n">
+        <v>1.3855</v>
+      </c>
+      <c r="Q68" s="11" t="n">
+        <v>1.4002</v>
+      </c>
+      <c r="R68" s="11" t="n">
+        <v>1.4111</v>
+      </c>
+      <c r="S68" s="11" t="n">
+        <v>1.4181</v>
+      </c>
+      <c r="T68" s="11" t="n">
+        <v>1.4213</v>
+      </c>
+      <c r="U68" s="11" t="n">
+        <v>1.4207</v>
+      </c>
+      <c r="V68" s="11" t="n">
+        <v>1.4162</v>
+      </c>
+      <c r="W68" s="11" t="n">
+        <v>1.4079</v>
+      </c>
+      <c r="X68" s="11" t="n">
+        <v>1.3957</v>
+      </c>
+      <c r="Y68" s="11" t="n">
+        <v>1.3797</v>
+      </c>
+      <c r="Z68" s="11" t="n">
+        <v>1.3598</v>
+      </c>
+      <c r="AA68" s="11" t="n">
+        <v>1.3361</v>
+      </c>
+      <c r="AB68" s="11" t="n">
+        <v>1.3085</v>
+      </c>
+      <c r="AC68" s="11" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="AD68" s="11" t="n">
+        <v>1.2592</v>
+      </c>
+      <c r="AE68" s="11" t="n">
+        <v>1.2398</v>
+      </c>
+      <c r="AF68" s="11" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="AG68" s="11" t="n">
+        <v>1.2116</v>
+      </c>
+      <c r="AH68" s="11" t="n">
+        <v>1.2028</v>
+      </c>
+      <c r="AI68" s="11" t="n">
+        <v>1.1975</v>
+      </c>
+      <c r="AJ68" s="11" t="n">
+        <v>1.1957</v>
+      </c>
+      <c r="AK68" s="11" t="n">
+        <v>1.1975</v>
+      </c>
+      <c r="AL68" s="11" t="n">
+        <v>1.2028</v>
+      </c>
+      <c r="AM68" s="11" t="n">
+        <v>1.2116</v>
+      </c>
+      <c r="AN68" s="11" t="n">
+        <v>1.2239</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>1.6099</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>1.5609</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>1.6195</v>
+      </c>
+      <c r="G69" s="11" t="n">
+        <v>1.6461</v>
+      </c>
+      <c r="H69" s="11" t="n">
+        <v>1.6406</v>
+      </c>
+      <c r="I69" s="11" t="n">
+        <v>1.6287</v>
+      </c>
+      <c r="J69" s="11" t="n">
+        <v>1.6134</v>
+      </c>
+      <c r="K69" s="11" t="n">
+        <v>1.5934</v>
+      </c>
+      <c r="L69" s="11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M69" s="11" t="n">
+        <v>1.5469</v>
+      </c>
+      <c r="N69" s="11" t="n">
+        <v>1.5262</v>
+      </c>
+      <c r="O69" s="11" t="n">
+        <v>1.5095</v>
+      </c>
+      <c r="P69" s="11" t="n">
+        <v>1.4975</v>
+      </c>
+      <c r="Q69" s="11" t="n">
+        <v>1.4895</v>
+      </c>
+      <c r="R69" s="11" t="n">
+        <v>1.4835</v>
+      </c>
+      <c r="S69" s="11" t="n">
+        <v>1.4789</v>
+      </c>
+      <c r="T69" s="11" t="n">
+        <v>1.4753</v>
+      </c>
+      <c r="U69" s="11" t="n">
+        <v>1.4721</v>
+      </c>
+      <c r="V69" s="11" t="n">
+        <v>1.4691</v>
+      </c>
+      <c r="W69" s="11" t="n">
+        <v>1.4661</v>
+      </c>
+      <c r="X69" s="11" t="n">
+        <v>1.4629</v>
+      </c>
+      <c r="Y69" s="11" t="n">
+        <v>1.4594</v>
+      </c>
+      <c r="Z69" s="11" t="n">
+        <v>1.4553</v>
+      </c>
+      <c r="AA69" s="11" t="n">
+        <v>1.4507</v>
+      </c>
+      <c r="AB69" s="11" t="n">
+        <v>1.4453</v>
+      </c>
+      <c r="AC69" s="11" t="n">
+        <v>1.4393</v>
+      </c>
+      <c r="AD69" s="11" t="n">
+        <v>1.4328</v>
+      </c>
+      <c r="AE69" s="11" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="AF69" s="11" t="n">
+        <v>1.4191</v>
+      </c>
+      <c r="AG69" s="11" t="n">
+        <v>1.4121</v>
+      </c>
+      <c r="AH69" s="11" t="n">
+        <v>1.4053</v>
+      </c>
+      <c r="AI69" s="11" t="n">
+        <v>1.3986</v>
+      </c>
+      <c r="AJ69" s="11" t="n">
+        <v>1.3923</v>
+      </c>
+      <c r="AK69" s="11" t="n">
+        <v>1.3864</v>
+      </c>
+      <c r="AL69" s="11" t="n">
+        <v>1.3809</v>
+      </c>
+      <c r="AM69" s="11" t="n">
+        <v>1.3759</v>
+      </c>
+      <c r="AN69" s="11" t="n">
+        <v>1.3715</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>5.6967</v>
+      </c>
+      <c r="E70" s="11" t="n">
+        <v>5.7047</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>5.838</v>
+      </c>
+      <c r="G70" s="11" t="n">
+        <v>5.6333</v>
+      </c>
+      <c r="H70" s="11" t="n">
+        <v>5.4364</v>
+      </c>
+      <c r="I70" s="11" t="n">
+        <v>5.3366</v>
+      </c>
+      <c r="J70" s="11" t="n">
+        <v>5.3339</v>
+      </c>
+      <c r="K70" s="11" t="n">
+        <v>5.2858</v>
+      </c>
+      <c r="L70" s="11" t="n">
+        <v>5.2356</v>
+      </c>
+      <c r="M70" s="11" t="n">
+        <v>5.1833</v>
+      </c>
+      <c r="N70" s="11" t="n">
+        <v>5.129</v>
+      </c>
+      <c r="O70" s="11" t="n">
+        <v>5.0726</v>
+      </c>
+      <c r="P70" s="11" t="n">
+        <v>5.0141</v>
+      </c>
+      <c r="Q70" s="11" t="n">
+        <v>4.8382</v>
+      </c>
+      <c r="R70" s="11" t="n">
+        <v>4.6967</v>
+      </c>
+      <c r="S70" s="11" t="n">
+        <v>4.5897</v>
+      </c>
+      <c r="T70" s="11" t="n">
+        <v>4.5171</v>
+      </c>
+      <c r="U70" s="11" t="n">
+        <v>4.479</v>
+      </c>
+      <c r="V70" s="11" t="n">
+        <v>4.4753</v>
+      </c>
+      <c r="W70" s="11" t="n">
+        <v>4.5061</v>
+      </c>
+      <c r="X70" s="11" t="n">
+        <v>4.5713</v>
+      </c>
+      <c r="Y70" s="11" t="n">
+        <v>4.6709</v>
+      </c>
+      <c r="Z70" s="11" t="n">
+        <v>4.805</v>
+      </c>
+      <c r="AA70" s="11" t="n">
+        <v>4.9736</v>
+      </c>
+      <c r="AB70" s="11" t="n">
+        <v>5.1766</v>
+      </c>
+      <c r="AC70" s="11" t="n">
+        <v>5.3311</v>
+      </c>
+      <c r="AD70" s="11" t="n">
+        <v>5.4651</v>
+      </c>
+      <c r="AE70" s="11" t="n">
+        <v>5.5784</v>
+      </c>
+      <c r="AF70" s="11" t="n">
+        <v>5.6711</v>
+      </c>
+      <c r="AG70" s="11" t="n">
+        <v>5.7433</v>
+      </c>
+      <c r="AH70" s="11" t="n">
+        <v>5.7948</v>
+      </c>
+      <c r="AI70" s="11" t="n">
+        <v>5.8257</v>
+      </c>
+      <c r="AJ70" s="11" t="n">
+        <v>5.836</v>
+      </c>
+      <c r="AK70" s="11" t="n">
+        <v>5.8257</v>
+      </c>
+      <c r="AL70" s="11" t="n">
+        <v>5.7948</v>
+      </c>
+      <c r="AM70" s="11" t="n">
+        <v>5.7433</v>
+      </c>
+      <c r="AN70" s="11" t="n">
+        <v>5.6711</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>5.6967</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>5.6662</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>5.7329</v>
+      </c>
+      <c r="G71" s="11" t="n">
+        <v>5.7432</v>
+      </c>
+      <c r="H71" s="11" t="n">
+        <v>5.6891</v>
+      </c>
+      <c r="I71" s="11" t="n">
+        <v>5.6269</v>
+      </c>
+      <c r="J71" s="11" t="n">
+        <v>5.577</v>
+      </c>
+      <c r="K71" s="11" t="n">
+        <v>5.5388</v>
+      </c>
+      <c r="L71" s="11" t="n">
+        <v>5.5041</v>
+      </c>
+      <c r="M71" s="11" t="n">
+        <v>5.4714</v>
+      </c>
+      <c r="N71" s="11" t="n">
+        <v>5.4399</v>
+      </c>
+      <c r="O71" s="11" t="n">
+        <v>5.4091</v>
+      </c>
+      <c r="P71" s="11" t="n">
+        <v>5.3786</v>
+      </c>
+      <c r="Q71" s="11" t="n">
+        <v>5.3436</v>
+      </c>
+      <c r="R71" s="11" t="n">
+        <v>5.3022</v>
+      </c>
+      <c r="S71" s="11" t="n">
+        <v>5.2581</v>
+      </c>
+      <c r="T71" s="11" t="n">
+        <v>5.2139</v>
+      </c>
+      <c r="U71" s="11" t="n">
+        <v>5.1716</v>
+      </c>
+      <c r="V71" s="11" t="n">
+        <v>5.1329</v>
+      </c>
+      <c r="W71" s="11" t="n">
+        <v>5.0989</v>
+      </c>
+      <c r="X71" s="11" t="n">
+        <v>5.0707</v>
+      </c>
+      <c r="Y71" s="11" t="n">
+        <v>5.0492</v>
+      </c>
+      <c r="Z71" s="11" t="n">
+        <v>5.0349</v>
+      </c>
+      <c r="AA71" s="11" t="n">
+        <v>5.0285</v>
+      </c>
+      <c r="AB71" s="11" t="n">
+        <v>5.0303</v>
+      </c>
+      <c r="AC71" s="11" t="n">
+        <v>5.0393</v>
+      </c>
+      <c r="AD71" s="11" t="n">
+        <v>5.0532</v>
+      </c>
+      <c r="AE71" s="11" t="n">
+        <v>5.0706</v>
+      </c>
+      <c r="AF71" s="11" t="n">
+        <v>5.0904</v>
+      </c>
+      <c r="AG71" s="11" t="n">
+        <v>5.1118</v>
+      </c>
+      <c r="AH71" s="11" t="n">
+        <v>5.1337</v>
+      </c>
+      <c r="AI71" s="11" t="n">
+        <v>5.1556</v>
+      </c>
+      <c r="AJ71" s="11" t="n">
+        <v>5.1768</v>
+      </c>
+      <c r="AK71" s="11" t="n">
+        <v>5.1966</v>
+      </c>
+      <c r="AL71" s="11" t="n">
+        <v>5.2147</v>
+      </c>
+      <c r="AM71" s="11" t="n">
+        <v>5.2306</v>
+      </c>
+      <c r="AN71" s="11" t="n">
+        <v>5.2439</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="n">
+        <v>2.6339</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>2.5815</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>2.442</v>
+      </c>
+      <c r="G72" s="11" t="n">
+        <v>2.5031</v>
+      </c>
+      <c r="H72" s="11" t="n">
+        <v>2.5963</v>
+      </c>
+      <c r="I72" s="11" t="n">
+        <v>2.5583</v>
+      </c>
+      <c r="J72" s="11" t="n">
+        <v>2.389</v>
+      </c>
+      <c r="K72" s="11" t="n">
+        <v>2.1936</v>
+      </c>
+      <c r="L72" s="11" t="n">
+        <v>2.0594</v>
+      </c>
+      <c r="M72" s="11" t="n">
+        <v>1.9864</v>
+      </c>
+      <c r="N72" s="11" t="n">
+        <v>1.9744</v>
+      </c>
+      <c r="O72" s="11" t="n">
+        <v>2.0237</v>
+      </c>
+      <c r="P72" s="11" t="n">
+        <v>2.1341</v>
+      </c>
+      <c r="Q72" s="11" t="n">
+        <v>2.1645</v>
+      </c>
+      <c r="R72" s="11" t="n">
+        <v>2.1915</v>
+      </c>
+      <c r="S72" s="11" t="n">
+        <v>2.2152</v>
+      </c>
+      <c r="T72" s="11" t="n">
+        <v>2.2356</v>
+      </c>
+      <c r="U72" s="11" t="n">
+        <v>2.2526</v>
+      </c>
+      <c r="V72" s="11" t="n">
+        <v>2.2662</v>
+      </c>
+      <c r="W72" s="11" t="n">
+        <v>2.2765</v>
+      </c>
+      <c r="X72" s="11" t="n">
+        <v>2.2834</v>
+      </c>
+      <c r="Y72" s="11" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="Z72" s="11" t="n">
+        <v>2.2873</v>
+      </c>
+      <c r="AA72" s="11" t="n">
+        <v>2.2841</v>
+      </c>
+      <c r="AB72" s="11" t="n">
+        <v>2.2777</v>
+      </c>
+      <c r="AC72" s="11" t="n">
+        <v>2.2875</v>
+      </c>
+      <c r="AD72" s="11" t="n">
+        <v>2.2961</v>
+      </c>
+      <c r="AE72" s="11" t="n">
+        <v>2.3033</v>
+      </c>
+      <c r="AF72" s="11" t="n">
+        <v>2.3093</v>
+      </c>
+      <c r="AG72" s="11" t="n">
+        <v>2.3139</v>
+      </c>
+      <c r="AH72" s="11" t="n">
+        <v>2.3172</v>
+      </c>
+      <c r="AI72" s="11" t="n">
+        <v>2.3191</v>
+      </c>
+      <c r="AJ72" s="11" t="n">
+        <v>2.3198</v>
+      </c>
+      <c r="AK72" s="11" t="n">
+        <v>2.3191</v>
+      </c>
+      <c r="AL72" s="11" t="n">
+        <v>2.3172</v>
+      </c>
+      <c r="AM72" s="11" t="n">
+        <v>2.3139</v>
+      </c>
+      <c r="AN72" s="11" t="n">
+        <v>2.3093</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="n">
+        <v>2.6339</v>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>2.6345</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>2.5648</v>
+      </c>
+      <c r="G73" s="11" t="n">
+        <v>2.5285</v>
+      </c>
+      <c r="H73" s="11" t="n">
+        <v>2.5365</v>
+      </c>
+      <c r="I73" s="11" t="n">
+        <v>2.5468</v>
+      </c>
+      <c r="J73" s="11" t="n">
+        <v>2.5365</v>
+      </c>
+      <c r="K73" s="11" t="n">
+        <v>2.5007</v>
+      </c>
+      <c r="L73" s="11" t="n">
+        <v>2.4533</v>
+      </c>
+      <c r="M73" s="11" t="n">
+        <v>2.4049</v>
+      </c>
+      <c r="N73" s="11" t="n">
+        <v>2.3619</v>
+      </c>
+      <c r="O73" s="11" t="n">
+        <v>2.3285</v>
+      </c>
+      <c r="P73" s="11" t="n">
+        <v>2.3073</v>
+      </c>
+      <c r="Q73" s="11" t="n">
+        <v>2.2951</v>
+      </c>
+      <c r="R73" s="11" t="n">
+        <v>2.2868</v>
+      </c>
+      <c r="S73" s="11" t="n">
+        <v>2.2812</v>
+      </c>
+      <c r="T73" s="11" t="n">
+        <v>2.2778</v>
+      </c>
+      <c r="U73" s="11" t="n">
+        <v>2.2758</v>
+      </c>
+      <c r="V73" s="11" t="n">
+        <v>2.2749</v>
+      </c>
+      <c r="W73" s="11" t="n">
+        <v>2.2747</v>
+      </c>
+      <c r="X73" s="11" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Y73" s="11" t="n">
+        <v>2.2755</v>
+      </c>
+      <c r="Z73" s="11" t="n">
+        <v>2.2761</v>
+      </c>
+      <c r="AA73" s="11" t="n">
+        <v>2.2765</v>
+      </c>
+      <c r="AB73" s="11" t="n">
+        <v>2.2767</v>
+      </c>
+      <c r="AC73" s="11" t="n">
+        <v>2.2769</v>
+      </c>
+      <c r="AD73" s="11" t="n">
+        <v>2.2775</v>
+      </c>
+      <c r="AE73" s="11" t="n">
+        <v>2.2783</v>
+      </c>
+      <c r="AF73" s="11" t="n">
+        <v>2.2793</v>
+      </c>
+      <c r="AG73" s="11" t="n">
+        <v>2.2804</v>
+      </c>
+      <c r="AH73" s="11" t="n">
+        <v>2.2816</v>
+      </c>
+      <c r="AI73" s="11" t="n">
+        <v>2.2828</v>
+      </c>
+      <c r="AJ73" s="11" t="n">
+        <v>2.2839</v>
+      </c>
+      <c r="AK73" s="11" t="n">
+        <v>2.285</v>
+      </c>
+      <c r="AL73" s="11" t="n">
+        <v>2.286</v>
+      </c>
+      <c r="AM73" s="11" t="n">
+        <v>2.2869</v>
+      </c>
+      <c r="AN73" s="11" t="n">
+        <v>2.2875</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN67"/>
+  <autoFilter ref="A1:AN73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39070,7 +39880,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-07  (11 daily snapshots, 66 curve rows)</t>
+          <t>2026-08-28 to 2026-09-08  (12 daily snapshots, 72 curve rows)</t>
         </is>
       </c>
     </row>
@@ -39166,7 +39976,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-07  (16 rows)</t>
+          <t>2026-08-23 to 2026-09-08  (17 rows)</t>
         </is>
       </c>
     </row>
@@ -39178,7 +39988,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-08 13:40 local</t>
+          <t>2026-09-08 19:27 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,10 +17,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$724</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$472</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$18</f>
+              <f>'GPU Rental'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$18</f>
+              <f>'GPU Rental'!$B$2:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$18</f>
+              <f>'GPU Rental'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$18</f>
+              <f>'GPU Rental'!$C$2:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$18</f>
+              <f>'GPU Rental'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$18</f>
+              <f>'GPU Rental'!$D$2:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$18</f>
+              <f>'GPU Rental'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$18</f>
+              <f>'GPU Rental'!$E$2:$E$19</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$18</f>
+              <f>'GPU Rental'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$18</f>
+              <f>'GPU Rental'!$F$2:$F$19</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$18</f>
+              <f>'GPU Rental'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$18</f>
+              <f>'GPU Rental'!$G$2:$G$19</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$18</f>
+              <f>'GPU Rental'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$18</f>
+              <f>'GPU Rental'!$H$2:$H$19</f>
             </numRef>
           </val>
         </ser>
@@ -1488,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2475,8 +2475,62 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I19" s="4">
+        <f>IF(OR(B19="",B18=""),"",B19/B18-1)</f>
+        <v/>
+      </c>
+      <c r="J19" s="4">
+        <f>IF(OR(C19="",C18=""),"",C19/C18-1)</f>
+        <v/>
+      </c>
+      <c r="K19" s="4">
+        <f>IF(OR(D19="",D18=""),"",D19/D18-1)</f>
+        <v/>
+      </c>
+      <c r="L19" s="4">
+        <f>IF(OR(E19="",E18=""),"",E19/E18-1)</f>
+        <v/>
+      </c>
+      <c r="M19" s="4">
+        <f>IF(OR(F19="",F18=""),"",F19/F18-1)</f>
+        <v/>
+      </c>
+      <c r="N19" s="4">
+        <f>IF(OR(G19="",G18=""),"",G19/G18-1)</f>
+        <v/>
+      </c>
+      <c r="O19" s="4">
+        <f>IF(OR(H19="",H18=""),"",H19/H18-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O18"/>
+  <autoFilter ref="A1:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2487,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN73"/>
+  <dimension ref="A1:AN79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11806,8 +11860,764 @@
         <v>2.2875</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="10" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="n">
+        <v>1.611</v>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>1.6127</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>1.7314</v>
+      </c>
+      <c r="G74" s="11" t="n">
+        <v>1.6542</v>
+      </c>
+      <c r="H74" s="11" t="n">
+        <v>1.6094</v>
+      </c>
+      <c r="I74" s="11" t="n">
+        <v>1.5651</v>
+      </c>
+      <c r="J74" s="11" t="n">
+        <v>1.5214</v>
+      </c>
+      <c r="K74" s="11" t="n">
+        <v>1.4437</v>
+      </c>
+      <c r="L74" s="11" t="n">
+        <v>1.3885</v>
+      </c>
+      <c r="M74" s="11" t="n">
+        <v>1.3557</v>
+      </c>
+      <c r="N74" s="11" t="n">
+        <v>1.3454</v>
+      </c>
+      <c r="O74" s="11" t="n">
+        <v>1.3575</v>
+      </c>
+      <c r="P74" s="11" t="n">
+        <v>1.3922</v>
+      </c>
+      <c r="Q74" s="11" t="n">
+        <v>1.4061</v>
+      </c>
+      <c r="R74" s="11" t="n">
+        <v>1.4163</v>
+      </c>
+      <c r="S74" s="11" t="n">
+        <v>1.4228</v>
+      </c>
+      <c r="T74" s="11" t="n">
+        <v>1.4256</v>
+      </c>
+      <c r="U74" s="11" t="n">
+        <v>1.4246</v>
+      </c>
+      <c r="V74" s="11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W74" s="11" t="n">
+        <v>1.4116</v>
+      </c>
+      <c r="X74" s="11" t="n">
+        <v>1.3995</v>
+      </c>
+      <c r="Y74" s="11" t="n">
+        <v>1.3837</v>
+      </c>
+      <c r="Z74" s="11" t="n">
+        <v>1.3641</v>
+      </c>
+      <c r="AA74" s="11" t="n">
+        <v>1.3409</v>
+      </c>
+      <c r="AB74" s="11" t="n">
+        <v>1.3139</v>
+      </c>
+      <c r="AC74" s="11" t="n">
+        <v>1.2877</v>
+      </c>
+      <c r="AD74" s="11" t="n">
+        <v>1.2651</v>
+      </c>
+      <c r="AE74" s="11" t="n">
+        <v>1.2459</v>
+      </c>
+      <c r="AF74" s="11" t="n">
+        <v>1.2302</v>
+      </c>
+      <c r="AG74" s="11" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="AH74" s="11" t="n">
+        <v>1.2092</v>
+      </c>
+      <c r="AI74" s="11" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="AJ74" s="11" t="n">
+        <v>1.2023</v>
+      </c>
+      <c r="AK74" s="11" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="AL74" s="11" t="n">
+        <v>1.2092</v>
+      </c>
+      <c r="AM74" s="11" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="AN74" s="11" t="n">
+        <v>1.2302</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="n">
+        <v>1.611</v>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>1.5697</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="G75" s="11" t="n">
+        <v>1.6557</v>
+      </c>
+      <c r="H75" s="11" t="n">
+        <v>1.6497</v>
+      </c>
+      <c r="I75" s="11" t="n">
+        <v>1.6372</v>
+      </c>
+      <c r="J75" s="11" t="n">
+        <v>1.6216</v>
+      </c>
+      <c r="K75" s="11" t="n">
+        <v>1.6014</v>
+      </c>
+      <c r="L75" s="11" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="M75" s="11" t="n">
+        <v>1.5549</v>
+      </c>
+      <c r="N75" s="11" t="n">
+        <v>1.5343</v>
+      </c>
+      <c r="O75" s="11" t="n">
+        <v>1.5175</v>
+      </c>
+      <c r="P75" s="11" t="n">
+        <v>1.5055</v>
+      </c>
+      <c r="Q75" s="11" t="n">
+        <v>1.4973</v>
+      </c>
+      <c r="R75" s="11" t="n">
+        <v>1.4912</v>
+      </c>
+      <c r="S75" s="11" t="n">
+        <v>1.4864</v>
+      </c>
+      <c r="T75" s="11" t="n">
+        <v>1.4826</v>
+      </c>
+      <c r="U75" s="11" t="n">
+        <v>1.4792</v>
+      </c>
+      <c r="V75" s="11" t="n">
+        <v>1.4761</v>
+      </c>
+      <c r="W75" s="11" t="n">
+        <v>1.4729</v>
+      </c>
+      <c r="X75" s="11" t="n">
+        <v>1.4695</v>
+      </c>
+      <c r="Y75" s="11" t="n">
+        <v>1.4659</v>
+      </c>
+      <c r="Z75" s="11" t="n">
+        <v>1.4617</v>
+      </c>
+      <c r="AA75" s="11" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="AB75" s="11" t="n">
+        <v>1.4516</v>
+      </c>
+      <c r="AC75" s="11" t="n">
+        <v>1.4455</v>
+      </c>
+      <c r="AD75" s="11" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="AE75" s="11" t="n">
+        <v>1.4322</v>
+      </c>
+      <c r="AF75" s="11" t="n">
+        <v>1.4253</v>
+      </c>
+      <c r="AG75" s="11" t="n">
+        <v>1.4183</v>
+      </c>
+      <c r="AH75" s="11" t="n">
+        <v>1.4115</v>
+      </c>
+      <c r="AI75" s="11" t="n">
+        <v>1.4049</v>
+      </c>
+      <c r="AJ75" s="11" t="n">
+        <v>1.3985</v>
+      </c>
+      <c r="AK75" s="11" t="n">
+        <v>1.3926</v>
+      </c>
+      <c r="AL75" s="11" t="n">
+        <v>1.3871</v>
+      </c>
+      <c r="AM75" s="11" t="n">
+        <v>1.3822</v>
+      </c>
+      <c r="AN75" s="11" t="n">
+        <v>1.3778</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>5.6965</v>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>5.7142</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>5.8228</v>
+      </c>
+      <c r="G76" s="11" t="n">
+        <v>5.6284</v>
+      </c>
+      <c r="H76" s="11" t="n">
+        <v>5.4385</v>
+      </c>
+      <c r="I76" s="11" t="n">
+        <v>5.3407</v>
+      </c>
+      <c r="J76" s="11" t="n">
+        <v>5.3351</v>
+      </c>
+      <c r="K76" s="11" t="n">
+        <v>5.2861</v>
+      </c>
+      <c r="L76" s="11" t="n">
+        <v>5.2353</v>
+      </c>
+      <c r="M76" s="11" t="n">
+        <v>5.1828</v>
+      </c>
+      <c r="N76" s="11" t="n">
+        <v>5.1285</v>
+      </c>
+      <c r="O76" s="11" t="n">
+        <v>5.0724</v>
+      </c>
+      <c r="P76" s="11" t="n">
+        <v>5.0146</v>
+      </c>
+      <c r="Q76" s="11" t="n">
+        <v>4.8392</v>
+      </c>
+      <c r="R76" s="11" t="n">
+        <v>4.6982</v>
+      </c>
+      <c r="S76" s="11" t="n">
+        <v>4.5915</v>
+      </c>
+      <c r="T76" s="11" t="n">
+        <v>4.5191</v>
+      </c>
+      <c r="U76" s="11" t="n">
+        <v>4.4811</v>
+      </c>
+      <c r="V76" s="11" t="n">
+        <v>4.4774</v>
+      </c>
+      <c r="W76" s="11" t="n">
+        <v>4.5081</v>
+      </c>
+      <c r="X76" s="11" t="n">
+        <v>4.5731</v>
+      </c>
+      <c r="Y76" s="11" t="n">
+        <v>4.6724</v>
+      </c>
+      <c r="Z76" s="11" t="n">
+        <v>4.8061</v>
+      </c>
+      <c r="AA76" s="11" t="n">
+        <v>4.9741</v>
+      </c>
+      <c r="AB76" s="11" t="n">
+        <v>5.1765</v>
+      </c>
+      <c r="AC76" s="11" t="n">
+        <v>5.3305</v>
+      </c>
+      <c r="AD76" s="11" t="n">
+        <v>5.4641</v>
+      </c>
+      <c r="AE76" s="11" t="n">
+        <v>5.577</v>
+      </c>
+      <c r="AF76" s="11" t="n">
+        <v>5.6695</v>
+      </c>
+      <c r="AG76" s="11" t="n">
+        <v>5.7414</v>
+      </c>
+      <c r="AH76" s="11" t="n">
+        <v>5.7927</v>
+      </c>
+      <c r="AI76" s="11" t="n">
+        <v>5.8236</v>
+      </c>
+      <c r="AJ76" s="11" t="n">
+        <v>5.8338</v>
+      </c>
+      <c r="AK76" s="11" t="n">
+        <v>5.8236</v>
+      </c>
+      <c r="AL76" s="11" t="n">
+        <v>5.7927</v>
+      </c>
+      <c r="AM76" s="11" t="n">
+        <v>5.7414</v>
+      </c>
+      <c r="AN76" s="11" t="n">
+        <v>5.6695</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="n">
+        <v>5.6965</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>5.6851</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>5.7395</v>
+      </c>
+      <c r="G77" s="11" t="n">
+        <v>5.7433</v>
+      </c>
+      <c r="H77" s="11" t="n">
+        <v>5.6889</v>
+      </c>
+      <c r="I77" s="11" t="n">
+        <v>5.6275</v>
+      </c>
+      <c r="J77" s="11" t="n">
+        <v>5.5779</v>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>5.5398</v>
+      </c>
+      <c r="L77" s="11" t="n">
+        <v>5.5049</v>
+      </c>
+      <c r="M77" s="11" t="n">
+        <v>5.4721</v>
+      </c>
+      <c r="N77" s="11" t="n">
+        <v>5.4404</v>
+      </c>
+      <c r="O77" s="11" t="n">
+        <v>5.4095</v>
+      </c>
+      <c r="P77" s="11" t="n">
+        <v>5.3791</v>
+      </c>
+      <c r="Q77" s="11" t="n">
+        <v>5.3441</v>
+      </c>
+      <c r="R77" s="11" t="n">
+        <v>5.3028</v>
+      </c>
+      <c r="S77" s="11" t="n">
+        <v>5.2587</v>
+      </c>
+      <c r="T77" s="11" t="n">
+        <v>5.2146</v>
+      </c>
+      <c r="U77" s="11" t="n">
+        <v>5.1724</v>
+      </c>
+      <c r="V77" s="11" t="n">
+        <v>5.1337</v>
+      </c>
+      <c r="W77" s="11" t="n">
+        <v>5.0998</v>
+      </c>
+      <c r="X77" s="11" t="n">
+        <v>5.0717</v>
+      </c>
+      <c r="Y77" s="11" t="n">
+        <v>5.0502</v>
+      </c>
+      <c r="Z77" s="11" t="n">
+        <v>5.0359</v>
+      </c>
+      <c r="AA77" s="11" t="n">
+        <v>5.0295</v>
+      </c>
+      <c r="AB77" s="11" t="n">
+        <v>5.0313</v>
+      </c>
+      <c r="AC77" s="11" t="n">
+        <v>5.0402</v>
+      </c>
+      <c r="AD77" s="11" t="n">
+        <v>5.054</v>
+      </c>
+      <c r="AE77" s="11" t="n">
+        <v>5.0714</v>
+      </c>
+      <c r="AF77" s="11" t="n">
+        <v>5.0911</v>
+      </c>
+      <c r="AG77" s="11" t="n">
+        <v>5.1124</v>
+      </c>
+      <c r="AH77" s="11" t="n">
+        <v>5.1343</v>
+      </c>
+      <c r="AI77" s="11" t="n">
+        <v>5.1561</v>
+      </c>
+      <c r="AJ77" s="11" t="n">
+        <v>5.1771</v>
+      </c>
+      <c r="AK77" s="11" t="n">
+        <v>5.1969</v>
+      </c>
+      <c r="AL77" s="11" t="n">
+        <v>5.2149</v>
+      </c>
+      <c r="AM77" s="11" t="n">
+        <v>5.2308</v>
+      </c>
+      <c r="AN77" s="11" t="n">
+        <v>5.244</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="n">
+        <v>2.6372</v>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>2.5882</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>2.3792</v>
+      </c>
+      <c r="G78" s="11" t="n">
+        <v>2.4652</v>
+      </c>
+      <c r="H78" s="11" t="n">
+        <v>2.5734</v>
+      </c>
+      <c r="I78" s="11" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="J78" s="11" t="n">
+        <v>2.3622</v>
+      </c>
+      <c r="K78" s="11" t="n">
+        <v>2.1662</v>
+      </c>
+      <c r="L78" s="11" t="n">
+        <v>2.0304</v>
+      </c>
+      <c r="M78" s="11" t="n">
+        <v>1.955</v>
+      </c>
+      <c r="N78" s="11" t="n">
+        <v>1.9397</v>
+      </c>
+      <c r="O78" s="11" t="n">
+        <v>1.9848</v>
+      </c>
+      <c r="P78" s="11" t="n">
+        <v>2.0901</v>
+      </c>
+      <c r="Q78" s="11" t="n">
+        <v>2.1154</v>
+      </c>
+      <c r="R78" s="11" t="n">
+        <v>2.1377</v>
+      </c>
+      <c r="S78" s="11" t="n">
+        <v>2.1571</v>
+      </c>
+      <c r="T78" s="11" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="U78" s="11" t="n">
+        <v>2.1869</v>
+      </c>
+      <c r="V78" s="11" t="n">
+        <v>2.1974</v>
+      </c>
+      <c r="W78" s="11" t="n">
+        <v>2.2049</v>
+      </c>
+      <c r="X78" s="11" t="n">
+        <v>2.2095</v>
+      </c>
+      <c r="Y78" s="11" t="n">
+        <v>2.2111</v>
+      </c>
+      <c r="Z78" s="11" t="n">
+        <v>2.2098</v>
+      </c>
+      <c r="AA78" s="11" t="n">
+        <v>2.2054</v>
+      </c>
+      <c r="AB78" s="11" t="n">
+        <v>2.1982</v>
+      </c>
+      <c r="AC78" s="11" t="n">
+        <v>2.204</v>
+      </c>
+      <c r="AD78" s="11" t="n">
+        <v>2.209</v>
+      </c>
+      <c r="AE78" s="11" t="n">
+        <v>2.2132</v>
+      </c>
+      <c r="AF78" s="11" t="n">
+        <v>2.2167</v>
+      </c>
+      <c r="AG78" s="11" t="n">
+        <v>2.2194</v>
+      </c>
+      <c r="AH78" s="11" t="n">
+        <v>2.2213</v>
+      </c>
+      <c r="AI78" s="11" t="n">
+        <v>2.2225</v>
+      </c>
+      <c r="AJ78" s="11" t="n">
+        <v>2.2228</v>
+      </c>
+      <c r="AK78" s="11" t="n">
+        <v>2.2225</v>
+      </c>
+      <c r="AL78" s="11" t="n">
+        <v>2.2213</v>
+      </c>
+      <c r="AM78" s="11" t="n">
+        <v>2.2194</v>
+      </c>
+      <c r="AN78" s="11" t="n">
+        <v>2.2167</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="n">
+        <v>2.6372</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>2.6681</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>2.5636</v>
+      </c>
+      <c r="G79" s="11" t="n">
+        <v>2.5083</v>
+      </c>
+      <c r="H79" s="11" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="I79" s="11" t="n">
+        <v>2.5248</v>
+      </c>
+      <c r="J79" s="11" t="n">
+        <v>2.5144</v>
+      </c>
+      <c r="K79" s="11" t="n">
+        <v>2.478</v>
+      </c>
+      <c r="L79" s="11" t="n">
+        <v>2.4299</v>
+      </c>
+      <c r="M79" s="11" t="n">
+        <v>2.3807</v>
+      </c>
+      <c r="N79" s="11" t="n">
+        <v>2.3369</v>
+      </c>
+      <c r="O79" s="11" t="n">
+        <v>2.3024</v>
+      </c>
+      <c r="P79" s="11" t="n">
+        <v>2.2799</v>
+      </c>
+      <c r="Q79" s="11" t="n">
+        <v>2.2663</v>
+      </c>
+      <c r="R79" s="11" t="n">
+        <v>2.2563</v>
+      </c>
+      <c r="S79" s="11" t="n">
+        <v>2.2491</v>
+      </c>
+      <c r="T79" s="11" t="n">
+        <v>2.2439</v>
+      </c>
+      <c r="U79" s="11" t="n">
+        <v>2.2401</v>
+      </c>
+      <c r="V79" s="11" t="n">
+        <v>2.2375</v>
+      </c>
+      <c r="W79" s="11" t="n">
+        <v>2.2356</v>
+      </c>
+      <c r="X79" s="11" t="n">
+        <v>2.2342</v>
+      </c>
+      <c r="Y79" s="11" t="n">
+        <v>2.2331</v>
+      </c>
+      <c r="Z79" s="11" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="AA79" s="11" t="n">
+        <v>2.231</v>
+      </c>
+      <c r="AB79" s="11" t="n">
+        <v>2.2298</v>
+      </c>
+      <c r="AC79" s="11" t="n">
+        <v>2.2286</v>
+      </c>
+      <c r="AD79" s="11" t="n">
+        <v>2.2278</v>
+      </c>
+      <c r="AE79" s="11" t="n">
+        <v>2.2272</v>
+      </c>
+      <c r="AF79" s="11" t="n">
+        <v>2.2267</v>
+      </c>
+      <c r="AG79" s="11" t="n">
+        <v>2.2264</v>
+      </c>
+      <c r="AH79" s="11" t="n">
+        <v>2.2262</v>
+      </c>
+      <c r="AI79" s="11" t="n">
+        <v>2.2261</v>
+      </c>
+      <c r="AJ79" s="11" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="AK79" s="11" t="n">
+        <v>2.2259</v>
+      </c>
+      <c r="AL79" s="11" t="n">
+        <v>2.2258</v>
+      </c>
+      <c r="AM79" s="11" t="n">
+        <v>2.2256</v>
+      </c>
+      <c r="AN79" s="11" t="n">
+        <v>2.2254</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN73"/>
+  <autoFilter ref="A1:AN79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11818,7 +12628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F724"/>
+  <dimension ref="A1:F785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27431,8 +28241,1344 @@
       </c>
       <c r="F724" s="5" t="n"/>
     </row>
+    <row r="725">
+      <c r="A725" s="12" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D725" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E725" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F725" s="5" t="n"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="12" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D726" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E726" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F726" s="5" t="n"/>
+    </row>
+    <row r="727">
+      <c r="A727" s="12" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D727" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E727" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F727" s="5" t="n"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="12" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D728" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E728" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F728" s="5" t="n"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="12" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D729" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E729" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F729" s="5" t="n"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="12" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D730" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E730" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F730" s="5" t="n"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="12" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D731" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E731" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F731" s="5" t="n"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="12" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D732" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E732" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F732" s="5" t="n"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="12" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D733" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E733" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F733" s="5" t="n"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="12" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D734" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E734" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F734" s="5" t="n"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="12" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D735" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E735" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F735" s="5" t="n"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="12" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D736" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E736" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F736" s="5" t="n"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="12" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D737" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E737" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F737" s="5" t="n"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="12" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D738" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E738" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F738" s="5" t="n"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="12" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D739" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E739" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F739" s="5" t="n"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="12" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D740" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E740" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F740" s="5" t="n"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="12" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D741" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E741" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F741" s="5" t="n"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="12" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D742" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E742" s="5" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F742" s="5" t="n"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="12" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D743" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E743" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F743" s="5" t="n"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="12" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D744" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E744" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F744" s="5" t="n"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="12" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D745" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E745" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F745" s="5" t="n"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="12" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D746" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E746" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F746" s="5" t="n"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="12" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D747" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E747" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F747" s="5" t="n"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="12" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D748" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E748" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F748" s="5" t="n"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="12" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D749" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E749" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F749" s="5" t="n"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="12" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D750" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E750" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F750" s="5" t="n"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="12" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D751" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E751" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F751" s="5" t="n"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="12" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D752" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E752" s="5" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F752" s="5" t="n"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="12" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D753" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E753" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F753" s="5" t="n"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="12" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D754" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E754" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F754" s="5" t="n"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="12" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D755" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E755" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F755" s="5" t="n"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="12" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D756" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E756" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F756" s="5" t="n"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D757" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E757" s="5" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F757" s="5" t="n"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D758" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E758" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F758" s="5" t="n"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D759" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E759" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F759" s="5" t="n"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D760" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E760" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F760" s="5" t="n"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D761" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E761" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F761" s="5" t="n"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D762" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E762" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F762" s="5" t="n"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D763" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E763" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F763" s="5" t="n"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D764" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E764" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F764" s="5" t="n"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D765" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E765" s="5" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F765" s="5" t="n"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D766" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E766" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F766" s="5" t="n"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D767" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E767" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F767" s="5" t="n"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Business size</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Large businesses</t>
+        </is>
+      </c>
+      <c r="D768" s="5" t="n">
+        <v>66.81999999999999</v>
+      </c>
+      <c r="E768" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F768" s="5" t="n"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Business size</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Medium-sized businesses</t>
+        </is>
+      </c>
+      <c r="D769" s="5" t="n">
+        <v>62.46</v>
+      </c>
+      <c r="E769" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F769" s="5" t="n"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Business size</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Small businesses</t>
+        </is>
+      </c>
+      <c r="D770" s="5" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="E770" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F770" s="5" t="n"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr"/>
+      <c r="D771" s="5" t="n">
+        <v>56.13</v>
+      </c>
+      <c r="E771" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F771" s="5" t="n">
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D772" s="5" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="E772" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F772" s="5" t="n"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="D773" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E773" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F773" s="5" t="n"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D774" s="5" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="E774" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F774" s="5" t="n"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="D775" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E775" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F775" s="5" t="n"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D776" s="5" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="E776" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F776" s="5" t="n"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="D777" s="5" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E777" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F777" s="5" t="n"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Accommodation &amp; Food</t>
+        </is>
+      </c>
+      <c r="D778" s="5" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="E778" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F778" s="5" t="n"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="D779" s="5" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="E779" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F779" s="5" t="n"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Finance &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="D780" s="5" t="n">
+        <v>73.69</v>
+      </c>
+      <c r="E780" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F780" s="5" t="n"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D781" s="5" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="E781" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F781" s="5" t="n"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="D782" s="5" t="n">
+        <v>80.92</v>
+      </c>
+      <c r="E782" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F782" s="5" t="n"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D783" s="5" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="E783" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F783" s="5" t="n"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Retail Trade</t>
+        </is>
+      </c>
+      <c r="D784" s="5" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="E784" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F784" s="5" t="n"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>US estimate</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr"/>
+      <c r="D785" s="5" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="E785" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F785" s="5" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F724"/>
+  <autoFilter ref="A1:F785"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27443,7 +29589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I472"/>
+  <dimension ref="A1:I487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39387,8 +41533,387 @@
         <v>144.18</v>
       </c>
     </row>
+    <row r="473">
+      <c r="A473" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Business size</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="D473" s="8" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="E473" s="8" t="n"/>
+      <c r="F473" s="8" t="n"/>
+      <c r="G473" s="8" t="n"/>
+      <c r="H473" s="8" t="n"/>
+      <c r="I473" s="8" t="n">
+        <v>82.70999999999999</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Business size</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D474" s="8" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="E474" s="8" t="n"/>
+      <c r="F474" s="8" t="n"/>
+      <c r="G474" s="8" t="n"/>
+      <c r="H474" s="8" t="n"/>
+      <c r="I474" s="8" t="n">
+        <v>137.33</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Business size</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="D475" s="8" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="E475" s="8" t="n"/>
+      <c r="F475" s="8" t="n"/>
+      <c r="G475" s="8" t="n"/>
+      <c r="H475" s="8" t="n"/>
+      <c r="I475" s="8" t="n">
+        <v>159.12</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Financing status</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D476" s="8" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E476" s="8" t="n"/>
+      <c r="F476" s="8" t="n"/>
+      <c r="G476" s="8" t="n"/>
+      <c r="H476" s="8" t="n"/>
+      <c r="I476" s="8" t="n">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Financing status</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>PE-backed</t>
+        </is>
+      </c>
+      <c r="D477" s="8" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="E477" s="8" t="n"/>
+      <c r="F477" s="8" t="n"/>
+      <c r="G477" s="8" t="n"/>
+      <c r="H477" s="8" t="n"/>
+      <c r="I477" s="8" t="n">
+        <v>13.35</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Financing status</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>VC-backed</t>
+        </is>
+      </c>
+      <c r="D478" s="8" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="E478" s="8" t="n"/>
+      <c r="F478" s="8" t="n"/>
+      <c r="G478" s="8" t="n"/>
+      <c r="H478" s="8" t="n"/>
+      <c r="I478" s="8" t="n">
+        <v>312.71</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E479" s="8" t="n">
+        <v>279.98</v>
+      </c>
+      <c r="F479" s="8" t="n">
+        <v>3768.57</v>
+      </c>
+      <c r="G479" s="8" t="n">
+        <v>675.6</v>
+      </c>
+      <c r="H479" s="8" t="n">
+        <v>7205.13</v>
+      </c>
+      <c r="I479" s="8" t="n">
+        <v>13.71</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Accommodation and food services</t>
+        </is>
+      </c>
+      <c r="D480" s="8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="E480" s="8" t="n"/>
+      <c r="F480" s="8" t="n"/>
+      <c r="G480" s="8" t="n"/>
+      <c r="H480" s="8" t="n"/>
+      <c r="I480" s="8" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="D481" s="8" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="E481" s="8" t="n"/>
+      <c r="F481" s="8" t="n"/>
+      <c r="G481" s="8" t="n"/>
+      <c r="H481" s="8" t="n"/>
+      <c r="I481" s="8" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Finance and insurance</t>
+        </is>
+      </c>
+      <c r="D482" s="8" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="E482" s="8" t="n"/>
+      <c r="F482" s="8" t="n"/>
+      <c r="G482" s="8" t="n"/>
+      <c r="H482" s="8" t="n"/>
+      <c r="I482" s="8" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Health care</t>
+        </is>
+      </c>
+      <c r="D483" s="8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E483" s="8" t="n"/>
+      <c r="F483" s="8" t="n"/>
+      <c r="G483" s="8" t="n"/>
+      <c r="H483" s="8" t="n"/>
+      <c r="I483" s="8" t="n">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D484" s="8" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="E484" s="8" t="n"/>
+      <c r="F484" s="8" t="n"/>
+      <c r="G484" s="8" t="n"/>
+      <c r="H484" s="8" t="n"/>
+      <c r="I484" s="8" t="n">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Professional, scientific, and technical services</t>
+        </is>
+      </c>
+      <c r="D485" s="8" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="E485" s="8" t="n"/>
+      <c r="F485" s="8" t="n"/>
+      <c r="G485" s="8" t="n"/>
+      <c r="H485" s="8" t="n"/>
+      <c r="I485" s="8" t="n">
+        <v>98.83</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D486" s="8" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="E486" s="8" t="n"/>
+      <c r="F486" s="8" t="n"/>
+      <c r="G486" s="8" t="n"/>
+      <c r="H486" s="8" t="n"/>
+      <c r="I486" s="8" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Technology and media</t>
+        </is>
+      </c>
+      <c r="D487" s="8" t="n">
+        <v>80.15000000000001</v>
+      </c>
+      <c r="E487" s="8" t="n"/>
+      <c r="F487" s="8" t="n"/>
+      <c r="G487" s="8" t="n"/>
+      <c r="H487" s="8" t="n"/>
+      <c r="I487" s="8" t="n">
+        <v>178.84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I472"/>
+  <autoFilter ref="A1:I487"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39880,7 +42405,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-08  (12 daily snapshots, 72 curve rows)</t>
+          <t>2026-08-28 to 2026-09-09  (13 daily snapshots, 78 curve rows)</t>
         </is>
       </c>
     </row>
@@ -39904,7 +42429,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2023-01-01 to 2026-07-01  (43 months, 723 rows)</t>
+          <t>2023-01-01 to 2026-08-01  (44 months, 784 rows)</t>
         </is>
       </c>
     </row>
@@ -39928,7 +42453,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2023-08-01 to 2026-07-01  (36 months, 471 rows)</t>
+          <t>2023-08-01 to 2026-08-01  (37 months, 486 rows)</t>
         </is>
       </c>
     </row>
@@ -39976,7 +42501,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-08  (17 rows)</t>
+          <t>2026-08-23 to 2026-09-09  (18 rows)</t>
         </is>
       </c>
     </row>
@@ -39988,7 +42513,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-08 19:27 local</t>
+          <t>2026-09-09 19:19 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$18</f>
+              <f>'Daily Index'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$18</f>
+              <f>'Daily Index'!$B$2:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$18</f>
+              <f>'Daily Index'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$18</f>
+              <f>'Daily Index'!$C$2:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$18</f>
+              <f>'Daily Index'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$18</f>
+              <f>'Daily Index'!$D$2:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1476,8 +1476,34 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>0.5394</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>1.816</v>
+      </c>
+      <c r="E19" s="4">
+        <f>IF(OR(B19="",B18=""),"",B19/B18-1)</f>
+        <v/>
+      </c>
+      <c r="F19" s="4">
+        <f>IF(OR(C19="",C18=""),"",C19/C18-1)</f>
+        <v/>
+      </c>
+      <c r="G19" s="4">
+        <f>IF(OR(D19="",D18=""),"",D19/D18-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29262,7 +29288,6 @@
           <t>Headline</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr"/>
       <c r="D771" s="5" t="n">
         <v>56.13</v>
       </c>
@@ -29568,7 +29593,6 @@
           <t>US estimate</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr"/>
       <c r="D785" s="5" t="n">
         <v>22.1</v>
       </c>
@@ -41692,7 +41716,6 @@
           <t>Overall</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr"/>
       <c r="D479" s="8" t="n">
         <v>12.5</v>
       </c>
@@ -42477,7 +42500,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-07  (17 rows)</t>
+          <t>2026-08-22 to 2026-09-08  (18 rows)</t>
         </is>
       </c>
     </row>
@@ -42513,7 +42536,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 19:19 local</t>
+          <t>2026-09-10 05:58 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
   </definedNames>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$19</f>
+              <f>'GPU Rental'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$19</f>
+              <f>'GPU Rental'!$B$2:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$19</f>
+              <f>'GPU Rental'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$19</f>
+              <f>'GPU Rental'!$C$2:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$19</f>
+              <f>'GPU Rental'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$19</f>
+              <f>'GPU Rental'!$D$2:$D$20</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$19</f>
+              <f>'GPU Rental'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$19</f>
+              <f>'GPU Rental'!$E$2:$E$20</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$19</f>
+              <f>'GPU Rental'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$19</f>
+              <f>'GPU Rental'!$F$2:$F$20</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$19</f>
+              <f>'GPU Rental'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$19</f>
+              <f>'GPU Rental'!$G$2:$G$20</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$19</f>
+              <f>'GPU Rental'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$19</f>
+              <f>'GPU Rental'!$H$2:$H$20</f>
             </numRef>
           </val>
         </ser>
@@ -1514,7 +1514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2555,8 +2555,62 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I20" s="4">
+        <f>IF(OR(B20="",B19=""),"",B20/B19-1)</f>
+        <v/>
+      </c>
+      <c r="J20" s="4">
+        <f>IF(OR(C20="",C19=""),"",C20/C19-1)</f>
+        <v/>
+      </c>
+      <c r="K20" s="4">
+        <f>IF(OR(D20="",D19=""),"",D20/D19-1)</f>
+        <v/>
+      </c>
+      <c r="L20" s="4">
+        <f>IF(OR(E20="",E19=""),"",E20/E19-1)</f>
+        <v/>
+      </c>
+      <c r="M20" s="4">
+        <f>IF(OR(F20="",F19=""),"",F20/F19-1)</f>
+        <v/>
+      </c>
+      <c r="N20" s="4">
+        <f>IF(OR(G20="",G19=""),"",G20/G19-1)</f>
+        <v/>
+      </c>
+      <c r="O20" s="4">
+        <f>IF(OR(H20="",H19=""),"",H20/H19-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2567,7 +2621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN79"/>
+  <dimension ref="A1:AN85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12642,8 +12696,764 @@
         <v>2.2254</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="10" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>1.6089</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>1.6138</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>1.7224</v>
+      </c>
+      <c r="G80" s="11" t="n">
+        <v>1.6507</v>
+      </c>
+      <c r="H80" s="11" t="n">
+        <v>1.6105</v>
+      </c>
+      <c r="I80" s="11" t="n">
+        <v>1.5675</v>
+      </c>
+      <c r="J80" s="11" t="n">
+        <v>1.5219</v>
+      </c>
+      <c r="K80" s="11" t="n">
+        <v>1.4433</v>
+      </c>
+      <c r="L80" s="11" t="n">
+        <v>1.3876</v>
+      </c>
+      <c r="M80" s="11" t="n">
+        <v>1.3548</v>
+      </c>
+      <c r="N80" s="11" t="n">
+        <v>1.3447</v>
+      </c>
+      <c r="O80" s="11" t="n">
+        <v>1.3575</v>
+      </c>
+      <c r="P80" s="11" t="n">
+        <v>1.3931</v>
+      </c>
+      <c r="Q80" s="11" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="R80" s="11" t="n">
+        <v>1.4191</v>
+      </c>
+      <c r="S80" s="11" t="n">
+        <v>1.4262</v>
+      </c>
+      <c r="T80" s="11" t="n">
+        <v>1.4295</v>
+      </c>
+      <c r="U80" s="11" t="n">
+        <v>1.4289</v>
+      </c>
+      <c r="V80" s="11" t="n">
+        <v>1.4245</v>
+      </c>
+      <c r="W80" s="11" t="n">
+        <v>1.4162</v>
+      </c>
+      <c r="X80" s="11" t="n">
+        <v>1.404</v>
+      </c>
+      <c r="Y80" s="11" t="n">
+        <v>1.3879</v>
+      </c>
+      <c r="Z80" s="11" t="n">
+        <v>1.368</v>
+      </c>
+      <c r="AA80" s="11" t="n">
+        <v>1.3442</v>
+      </c>
+      <c r="AB80" s="11" t="n">
+        <v>1.3165</v>
+      </c>
+      <c r="AC80" s="11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD80" s="11" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="AE80" s="11" t="n">
+        <v>1.2476</v>
+      </c>
+      <c r="AF80" s="11" t="n">
+        <v>1.2317</v>
+      </c>
+      <c r="AG80" s="11" t="n">
+        <v>1.2193</v>
+      </c>
+      <c r="AH80" s="11" t="n">
+        <v>1.2105</v>
+      </c>
+      <c r="AI80" s="11" t="n">
+        <v>1.2052</v>
+      </c>
+      <c r="AJ80" s="11" t="n">
+        <v>1.2034</v>
+      </c>
+      <c r="AK80" s="11" t="n">
+        <v>1.2052</v>
+      </c>
+      <c r="AL80" s="11" t="n">
+        <v>1.2105</v>
+      </c>
+      <c r="AM80" s="11" t="n">
+        <v>1.2193</v>
+      </c>
+      <c r="AN80" s="11" t="n">
+        <v>1.2317</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="n">
+        <v>1.6089</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>1.5745</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>1.6288</v>
+      </c>
+      <c r="G81" s="11" t="n">
+        <v>1.6531</v>
+      </c>
+      <c r="H81" s="11" t="n">
+        <v>1.6475</v>
+      </c>
+      <c r="I81" s="11" t="n">
+        <v>1.6359</v>
+      </c>
+      <c r="J81" s="11" t="n">
+        <v>1.6207</v>
+      </c>
+      <c r="K81" s="11" t="n">
+        <v>1.6007</v>
+      </c>
+      <c r="L81" s="11" t="n">
+        <v>1.5773</v>
+      </c>
+      <c r="M81" s="11" t="n">
+        <v>1.5542</v>
+      </c>
+      <c r="N81" s="11" t="n">
+        <v>1.5336</v>
+      </c>
+      <c r="O81" s="11" t="n">
+        <v>1.5168</v>
+      </c>
+      <c r="P81" s="11" t="n">
+        <v>1.5049</v>
+      </c>
+      <c r="Q81" s="11" t="n">
+        <v>1.4969</v>
+      </c>
+      <c r="R81" s="11" t="n">
+        <v>1.4909</v>
+      </c>
+      <c r="S81" s="11" t="n">
+        <v>1.4864</v>
+      </c>
+      <c r="T81" s="11" t="n">
+        <v>1.4828</v>
+      </c>
+      <c r="U81" s="11" t="n">
+        <v>1.4796</v>
+      </c>
+      <c r="V81" s="11" t="n">
+        <v>1.4767</v>
+      </c>
+      <c r="W81" s="11" t="n">
+        <v>1.4738</v>
+      </c>
+      <c r="X81" s="11" t="n">
+        <v>1.4706</v>
+      </c>
+      <c r="Y81" s="11" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="Z81" s="11" t="n">
+        <v>1.463</v>
+      </c>
+      <c r="AA81" s="11" t="n">
+        <v>1.4584</v>
+      </c>
+      <c r="AB81" s="11" t="n">
+        <v>1.4531</v>
+      </c>
+      <c r="AC81" s="11" t="n">
+        <v>1.447</v>
+      </c>
+      <c r="AD81" s="11" t="n">
+        <v>1.4406</v>
+      </c>
+      <c r="AE81" s="11" t="n">
+        <v>1.4338</v>
+      </c>
+      <c r="AF81" s="11" t="n">
+        <v>1.4268</v>
+      </c>
+      <c r="AG81" s="11" t="n">
+        <v>1.4199</v>
+      </c>
+      <c r="AH81" s="11" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="AI81" s="11" t="n">
+        <v>1.4064</v>
+      </c>
+      <c r="AJ81" s="11" t="n">
+        <v>1.4001</v>
+      </c>
+      <c r="AK81" s="11" t="n">
+        <v>1.3941</v>
+      </c>
+      <c r="AL81" s="11" t="n">
+        <v>1.3886</v>
+      </c>
+      <c r="AM81" s="11" t="n">
+        <v>1.3837</v>
+      </c>
+      <c r="AN81" s="11" t="n">
+        <v>1.3793</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>5.6789</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>5.6831</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>5.817</v>
+      </c>
+      <c r="G82" s="11" t="n">
+        <v>5.6121</v>
+      </c>
+      <c r="H82" s="11" t="n">
+        <v>5.415</v>
+      </c>
+      <c r="I82" s="11" t="n">
+        <v>5.3152</v>
+      </c>
+      <c r="J82" s="11" t="n">
+        <v>5.3125</v>
+      </c>
+      <c r="K82" s="11" t="n">
+        <v>5.2644</v>
+      </c>
+      <c r="L82" s="11" t="n">
+        <v>5.2142</v>
+      </c>
+      <c r="M82" s="11" t="n">
+        <v>5.1619</v>
+      </c>
+      <c r="N82" s="11" t="n">
+        <v>5.1076</v>
+      </c>
+      <c r="O82" s="11" t="n">
+        <v>5.0512</v>
+      </c>
+      <c r="P82" s="11" t="n">
+        <v>4.9928</v>
+      </c>
+      <c r="Q82" s="11" t="n">
+        <v>4.8168</v>
+      </c>
+      <c r="R82" s="11" t="n">
+        <v>4.6753</v>
+      </c>
+      <c r="S82" s="11" t="n">
+        <v>4.5683</v>
+      </c>
+      <c r="T82" s="11" t="n">
+        <v>4.4957</v>
+      </c>
+      <c r="U82" s="11" t="n">
+        <v>4.4576</v>
+      </c>
+      <c r="V82" s="11" t="n">
+        <v>4.4539</v>
+      </c>
+      <c r="W82" s="11" t="n">
+        <v>4.4847</v>
+      </c>
+      <c r="X82" s="11" t="n">
+        <v>4.5499</v>
+      </c>
+      <c r="Y82" s="11" t="n">
+        <v>4.6495</v>
+      </c>
+      <c r="Z82" s="11" t="n">
+        <v>4.7836</v>
+      </c>
+      <c r="AA82" s="11" t="n">
+        <v>4.9522</v>
+      </c>
+      <c r="AB82" s="11" t="n">
+        <v>5.1552</v>
+      </c>
+      <c r="AC82" s="11" t="n">
+        <v>5.3098</v>
+      </c>
+      <c r="AD82" s="11" t="n">
+        <v>5.4437</v>
+      </c>
+      <c r="AE82" s="11" t="n">
+        <v>5.5571</v>
+      </c>
+      <c r="AF82" s="11" t="n">
+        <v>5.6498</v>
+      </c>
+      <c r="AG82" s="11" t="n">
+        <v>5.722</v>
+      </c>
+      <c r="AH82" s="11" t="n">
+        <v>5.7735</v>
+      </c>
+      <c r="AI82" s="11" t="n">
+        <v>5.8044</v>
+      </c>
+      <c r="AJ82" s="11" t="n">
+        <v>5.8147</v>
+      </c>
+      <c r="AK82" s="11" t="n">
+        <v>5.8044</v>
+      </c>
+      <c r="AL82" s="11" t="n">
+        <v>5.7735</v>
+      </c>
+      <c r="AM82" s="11" t="n">
+        <v>5.722</v>
+      </c>
+      <c r="AN82" s="11" t="n">
+        <v>5.6498</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="n">
+        <v>5.6789</v>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>5.6444</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>5.7113</v>
+      </c>
+      <c r="G83" s="11" t="n">
+        <v>5.7218</v>
+      </c>
+      <c r="H83" s="11" t="n">
+        <v>5.6677</v>
+      </c>
+      <c r="I83" s="11" t="n">
+        <v>5.6056</v>
+      </c>
+      <c r="J83" s="11" t="n">
+        <v>5.5556</v>
+      </c>
+      <c r="K83" s="11" t="n">
+        <v>5.5175</v>
+      </c>
+      <c r="L83" s="11" t="n">
+        <v>5.4827</v>
+      </c>
+      <c r="M83" s="11" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="N83" s="11" t="n">
+        <v>5.4185</v>
+      </c>
+      <c r="O83" s="11" t="n">
+        <v>5.3877</v>
+      </c>
+      <c r="P83" s="11" t="n">
+        <v>5.3572</v>
+      </c>
+      <c r="Q83" s="11" t="n">
+        <v>5.3222</v>
+      </c>
+      <c r="R83" s="11" t="n">
+        <v>5.2808</v>
+      </c>
+      <c r="S83" s="11" t="n">
+        <v>5.2367</v>
+      </c>
+      <c r="T83" s="11" t="n">
+        <v>5.1925</v>
+      </c>
+      <c r="U83" s="11" t="n">
+        <v>5.1502</v>
+      </c>
+      <c r="V83" s="11" t="n">
+        <v>5.1115</v>
+      </c>
+      <c r="W83" s="11" t="n">
+        <v>5.0775</v>
+      </c>
+      <c r="X83" s="11" t="n">
+        <v>5.0494</v>
+      </c>
+      <c r="Y83" s="11" t="n">
+        <v>5.0278</v>
+      </c>
+      <c r="Z83" s="11" t="n">
+        <v>5.0135</v>
+      </c>
+      <c r="AA83" s="11" t="n">
+        <v>5.0071</v>
+      </c>
+      <c r="AB83" s="11" t="n">
+        <v>5.0089</v>
+      </c>
+      <c r="AC83" s="11" t="n">
+        <v>5.0179</v>
+      </c>
+      <c r="AD83" s="11" t="n">
+        <v>5.0318</v>
+      </c>
+      <c r="AE83" s="11" t="n">
+        <v>5.0492</v>
+      </c>
+      <c r="AF83" s="11" t="n">
+        <v>5.0691</v>
+      </c>
+      <c r="AG83" s="11" t="n">
+        <v>5.0904</v>
+      </c>
+      <c r="AH83" s="11" t="n">
+        <v>5.1124</v>
+      </c>
+      <c r="AI83" s="11" t="n">
+        <v>5.1342</v>
+      </c>
+      <c r="AJ83" s="11" t="n">
+        <v>5.1554</v>
+      </c>
+      <c r="AK83" s="11" t="n">
+        <v>5.1753</v>
+      </c>
+      <c r="AL83" s="11" t="n">
+        <v>5.1934</v>
+      </c>
+      <c r="AM83" s="11" t="n">
+        <v>5.2093</v>
+      </c>
+      <c r="AN83" s="11" t="n">
+        <v>5.2225</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="n">
+        <v>2.6361</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>2.5944</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>2.3997</v>
+      </c>
+      <c r="G84" s="11" t="n">
+        <v>2.4795</v>
+      </c>
+      <c r="H84" s="11" t="n">
+        <v>2.5834</v>
+      </c>
+      <c r="I84" s="11" t="n">
+        <v>2.5476</v>
+      </c>
+      <c r="J84" s="11" t="n">
+        <v>2.3719</v>
+      </c>
+      <c r="K84" s="11" t="n">
+        <v>2.1766</v>
+      </c>
+      <c r="L84" s="11" t="n">
+        <v>2.041</v>
+      </c>
+      <c r="M84" s="11" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="N84" s="11" t="n">
+        <v>1.9487</v>
+      </c>
+      <c r="O84" s="11" t="n">
+        <v>1.992</v>
+      </c>
+      <c r="P84" s="11" t="n">
+        <v>2.0949</v>
+      </c>
+      <c r="Q84" s="11" t="n">
+        <v>2.1181</v>
+      </c>
+      <c r="R84" s="11" t="n">
+        <v>2.1385</v>
+      </c>
+      <c r="S84" s="11" t="n">
+        <v>2.1561</v>
+      </c>
+      <c r="T84" s="11" t="n">
+        <v>2.171</v>
+      </c>
+      <c r="U84" s="11" t="n">
+        <v>2.1831</v>
+      </c>
+      <c r="V84" s="11" t="n">
+        <v>2.1924</v>
+      </c>
+      <c r="W84" s="11" t="n">
+        <v>2.1989</v>
+      </c>
+      <c r="X84" s="11" t="n">
+        <v>2.2026</v>
+      </c>
+      <c r="Y84" s="11" t="n">
+        <v>2.2036</v>
+      </c>
+      <c r="Z84" s="11" t="n">
+        <v>2.2018</v>
+      </c>
+      <c r="AA84" s="11" t="n">
+        <v>2.1972</v>
+      </c>
+      <c r="AB84" s="11" t="n">
+        <v>2.1899</v>
+      </c>
+      <c r="AC84" s="11" t="n">
+        <v>2.1943</v>
+      </c>
+      <c r="AD84" s="11" t="n">
+        <v>2.1982</v>
+      </c>
+      <c r="AE84" s="11" t="n">
+        <v>2.2014</v>
+      </c>
+      <c r="AF84" s="11" t="n">
+        <v>2.2041</v>
+      </c>
+      <c r="AG84" s="11" t="n">
+        <v>2.2061</v>
+      </c>
+      <c r="AH84" s="11" t="n">
+        <v>2.2076</v>
+      </c>
+      <c r="AI84" s="11" t="n">
+        <v>2.2085</v>
+      </c>
+      <c r="AJ84" s="11" t="n">
+        <v>2.2088</v>
+      </c>
+      <c r="AK84" s="11" t="n">
+        <v>2.2085</v>
+      </c>
+      <c r="AL84" s="11" t="n">
+        <v>2.2076</v>
+      </c>
+      <c r="AM84" s="11" t="n">
+        <v>2.2061</v>
+      </c>
+      <c r="AN84" s="11" t="n">
+        <v>2.2041</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="n">
+        <v>2.6361</v>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v>2.6689</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>2.5716</v>
+      </c>
+      <c r="G85" s="11" t="n">
+        <v>2.5199</v>
+      </c>
+      <c r="H85" s="11" t="n">
+        <v>2.5257</v>
+      </c>
+      <c r="I85" s="11" t="n">
+        <v>2.536</v>
+      </c>
+      <c r="J85" s="11" t="n">
+        <v>2.5252</v>
+      </c>
+      <c r="K85" s="11" t="n">
+        <v>2.4887</v>
+      </c>
+      <c r="L85" s="11" t="n">
+        <v>2.4406</v>
+      </c>
+      <c r="M85" s="11" t="n">
+        <v>2.3914</v>
+      </c>
+      <c r="N85" s="11" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="O85" s="11" t="n">
+        <v>2.3127</v>
+      </c>
+      <c r="P85" s="11" t="n">
+        <v>2.2899</v>
+      </c>
+      <c r="Q85" s="11" t="n">
+        <v>2.2758</v>
+      </c>
+      <c r="R85" s="11" t="n">
+        <v>2.2653</v>
+      </c>
+      <c r="S85" s="11" t="n">
+        <v>2.2574</v>
+      </c>
+      <c r="T85" s="11" t="n">
+        <v>2.2516</v>
+      </c>
+      <c r="U85" s="11" t="n">
+        <v>2.2472</v>
+      </c>
+      <c r="V85" s="11" t="n">
+        <v>2.2439</v>
+      </c>
+      <c r="W85" s="11" t="n">
+        <v>2.2414</v>
+      </c>
+      <c r="X85" s="11" t="n">
+        <v>2.2393</v>
+      </c>
+      <c r="Y85" s="11" t="n">
+        <v>2.2376</v>
+      </c>
+      <c r="Z85" s="11" t="n">
+        <v>2.2361</v>
+      </c>
+      <c r="AA85" s="11" t="n">
+        <v>2.2345</v>
+      </c>
+      <c r="AB85" s="11" t="n">
+        <v>2.2328</v>
+      </c>
+      <c r="AC85" s="11" t="n">
+        <v>2.2312</v>
+      </c>
+      <c r="AD85" s="11" t="n">
+        <v>2.2298</v>
+      </c>
+      <c r="AE85" s="11" t="n">
+        <v>2.2287</v>
+      </c>
+      <c r="AF85" s="11" t="n">
+        <v>2.2278</v>
+      </c>
+      <c r="AG85" s="11" t="n">
+        <v>2.227</v>
+      </c>
+      <c r="AH85" s="11" t="n">
+        <v>2.2263</v>
+      </c>
+      <c r="AI85" s="11" t="n">
+        <v>2.2257</v>
+      </c>
+      <c r="AJ85" s="11" t="n">
+        <v>2.2252</v>
+      </c>
+      <c r="AK85" s="11" t="n">
+        <v>2.2247</v>
+      </c>
+      <c r="AL85" s="11" t="n">
+        <v>2.2242</v>
+      </c>
+      <c r="AM85" s="11" t="n">
+        <v>2.2237</v>
+      </c>
+      <c r="AN85" s="11" t="n">
+        <v>2.2232</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN79"/>
+  <autoFilter ref="A1:AN85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42428,7 +43238,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-09  (13 daily snapshots, 78 curve rows)</t>
+          <t>2026-08-28 to 2026-09-10  (14 daily snapshots, 84 curve rows)</t>
         </is>
       </c>
     </row>
@@ -42524,7 +43334,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-09  (18 rows)</t>
+          <t>2026-08-23 to 2026-09-10  (19 rows)</t>
         </is>
       </c>
     </row>
@@ -42536,7 +43346,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-10 05:58 local</t>
+          <t>2026-09-10 19:09 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$19</f>
+              <f>'Daily Index'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$19</f>
+              <f>'Daily Index'!$B$2:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$19</f>
+              <f>'Daily Index'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$19</f>
+              <f>'Daily Index'!$C$2:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$19</f>
+              <f>'Daily Index'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$19</f>
+              <f>'Daily Index'!$D$2:$D$20</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1502,8 +1502,34 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>0.6447000000000001</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>1.9726</v>
+      </c>
+      <c r="E20" s="4">
+        <f>IF(OR(B20="",B19=""),"",B20/B19-1)</f>
+        <v/>
+      </c>
+      <c r="F20" s="4">
+        <f>IF(OR(C20="",C19=""),"",C20/C19-1)</f>
+        <v/>
+      </c>
+      <c r="G20" s="4">
+        <f>IF(OR(D20="",D19=""),"",D20/D19-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:G20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43310,7 +43336,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-08  (18 rows)</t>
+          <t>2026-08-22 to 2026-09-09  (19 rows)</t>
         </is>
       </c>
     </row>
@@ -43346,7 +43372,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-10 19:09 local</t>
+          <t>2026-09-11 06:00 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
   </definedNames>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$20</f>
+              <f>'GPU Rental'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$20</f>
+              <f>'GPU Rental'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$20</f>
+              <f>'GPU Rental'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$20</f>
+              <f>'GPU Rental'!$C$2:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$20</f>
+              <f>'GPU Rental'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$20</f>
+              <f>'GPU Rental'!$D$2:$D$21</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$20</f>
+              <f>'GPU Rental'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$20</f>
+              <f>'GPU Rental'!$E$2:$E$21</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$20</f>
+              <f>'GPU Rental'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$20</f>
+              <f>'GPU Rental'!$F$2:$F$21</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$20</f>
+              <f>'GPU Rental'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$20</f>
+              <f>'GPU Rental'!$G$2:$G$21</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$20</f>
+              <f>'GPU Rental'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$20</f>
+              <f>'GPU Rental'!$H$2:$H$21</f>
             </numRef>
           </val>
         </ser>
@@ -1540,7 +1540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2635,8 +2635,62 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I21" s="4">
+        <f>IF(OR(B21="",B20=""),"",B21/B20-1)</f>
+        <v/>
+      </c>
+      <c r="J21" s="4">
+        <f>IF(OR(C21="",C20=""),"",C21/C20-1)</f>
+        <v/>
+      </c>
+      <c r="K21" s="4">
+        <f>IF(OR(D21="",D20=""),"",D21/D20-1)</f>
+        <v/>
+      </c>
+      <c r="L21" s="4">
+        <f>IF(OR(E21="",E20=""),"",E21/E20-1)</f>
+        <v/>
+      </c>
+      <c r="M21" s="4">
+        <f>IF(OR(F21="",F20=""),"",F21/F20-1)</f>
+        <v/>
+      </c>
+      <c r="N21" s="4">
+        <f>IF(OR(G21="",G20=""),"",G21/G20-1)</f>
+        <v/>
+      </c>
+      <c r="O21" s="4">
+        <f>IF(OR(H21="",H20=""),"",H21/H20-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O20"/>
+  <autoFilter ref="A1:O21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2647,7 +2701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN85"/>
+  <dimension ref="A1:AN91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13478,8 +13532,764 @@
         <v>2.2232</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="n">
+        <v>1.6121</v>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>1.6104</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>1.7308</v>
+      </c>
+      <c r="G86" s="11" t="n">
+        <v>1.6556</v>
+      </c>
+      <c r="H86" s="11" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="I86" s="11" t="n">
+        <v>1.5705</v>
+      </c>
+      <c r="J86" s="11" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="K86" s="11" t="n">
+        <v>1.446</v>
+      </c>
+      <c r="L86" s="11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M86" s="11" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N86" s="11" t="n">
+        <v>1.3471</v>
+      </c>
+      <c r="O86" s="11" t="n">
+        <v>1.3603</v>
+      </c>
+      <c r="P86" s="11" t="n">
+        <v>1.3965</v>
+      </c>
+      <c r="Q86" s="11" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="R86" s="11" t="n">
+        <v>1.4236</v>
+      </c>
+      <c r="S86" s="11" t="n">
+        <v>1.4312</v>
+      </c>
+      <c r="T86" s="11" t="n">
+        <v>1.4348</v>
+      </c>
+      <c r="U86" s="11" t="n">
+        <v>1.4344</v>
+      </c>
+      <c r="V86" s="11" t="n">
+        <v>1.4301</v>
+      </c>
+      <c r="W86" s="11" t="n">
+        <v>1.4218</v>
+      </c>
+      <c r="X86" s="11" t="n">
+        <v>1.4096</v>
+      </c>
+      <c r="Y86" s="11" t="n">
+        <v>1.3933</v>
+      </c>
+      <c r="Z86" s="11" t="n">
+        <v>1.3731</v>
+      </c>
+      <c r="AA86" s="11" t="n">
+        <v>1.349</v>
+      </c>
+      <c r="AB86" s="11" t="n">
+        <v>1.3209</v>
+      </c>
+      <c r="AC86" s="11" t="n">
+        <v>1.2942</v>
+      </c>
+      <c r="AD86" s="11" t="n">
+        <v>1.271</v>
+      </c>
+      <c r="AE86" s="11" t="n">
+        <v>1.2514</v>
+      </c>
+      <c r="AF86" s="11" t="n">
+        <v>1.2354</v>
+      </c>
+      <c r="AG86" s="11" t="n">
+        <v>1.223</v>
+      </c>
+      <c r="AH86" s="11" t="n">
+        <v>1.2141</v>
+      </c>
+      <c r="AI86" s="11" t="n">
+        <v>1.2087</v>
+      </c>
+      <c r="AJ86" s="11" t="n">
+        <v>1.2069</v>
+      </c>
+      <c r="AK86" s="11" t="n">
+        <v>1.2087</v>
+      </c>
+      <c r="AL86" s="11" t="n">
+        <v>1.2141</v>
+      </c>
+      <c r="AM86" s="11" t="n">
+        <v>1.223</v>
+      </c>
+      <c r="AN86" s="11" t="n">
+        <v>1.2354</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="n">
+        <v>1.6121</v>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>1.5665</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="G87" s="11" t="n">
+        <v>1.6543</v>
+      </c>
+      <c r="H87" s="11" t="n">
+        <v>1.6495</v>
+      </c>
+      <c r="I87" s="11" t="n">
+        <v>1.6381</v>
+      </c>
+      <c r="J87" s="11" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="K87" s="11" t="n">
+        <v>1.6031</v>
+      </c>
+      <c r="L87" s="11" t="n">
+        <v>1.5797</v>
+      </c>
+      <c r="M87" s="11" t="n">
+        <v>1.5566</v>
+      </c>
+      <c r="N87" s="11" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="O87" s="11" t="n">
+        <v>1.5192</v>
+      </c>
+      <c r="P87" s="11" t="n">
+        <v>1.5073</v>
+      </c>
+      <c r="Q87" s="11" t="n">
+        <v>1.4994</v>
+      </c>
+      <c r="R87" s="11" t="n">
+        <v>1.4936</v>
+      </c>
+      <c r="S87" s="11" t="n">
+        <v>1.4892</v>
+      </c>
+      <c r="T87" s="11" t="n">
+        <v>1.4857</v>
+      </c>
+      <c r="U87" s="11" t="n">
+        <v>1.4827</v>
+      </c>
+      <c r="V87" s="11" t="n">
+        <v>1.4799</v>
+      </c>
+      <c r="W87" s="11" t="n">
+        <v>1.4771</v>
+      </c>
+      <c r="X87" s="11" t="n">
+        <v>1.4741</v>
+      </c>
+      <c r="Y87" s="11" t="n">
+        <v>1.4706</v>
+      </c>
+      <c r="Z87" s="11" t="n">
+        <v>1.4667</v>
+      </c>
+      <c r="AA87" s="11" t="n">
+        <v>1.4621</v>
+      </c>
+      <c r="AB87" s="11" t="n">
+        <v>1.4568</v>
+      </c>
+      <c r="AC87" s="11" t="n">
+        <v>1.4508</v>
+      </c>
+      <c r="AD87" s="11" t="n">
+        <v>1.4443</v>
+      </c>
+      <c r="AE87" s="11" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="AF87" s="11" t="n">
+        <v>1.4306</v>
+      </c>
+      <c r="AG87" s="11" t="n">
+        <v>1.4236</v>
+      </c>
+      <c r="AH87" s="11" t="n">
+        <v>1.4168</v>
+      </c>
+      <c r="AI87" s="11" t="n">
+        <v>1.4102</v>
+      </c>
+      <c r="AJ87" s="11" t="n">
+        <v>1.4038</v>
+      </c>
+      <c r="AK87" s="11" t="n">
+        <v>1.3979</v>
+      </c>
+      <c r="AL87" s="11" t="n">
+        <v>1.3924</v>
+      </c>
+      <c r="AM87" s="11" t="n">
+        <v>1.3874</v>
+      </c>
+      <c r="AN87" s="11" t="n">
+        <v>1.383</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="n">
+        <v>5.6724</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>5.6866</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>5.7979</v>
+      </c>
+      <c r="G88" s="11" t="n">
+        <v>5.6256</v>
+      </c>
+      <c r="H88" s="11" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="I88" s="11" t="n">
+        <v>5.3756</v>
+      </c>
+      <c r="J88" s="11" t="n">
+        <v>5.3422</v>
+      </c>
+      <c r="K88" s="11" t="n">
+        <v>5.268</v>
+      </c>
+      <c r="L88" s="11" t="n">
+        <v>5.2006</v>
+      </c>
+      <c r="M88" s="11" t="n">
+        <v>5.1401</v>
+      </c>
+      <c r="N88" s="11" t="n">
+        <v>5.0865</v>
+      </c>
+      <c r="O88" s="11" t="n">
+        <v>5.0398</v>
+      </c>
+      <c r="P88" s="11" t="n">
+        <v>4.9999</v>
+      </c>
+      <c r="Q88" s="11" t="n">
+        <v>4.8405</v>
+      </c>
+      <c r="R88" s="11" t="n">
+        <v>4.7123</v>
+      </c>
+      <c r="S88" s="11" t="n">
+        <v>4.6153</v>
+      </c>
+      <c r="T88" s="11" t="n">
+        <v>4.5496</v>
+      </c>
+      <c r="U88" s="11" t="n">
+        <v>4.515</v>
+      </c>
+      <c r="V88" s="11" t="n">
+        <v>4.5116</v>
+      </c>
+      <c r="W88" s="11" t="n">
+        <v>4.5395</v>
+      </c>
+      <c r="X88" s="11" t="n">
+        <v>4.5985</v>
+      </c>
+      <c r="Y88" s="11" t="n">
+        <v>4.6888</v>
+      </c>
+      <c r="Z88" s="11" t="n">
+        <v>4.8103</v>
+      </c>
+      <c r="AA88" s="11" t="n">
+        <v>4.9629</v>
+      </c>
+      <c r="AB88" s="11" t="n">
+        <v>5.1468</v>
+      </c>
+      <c r="AC88" s="11" t="n">
+        <v>5.2868</v>
+      </c>
+      <c r="AD88" s="11" t="n">
+        <v>5.4081</v>
+      </c>
+      <c r="AE88" s="11" t="n">
+        <v>5.5108</v>
+      </c>
+      <c r="AF88" s="11" t="n">
+        <v>5.5948</v>
+      </c>
+      <c r="AG88" s="11" t="n">
+        <v>5.6601</v>
+      </c>
+      <c r="AH88" s="11" t="n">
+        <v>5.7068</v>
+      </c>
+      <c r="AI88" s="11" t="n">
+        <v>5.7348</v>
+      </c>
+      <c r="AJ88" s="11" t="n">
+        <v>5.7441</v>
+      </c>
+      <c r="AK88" s="11" t="n">
+        <v>5.7348</v>
+      </c>
+      <c r="AL88" s="11" t="n">
+        <v>5.7068</v>
+      </c>
+      <c r="AM88" s="11" t="n">
+        <v>5.6601</v>
+      </c>
+      <c r="AN88" s="11" t="n">
+        <v>5.5948</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="n">
+        <v>5.6724</v>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>5.6546</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>5.7102</v>
+      </c>
+      <c r="G89" s="11" t="n">
+        <v>5.7186</v>
+      </c>
+      <c r="H89" s="11" t="n">
+        <v>5.6746</v>
+      </c>
+      <c r="I89" s="11" t="n">
+        <v>5.6233</v>
+      </c>
+      <c r="J89" s="11" t="n">
+        <v>5.5783</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>5.5392</v>
+      </c>
+      <c r="L89" s="11" t="n">
+        <v>5.501</v>
+      </c>
+      <c r="M89" s="11" t="n">
+        <v>5.4642</v>
+      </c>
+      <c r="N89" s="11" t="n">
+        <v>5.4291</v>
+      </c>
+      <c r="O89" s="11" t="n">
+        <v>5.3958</v>
+      </c>
+      <c r="P89" s="11" t="n">
+        <v>5.3644</v>
+      </c>
+      <c r="Q89" s="11" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="R89" s="11" t="n">
+        <v>5.2903</v>
+      </c>
+      <c r="S89" s="11" t="n">
+        <v>5.2484</v>
+      </c>
+      <c r="T89" s="11" t="n">
+        <v>5.2066</v>
+      </c>
+      <c r="U89" s="11" t="n">
+        <v>5.1668</v>
+      </c>
+      <c r="V89" s="11" t="n">
+        <v>5.1303</v>
+      </c>
+      <c r="W89" s="11" t="n">
+        <v>5.0983</v>
+      </c>
+      <c r="X89" s="11" t="n">
+        <v>5.0718</v>
+      </c>
+      <c r="Y89" s="11" t="n">
+        <v>5.0512</v>
+      </c>
+      <c r="Z89" s="11" t="n">
+        <v>5.0374</v>
+      </c>
+      <c r="AA89" s="11" t="n">
+        <v>5.0307</v>
+      </c>
+      <c r="AB89" s="11" t="n">
+        <v>5.0316</v>
+      </c>
+      <c r="AC89" s="11" t="n">
+        <v>5.0391</v>
+      </c>
+      <c r="AD89" s="11" t="n">
+        <v>5.051</v>
+      </c>
+      <c r="AE89" s="11" t="n">
+        <v>5.0662</v>
+      </c>
+      <c r="AF89" s="11" t="n">
+        <v>5.0836</v>
+      </c>
+      <c r="AG89" s="11" t="n">
+        <v>5.1025</v>
+      </c>
+      <c r="AH89" s="11" t="n">
+        <v>5.1219</v>
+      </c>
+      <c r="AI89" s="11" t="n">
+        <v>5.1412</v>
+      </c>
+      <c r="AJ89" s="11" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AK89" s="11" t="n">
+        <v>5.1776</v>
+      </c>
+      <c r="AL89" s="11" t="n">
+        <v>5.1936</v>
+      </c>
+      <c r="AM89" s="11" t="n">
+        <v>5.2076</v>
+      </c>
+      <c r="AN89" s="11" t="n">
+        <v>5.2194</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="n">
+        <v>2.6406</v>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>2.6222</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>2.4141</v>
+      </c>
+      <c r="G90" s="11" t="n">
+        <v>2.4996</v>
+      </c>
+      <c r="H90" s="11" t="n">
+        <v>2.6065</v>
+      </c>
+      <c r="I90" s="11" t="n">
+        <v>2.5727</v>
+      </c>
+      <c r="J90" s="11" t="n">
+        <v>2.398</v>
+      </c>
+      <c r="K90" s="11" t="n">
+        <v>2.2043</v>
+      </c>
+      <c r="L90" s="11" t="n">
+        <v>2.0703</v>
+      </c>
+      <c r="M90" s="11" t="n">
+        <v>1.9958</v>
+      </c>
+      <c r="N90" s="11" t="n">
+        <v>1.9808</v>
+      </c>
+      <c r="O90" s="11" t="n">
+        <v>2.0254</v>
+      </c>
+      <c r="P90" s="11" t="n">
+        <v>2.1296</v>
+      </c>
+      <c r="Q90" s="11" t="n">
+        <v>2.1544</v>
+      </c>
+      <c r="R90" s="11" t="n">
+        <v>2.1764</v>
+      </c>
+      <c r="S90" s="11" t="n">
+        <v>2.1955</v>
+      </c>
+      <c r="T90" s="11" t="n">
+        <v>2.2118</v>
+      </c>
+      <c r="U90" s="11" t="n">
+        <v>2.2252</v>
+      </c>
+      <c r="V90" s="11" t="n">
+        <v>2.2357</v>
+      </c>
+      <c r="W90" s="11" t="n">
+        <v>2.2434</v>
+      </c>
+      <c r="X90" s="11" t="n">
+        <v>2.2482</v>
+      </c>
+      <c r="Y90" s="11" t="n">
+        <v>2.2502</v>
+      </c>
+      <c r="Z90" s="11" t="n">
+        <v>2.2493</v>
+      </c>
+      <c r="AA90" s="11" t="n">
+        <v>2.2455</v>
+      </c>
+      <c r="AB90" s="11" t="n">
+        <v>2.2389</v>
+      </c>
+      <c r="AC90" s="11" t="n">
+        <v>2.2453</v>
+      </c>
+      <c r="AD90" s="11" t="n">
+        <v>2.2508</v>
+      </c>
+      <c r="AE90" s="11" t="n">
+        <v>2.2554</v>
+      </c>
+      <c r="AF90" s="11" t="n">
+        <v>2.2593</v>
+      </c>
+      <c r="AG90" s="11" t="n">
+        <v>2.2622</v>
+      </c>
+      <c r="AH90" s="11" t="n">
+        <v>2.2643</v>
+      </c>
+      <c r="AI90" s="11" t="n">
+        <v>2.2656</v>
+      </c>
+      <c r="AJ90" s="11" t="n">
+        <v>2.266</v>
+      </c>
+      <c r="AK90" s="11" t="n">
+        <v>2.2656</v>
+      </c>
+      <c r="AL90" s="11" t="n">
+        <v>2.2643</v>
+      </c>
+      <c r="AM90" s="11" t="n">
+        <v>2.2622</v>
+      </c>
+      <c r="AN90" s="11" t="n">
+        <v>2.2593</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="n">
+        <v>2.6406</v>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v>2.7018</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>2.5977</v>
+      </c>
+      <c r="G91" s="11" t="n">
+        <v>2.5426</v>
+      </c>
+      <c r="H91" s="11" t="n">
+        <v>2.5482</v>
+      </c>
+      <c r="I91" s="11" t="n">
+        <v>2.5588</v>
+      </c>
+      <c r="J91" s="11" t="n">
+        <v>2.5485</v>
+      </c>
+      <c r="K91" s="11" t="n">
+        <v>2.5125</v>
+      </c>
+      <c r="L91" s="11" t="n">
+        <v>2.4649</v>
+      </c>
+      <c r="M91" s="11" t="n">
+        <v>2.4164</v>
+      </c>
+      <c r="N91" s="11" t="n">
+        <v>2.3731</v>
+      </c>
+      <c r="O91" s="11" t="n">
+        <v>2.339</v>
+      </c>
+      <c r="P91" s="11" t="n">
+        <v>2.3168</v>
+      </c>
+      <c r="Q91" s="11" t="n">
+        <v>2.3034</v>
+      </c>
+      <c r="R91" s="11" t="n">
+        <v>2.2935</v>
+      </c>
+      <c r="S91" s="11" t="n">
+        <v>2.2864</v>
+      </c>
+      <c r="T91" s="11" t="n">
+        <v>2.2812</v>
+      </c>
+      <c r="U91" s="11" t="n">
+        <v>2.2775</v>
+      </c>
+      <c r="V91" s="11" t="n">
+        <v>2.2749</v>
+      </c>
+      <c r="W91" s="11" t="n">
+        <v>2.2731</v>
+      </c>
+      <c r="X91" s="11" t="n">
+        <v>2.2717</v>
+      </c>
+      <c r="Y91" s="11" t="n">
+        <v>2.2707</v>
+      </c>
+      <c r="Z91" s="11" t="n">
+        <v>2.2697</v>
+      </c>
+      <c r="AA91" s="11" t="n">
+        <v>2.2688</v>
+      </c>
+      <c r="AB91" s="11" t="n">
+        <v>2.2677</v>
+      </c>
+      <c r="AC91" s="11" t="n">
+        <v>2.2667</v>
+      </c>
+      <c r="AD91" s="11" t="n">
+        <v>2.2659</v>
+      </c>
+      <c r="AE91" s="11" t="n">
+        <v>2.2655</v>
+      </c>
+      <c r="AF91" s="11" t="n">
+        <v>2.2652</v>
+      </c>
+      <c r="AG91" s="11" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="AH91" s="11" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="AI91" s="11" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="AJ91" s="11" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="AK91" s="11" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="AL91" s="11" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="AM91" s="11" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="AN91" s="11" t="n">
+        <v>2.2649</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN85"/>
+  <autoFilter ref="A1:AN91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43264,7 +44074,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-10  (14 daily snapshots, 84 curve rows)</t>
+          <t>2026-08-28 to 2026-09-11  (15 daily snapshots, 90 curve rows)</t>
         </is>
       </c>
     </row>
@@ -43360,7 +44170,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-10  (19 rows)</t>
+          <t>2026-08-23 to 2026-09-11  (20 rows)</t>
         </is>
       </c>
     </row>
@@ -43372,7 +44182,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-11 06:00 local</t>
+          <t>2026-09-11 19:11 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$20</f>
+              <f>'Daily Index'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$20</f>
+              <f>'Daily Index'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$20</f>
+              <f>'Daily Index'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$20</f>
+              <f>'Daily Index'!$C$2:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$20</f>
+              <f>'Daily Index'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$20</f>
+              <f>'Daily Index'!$D$2:$D$21</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1528,8 +1528,34 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>0.5311</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>1.8026</v>
+      </c>
+      <c r="E21" s="4">
+        <f>IF(OR(B21="",B20=""),"",B21/B20-1)</f>
+        <v/>
+      </c>
+      <c r="F21" s="4">
+        <f>IF(OR(C21="",C20=""),"",C21/C20-1)</f>
+        <v/>
+      </c>
+      <c r="G21" s="4">
+        <f>IF(OR(D21="",D20=""),"",D21/D20-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44146,7 +44172,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-09  (19 rows)</t>
+          <t>2026-08-22 to 2026-09-10  (20 rows)</t>
         </is>
       </c>
     </row>
@@ -44182,7 +44208,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11 local</t>
+          <t>2026-09-12 05:48 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
   </definedNames>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$21</f>
+              <f>'GPU Rental'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$21</f>
+              <f>'GPU Rental'!$B$2:$B$22</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$21</f>
+              <f>'GPU Rental'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$21</f>
+              <f>'GPU Rental'!$C$2:$C$22</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$21</f>
+              <f>'GPU Rental'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$21</f>
+              <f>'GPU Rental'!$D$2:$D$22</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$21</f>
+              <f>'GPU Rental'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$21</f>
+              <f>'GPU Rental'!$E$2:$E$22</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$21</f>
+              <f>'GPU Rental'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$21</f>
+              <f>'GPU Rental'!$F$2:$F$22</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$21</f>
+              <f>'GPU Rental'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$21</f>
+              <f>'GPU Rental'!$G$2:$G$22</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$21</f>
+              <f>'GPU Rental'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$21</f>
+              <f>'GPU Rental'!$H$2:$H$22</f>
             </numRef>
           </val>
         </ser>
@@ -1566,7 +1566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2715,8 +2715,62 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I22" s="4">
+        <f>IF(OR(B22="",B21=""),"",B22/B21-1)</f>
+        <v/>
+      </c>
+      <c r="J22" s="4">
+        <f>IF(OR(C22="",C21=""),"",C22/C21-1)</f>
+        <v/>
+      </c>
+      <c r="K22" s="4">
+        <f>IF(OR(D22="",D21=""),"",D22/D21-1)</f>
+        <v/>
+      </c>
+      <c r="L22" s="4">
+        <f>IF(OR(E22="",E21=""),"",E22/E21-1)</f>
+        <v/>
+      </c>
+      <c r="M22" s="4">
+        <f>IF(OR(F22="",F21=""),"",F22/F21-1)</f>
+        <v/>
+      </c>
+      <c r="N22" s="4">
+        <f>IF(OR(G22="",G21=""),"",G22/G21-1)</f>
+        <v/>
+      </c>
+      <c r="O22" s="4">
+        <f>IF(OR(H22="",H21=""),"",H22/H21-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O21"/>
+  <autoFilter ref="A1:O22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2727,7 +2781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN91"/>
+  <dimension ref="A1:AN97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14314,8 +14368,764 @@
         <v>2.2649</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="n">
+        <v>1.5978</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>1.6006</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>1.7171</v>
+      </c>
+      <c r="G92" s="11" t="n">
+        <v>1.6403</v>
+      </c>
+      <c r="H92" s="11" t="n">
+        <v>1.5955</v>
+      </c>
+      <c r="I92" s="11" t="n">
+        <v>1.5512</v>
+      </c>
+      <c r="J92" s="11" t="n">
+        <v>1.5076</v>
+      </c>
+      <c r="K92" s="11" t="n">
+        <v>1.4301</v>
+      </c>
+      <c r="L92" s="11" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="M92" s="11" t="n">
+        <v>1.3423</v>
+      </c>
+      <c r="N92" s="11" t="n">
+        <v>1.3319</v>
+      </c>
+      <c r="O92" s="11" t="n">
+        <v>1.3439</v>
+      </c>
+      <c r="P92" s="11" t="n">
+        <v>1.3783</v>
+      </c>
+      <c r="Q92" s="11" t="n">
+        <v>1.3919</v>
+      </c>
+      <c r="R92" s="11" t="n">
+        <v>1.4019</v>
+      </c>
+      <c r="S92" s="11" t="n">
+        <v>1.4083</v>
+      </c>
+      <c r="T92" s="11" t="n">
+        <v>1.4109</v>
+      </c>
+      <c r="U92" s="11" t="n">
+        <v>1.4099</v>
+      </c>
+      <c r="V92" s="11" t="n">
+        <v>1.4052</v>
+      </c>
+      <c r="W92" s="11" t="n">
+        <v>1.3968</v>
+      </c>
+      <c r="X92" s="11" t="n">
+        <v>1.3847</v>
+      </c>
+      <c r="Y92" s="11" t="n">
+        <v>1.3689</v>
+      </c>
+      <c r="Z92" s="11" t="n">
+        <v>1.3495</v>
+      </c>
+      <c r="AA92" s="11" t="n">
+        <v>1.3264</v>
+      </c>
+      <c r="AB92" s="11" t="n">
+        <v>1.2996</v>
+      </c>
+      <c r="AC92" s="11" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="AD92" s="11" t="n">
+        <v>1.2509</v>
+      </c>
+      <c r="AE92" s="11" t="n">
+        <v>1.2318</v>
+      </c>
+      <c r="AF92" s="11" t="n">
+        <v>1.2161</v>
+      </c>
+      <c r="AG92" s="11" t="n">
+        <v>1.2039</v>
+      </c>
+      <c r="AH92" s="11" t="n">
+        <v>1.1952</v>
+      </c>
+      <c r="AI92" s="11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AJ92" s="11" t="n">
+        <v>1.1883</v>
+      </c>
+      <c r="AK92" s="11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL92" s="11" t="n">
+        <v>1.1952</v>
+      </c>
+      <c r="AM92" s="11" t="n">
+        <v>1.2039</v>
+      </c>
+      <c r="AN92" s="11" t="n">
+        <v>1.2161</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="n">
+        <v>1.5978</v>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v>1.5584</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>1.6167</v>
+      </c>
+      <c r="G93" s="11" t="n">
+        <v>1.6427</v>
+      </c>
+      <c r="H93" s="11" t="n">
+        <v>1.6365</v>
+      </c>
+      <c r="I93" s="11" t="n">
+        <v>1.6239</v>
+      </c>
+      <c r="J93" s="11" t="n">
+        <v>1.6081</v>
+      </c>
+      <c r="K93" s="11" t="n">
+        <v>1.588</v>
+      </c>
+      <c r="L93" s="11" t="n">
+        <v>1.5646</v>
+      </c>
+      <c r="M93" s="11" t="n">
+        <v>1.5415</v>
+      </c>
+      <c r="N93" s="11" t="n">
+        <v>1.5209</v>
+      </c>
+      <c r="O93" s="11" t="n">
+        <v>1.5041</v>
+      </c>
+      <c r="P93" s="11" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="Q93" s="11" t="n">
+        <v>1.4838</v>
+      </c>
+      <c r="R93" s="11" t="n">
+        <v>1.4776</v>
+      </c>
+      <c r="S93" s="11" t="n">
+        <v>1.4728</v>
+      </c>
+      <c r="T93" s="11" t="n">
+        <v>1.4689</v>
+      </c>
+      <c r="U93" s="11" t="n">
+        <v>1.4654</v>
+      </c>
+      <c r="V93" s="11" t="n">
+        <v>1.4622</v>
+      </c>
+      <c r="W93" s="11" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="X93" s="11" t="n">
+        <v>1.4556</v>
+      </c>
+      <c r="Y93" s="11" t="n">
+        <v>1.4519</v>
+      </c>
+      <c r="Z93" s="11" t="n">
+        <v>1.4477</v>
+      </c>
+      <c r="AA93" s="11" t="n">
+        <v>1.4429</v>
+      </c>
+      <c r="AB93" s="11" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="AC93" s="11" t="n">
+        <v>1.4315</v>
+      </c>
+      <c r="AD93" s="11" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="AE93" s="11" t="n">
+        <v>1.4181</v>
+      </c>
+      <c r="AF93" s="11" t="n">
+        <v>1.4112</v>
+      </c>
+      <c r="AG93" s="11" t="n">
+        <v>1.4043</v>
+      </c>
+      <c r="AH93" s="11" t="n">
+        <v>1.3974</v>
+      </c>
+      <c r="AI93" s="11" t="n">
+        <v>1.3908</v>
+      </c>
+      <c r="AJ93" s="11" t="n">
+        <v>1.3845</v>
+      </c>
+      <c r="AK93" s="11" t="n">
+        <v>1.3786</v>
+      </c>
+      <c r="AL93" s="11" t="n">
+        <v>1.3731</v>
+      </c>
+      <c r="AM93" s="11" t="n">
+        <v>1.3681</v>
+      </c>
+      <c r="AN93" s="11" t="n">
+        <v>1.3637</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>5.6747</v>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>5.6647</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>5.8322</v>
+      </c>
+      <c r="G94" s="11" t="n">
+        <v>5.6132</v>
+      </c>
+      <c r="H94" s="11" t="n">
+        <v>5.4068</v>
+      </c>
+      <c r="I94" s="11" t="n">
+        <v>5.3042</v>
+      </c>
+      <c r="J94" s="11" t="n">
+        <v>5.3055</v>
+      </c>
+      <c r="K94" s="11" t="n">
+        <v>5.2585</v>
+      </c>
+      <c r="L94" s="11" t="n">
+        <v>5.2091</v>
+      </c>
+      <c r="M94" s="11" t="n">
+        <v>5.1572</v>
+      </c>
+      <c r="N94" s="11" t="n">
+        <v>5.1028</v>
+      </c>
+      <c r="O94" s="11" t="n">
+        <v>5.046</v>
+      </c>
+      <c r="P94" s="11" t="n">
+        <v>4.9867</v>
+      </c>
+      <c r="Q94" s="11" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="R94" s="11" t="n">
+        <v>4.6679</v>
+      </c>
+      <c r="S94" s="11" t="n">
+        <v>4.5604</v>
+      </c>
+      <c r="T94" s="11" t="n">
+        <v>4.4875</v>
+      </c>
+      <c r="U94" s="11" t="n">
+        <v>4.4492</v>
+      </c>
+      <c r="V94" s="11" t="n">
+        <v>4.4455</v>
+      </c>
+      <c r="W94" s="11" t="n">
+        <v>4.4764</v>
+      </c>
+      <c r="X94" s="11" t="n">
+        <v>4.5419</v>
+      </c>
+      <c r="Y94" s="11" t="n">
+        <v>4.642</v>
+      </c>
+      <c r="Z94" s="11" t="n">
+        <v>4.7766</v>
+      </c>
+      <c r="AA94" s="11" t="n">
+        <v>4.9459</v>
+      </c>
+      <c r="AB94" s="11" t="n">
+        <v>5.1498</v>
+      </c>
+      <c r="AC94" s="11" t="n">
+        <v>5.3051</v>
+      </c>
+      <c r="AD94" s="11" t="n">
+        <v>5.4396</v>
+      </c>
+      <c r="AE94" s="11" t="n">
+        <v>5.5534</v>
+      </c>
+      <c r="AF94" s="11" t="n">
+        <v>5.6466</v>
+      </c>
+      <c r="AG94" s="11" t="n">
+        <v>5.719</v>
+      </c>
+      <c r="AH94" s="11" t="n">
+        <v>5.7708</v>
+      </c>
+      <c r="AI94" s="11" t="n">
+        <v>5.8018</v>
+      </c>
+      <c r="AJ94" s="11" t="n">
+        <v>5.8122</v>
+      </c>
+      <c r="AK94" s="11" t="n">
+        <v>5.8018</v>
+      </c>
+      <c r="AL94" s="11" t="n">
+        <v>5.7708</v>
+      </c>
+      <c r="AM94" s="11" t="n">
+        <v>5.719</v>
+      </c>
+      <c r="AN94" s="11" t="n">
+        <v>5.6466</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>5.6747</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>5.6131</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>5.6969</v>
+      </c>
+      <c r="G95" s="11" t="n">
+        <v>5.7162</v>
+      </c>
+      <c r="H95" s="11" t="n">
+        <v>5.6625</v>
+      </c>
+      <c r="I95" s="11" t="n">
+        <v>5.5994</v>
+      </c>
+      <c r="J95" s="11" t="n">
+        <v>5.5488</v>
+      </c>
+      <c r="K95" s="11" t="n">
+        <v>5.5107</v>
+      </c>
+      <c r="L95" s="11" t="n">
+        <v>5.4762</v>
+      </c>
+      <c r="M95" s="11" t="n">
+        <v>5.4436</v>
+      </c>
+      <c r="N95" s="11" t="n">
+        <v>5.4123</v>
+      </c>
+      <c r="O95" s="11" t="n">
+        <v>5.3816</v>
+      </c>
+      <c r="P95" s="11" t="n">
+        <v>5.3512</v>
+      </c>
+      <c r="Q95" s="11" t="n">
+        <v>5.3161</v>
+      </c>
+      <c r="R95" s="11" t="n">
+        <v>5.2747</v>
+      </c>
+      <c r="S95" s="11" t="n">
+        <v>5.2304</v>
+      </c>
+      <c r="T95" s="11" t="n">
+        <v>5.1861</v>
+      </c>
+      <c r="U95" s="11" t="n">
+        <v>5.1437</v>
+      </c>
+      <c r="V95" s="11" t="n">
+        <v>5.1049</v>
+      </c>
+      <c r="W95" s="11" t="n">
+        <v>5.0708</v>
+      </c>
+      <c r="X95" s="11" t="n">
+        <v>5.0426</v>
+      </c>
+      <c r="Y95" s="11" t="n">
+        <v>5.021</v>
+      </c>
+      <c r="Z95" s="11" t="n">
+        <v>5.0067</v>
+      </c>
+      <c r="AA95" s="11" t="n">
+        <v>5.0003</v>
+      </c>
+      <c r="AB95" s="11" t="n">
+        <v>5.0021</v>
+      </c>
+      <c r="AC95" s="11" t="n">
+        <v>5.0112</v>
+      </c>
+      <c r="AD95" s="11" t="n">
+        <v>5.0252</v>
+      </c>
+      <c r="AE95" s="11" t="n">
+        <v>5.0427</v>
+      </c>
+      <c r="AF95" s="11" t="n">
+        <v>5.0626</v>
+      </c>
+      <c r="AG95" s="11" t="n">
+        <v>5.0841</v>
+      </c>
+      <c r="AH95" s="11" t="n">
+        <v>5.1062</v>
+      </c>
+      <c r="AI95" s="11" t="n">
+        <v>5.1282</v>
+      </c>
+      <c r="AJ95" s="11" t="n">
+        <v>5.1494</v>
+      </c>
+      <c r="AK95" s="11" t="n">
+        <v>5.1694</v>
+      </c>
+      <c r="AL95" s="11" t="n">
+        <v>5.1876</v>
+      </c>
+      <c r="AM95" s="11" t="n">
+        <v>5.2036</v>
+      </c>
+      <c r="AN95" s="11" t="n">
+        <v>5.2169</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="n">
+        <v>2.6513</v>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>2.6058</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="G96" s="11" t="n">
+        <v>2.4751</v>
+      </c>
+      <c r="H96" s="11" t="n">
+        <v>2.5852</v>
+      </c>
+      <c r="I96" s="11" t="n">
+        <v>2.5509</v>
+      </c>
+      <c r="J96" s="11" t="n">
+        <v>2.3722</v>
+      </c>
+      <c r="K96" s="11" t="n">
+        <v>2.1742</v>
+      </c>
+      <c r="L96" s="11" t="n">
+        <v>2.0372</v>
+      </c>
+      <c r="M96" s="11" t="n">
+        <v>1.9612</v>
+      </c>
+      <c r="N96" s="11" t="n">
+        <v>1.9462</v>
+      </c>
+      <c r="O96" s="11" t="n">
+        <v>1.9923</v>
+      </c>
+      <c r="P96" s="11" t="n">
+        <v>2.0994</v>
+      </c>
+      <c r="Q96" s="11" t="n">
+        <v>2.1264</v>
+      </c>
+      <c r="R96" s="11" t="n">
+        <v>2.1501</v>
+      </c>
+      <c r="S96" s="11" t="n">
+        <v>2.1705</v>
+      </c>
+      <c r="T96" s="11" t="n">
+        <v>2.1877</v>
+      </c>
+      <c r="U96" s="11" t="n">
+        <v>2.2016</v>
+      </c>
+      <c r="V96" s="11" t="n">
+        <v>2.2123</v>
+      </c>
+      <c r="W96" s="11" t="n">
+        <v>2.2197</v>
+      </c>
+      <c r="X96" s="11" t="n">
+        <v>2.2238</v>
+      </c>
+      <c r="Y96" s="11" t="n">
+        <v>2.2247</v>
+      </c>
+      <c r="Z96" s="11" t="n">
+        <v>2.2223</v>
+      </c>
+      <c r="AA96" s="11" t="n">
+        <v>2.2167</v>
+      </c>
+      <c r="AB96" s="11" t="n">
+        <v>2.2078</v>
+      </c>
+      <c r="AC96" s="11" t="n">
+        <v>2.2125</v>
+      </c>
+      <c r="AD96" s="11" t="n">
+        <v>2.2166</v>
+      </c>
+      <c r="AE96" s="11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AF96" s="11" t="n">
+        <v>2.2228</v>
+      </c>
+      <c r="AG96" s="11" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AH96" s="11" t="n">
+        <v>2.2266</v>
+      </c>
+      <c r="AI96" s="11" t="n">
+        <v>2.2275</v>
+      </c>
+      <c r="AJ96" s="11" t="n">
+        <v>2.2278</v>
+      </c>
+      <c r="AK96" s="11" t="n">
+        <v>2.2275</v>
+      </c>
+      <c r="AL96" s="11" t="n">
+        <v>2.2266</v>
+      </c>
+      <c r="AM96" s="11" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AN96" s="11" t="n">
+        <v>2.2228</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="n">
+        <v>2.6513</v>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v>2.6902</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G97" s="11" t="n">
+        <v>2.5215</v>
+      </c>
+      <c r="H97" s="11" t="n">
+        <v>2.5267</v>
+      </c>
+      <c r="I97" s="11" t="n">
+        <v>2.5374</v>
+      </c>
+      <c r="J97" s="11" t="n">
+        <v>2.5267</v>
+      </c>
+      <c r="K97" s="11" t="n">
+        <v>2.4898</v>
+      </c>
+      <c r="L97" s="11" t="n">
+        <v>2.4411</v>
+      </c>
+      <c r="M97" s="11" t="n">
+        <v>2.3915</v>
+      </c>
+      <c r="N97" s="11" t="n">
+        <v>2.3472</v>
+      </c>
+      <c r="O97" s="11" t="n">
+        <v>2.3124</v>
+      </c>
+      <c r="P97" s="11" t="n">
+        <v>2.2897</v>
+      </c>
+      <c r="Q97" s="11" t="n">
+        <v>2.2762</v>
+      </c>
+      <c r="R97" s="11" t="n">
+        <v>2.2663</v>
+      </c>
+      <c r="S97" s="11" t="n">
+        <v>2.2593</v>
+      </c>
+      <c r="T97" s="11" t="n">
+        <v>2.2543</v>
+      </c>
+      <c r="U97" s="11" t="n">
+        <v>2.2508</v>
+      </c>
+      <c r="V97" s="11" t="n">
+        <v>2.2484</v>
+      </c>
+      <c r="W97" s="11" t="n">
+        <v>2.2467</v>
+      </c>
+      <c r="X97" s="11" t="n">
+        <v>2.2454</v>
+      </c>
+      <c r="Y97" s="11" t="n">
+        <v>2.2445</v>
+      </c>
+      <c r="Z97" s="11" t="n">
+        <v>2.2435</v>
+      </c>
+      <c r="AA97" s="11" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="AB97" s="11" t="n">
+        <v>2.2412</v>
+      </c>
+      <c r="AC97" s="11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD97" s="11" t="n">
+        <v>2.239</v>
+      </c>
+      <c r="AE97" s="11" t="n">
+        <v>2.2382</v>
+      </c>
+      <c r="AF97" s="11" t="n">
+        <v>2.2376</v>
+      </c>
+      <c r="AG97" s="11" t="n">
+        <v>2.2372</v>
+      </c>
+      <c r="AH97" s="11" t="n">
+        <v>2.2368</v>
+      </c>
+      <c r="AI97" s="11" t="n">
+        <v>2.2365</v>
+      </c>
+      <c r="AJ97" s="11" t="n">
+        <v>2.2362</v>
+      </c>
+      <c r="AK97" s="11" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="AL97" s="11" t="n">
+        <v>2.2357</v>
+      </c>
+      <c r="AM97" s="11" t="n">
+        <v>2.2354</v>
+      </c>
+      <c r="AN97" s="11" t="n">
+        <v>2.2351</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN91"/>
+  <autoFilter ref="A1:AN97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44100,7 +44910,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-11  (15 daily snapshots, 90 curve rows)</t>
+          <t>2026-08-28 to 2026-09-12  (16 daily snapshots, 96 curve rows)</t>
         </is>
       </c>
     </row>
@@ -44196,7 +45006,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-11  (20 rows)</t>
+          <t>2026-08-23 to 2026-09-12  (21 rows)</t>
         </is>
       </c>
     </row>
@@ -44208,7 +45018,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-12 05:48 local</t>
+          <t>2026-09-12 18:28 local</t>
         </is>
       </c>
     </row>
